--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -460,7 +460,7 @@
         <v>Aarhus, DK</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -501,7 +501,7 @@
         <v>Trondheim, NO</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -542,7 +542,7 @@
         <v>Kongsberg, NO</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -583,7 +583,7 @@
         <v>Solna, SE</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -624,7 +624,7 @@
         <v>Fornebu, NO</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -665,7 +665,7 @@
         <v>Lund, SE</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v>Stockholm, SE</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -747,7 +747,7 @@
         <v>Södertälje, SE</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -788,7 +788,7 @@
         <v>Gothenburg, SE</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -829,7 +829,7 @@
         <v>Espoo, FI</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -870,7 +870,7 @@
         <v>Geneva, CH</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -911,7 +911,7 @@
         <v>Augsburg, DE</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -952,7 +952,7 @@
         <v>Friedrichshafen, DE</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -993,7 +993,7 @@
         <v>Hanover, DE</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1034,7 +1034,7 @@
         <v>London, UK</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1075,7 +1075,7 @@
         <v>Bucharest, RO</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1116,7 +1116,7 @@
         <v>Cambridge, UK</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1157,7 +1157,7 @@
         <v>Abingdon, UK</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1198,7 +1198,7 @@
         <v>Bilbao, ES</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1239,7 +1239,7 @@
         <v>Bochum, DE</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1280,7 +1280,7 @@
         <v>Tettnang, DE</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1321,7 +1321,7 @@
         <v>Bratislava, SK</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>Manchester, UK</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v>Helsinki, FI</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1444,7 +1444,7 @@
         <v>Zurich, CH</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1485,7 +1485,7 @@
         <v>Munich, DE</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1526,7 +1526,7 @@
         <v>Stockholm, SE</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1567,7 +1567,7 @@
         <v>Munich, DE</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1608,7 +1608,7 @@
         <v>Gerlingen, DE</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1649,7 +1649,7 @@
         <v>Neubiberg, DE</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="str">
         <v/>

--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -472,13 +472,13 @@
         <v>High</v>
       </c>
       <c r="K2" t="str">
-        <v>Systems,Hardware,Embedded</v>
+        <v>Embedded,Systems,Hardware</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-04 22:59:49</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-02-04 22:59:49</v>
+        <v>2026-03-26 16:06:45</v>
       </c>
     </row>
     <row r="3">

--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -448,7 +448,7 @@
         <v>Vestas</v>
       </c>
       <c r="C2" t="str">
-        <v>Researching</v>
+        <v>Applied</v>
       </c>
       <c r="D2" t="str">
         <v>2026 Summer | Nordic HQ; systems/embedded fit. Initiative application.</v>
@@ -478,7 +478,7 @@
         <v>2026-02-04 22:59:49</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-03-26 16:06:45</v>
+        <v>2026-03-26 20:11:30</v>
       </c>
     </row>
     <row r="3">

--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,25 +442,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B2" t="str">
-        <v>Vestas</v>
+        <v>Fraunhofer SIT</v>
       </c>
       <c r="C2" t="str">
-        <v>Applied</v>
+        <v>Researching</v>
       </c>
       <c r="D2" t="str">
-        <v>2026 Summer | Nordic HQ; systems/embedded fit. Initiative application.</v>
+        <v>2026 Summer | Embedded and IoT security institute working on protocol security, trusted computing, and secure firmware updates. Initiative application.</v>
       </c>
       <c r="E2" t="str">
-        <v>https://www.vestas.com</v>
+        <v>https://www.sit.fraunhofer.de/en/</v>
       </c>
       <c r="F2" t="str">
-        <v>Aarhus, DK</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -472,36 +472,36 @@
         <v>High</v>
       </c>
       <c r="K2" t="str">
-        <v>Embedded,Systems,Hardware</v>
+        <v>Embedded,Firmware,Security,IoT,Systems</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-04 22:59:49</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-03-26 20:11:30</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B3" t="str">
-        <v>Nordic Semiconductor</v>
+        <v>Fraunhofer EMFT</v>
       </c>
       <c r="C3" t="str">
         <v>Researching</v>
       </c>
       <c r="D3" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Trusted electronics team focused on tamper protection, PUF-based key generation, and secure IoT hardware. Initiative application.</v>
       </c>
       <c r="E3" t="str">
-        <v>https://www.nordicsemi.com</v>
+        <v>https://www.emft.fraunhofer.de/en.html</v>
       </c>
       <c r="F3" t="str">
-        <v>Trondheim, NO</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -513,36 +513,36 @@
         <v>High</v>
       </c>
       <c r="K3" t="str">
-        <v>Embedded,Hardware,IoT</v>
+        <v>Hardware,Embedded,Security,IoT,Firmware</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B4" t="str">
-        <v>Kongsberg Gruppen</v>
+        <v>Fraunhofer IMS</v>
       </c>
       <c r="C4" t="str">
         <v>Researching</v>
       </c>
       <c r="D4" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Trusted electronics group researching secure key memory, PUFs, encrypted firmware storage, and secure RISC-V cores. Initiative application.</v>
       </c>
       <c r="E4" t="str">
-        <v>https://www.kongsberg.com</v>
+        <v>https://www.ims.fraunhofer.de/en.html</v>
       </c>
       <c r="F4" t="str">
-        <v>Kongsberg, NO</v>
+        <v>Duisburg, DE</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -554,36 +554,36 @@
         <v>High</v>
       </c>
       <c r="K4" t="str">
-        <v>Embedded,Hardware,Security</v>
+        <v>Hardware,Embedded,Firmware,Security,Systems</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B5" t="str">
-        <v>Telia Company</v>
+        <v>TUM Chair of IT Security</v>
       </c>
       <c r="C5" t="str">
         <v>Researching</v>
       </c>
       <c r="D5" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | University chair with a strong hardware and embedded security track plus thesis and student project intake. Initiative application.</v>
       </c>
       <c r="E5" t="str">
-        <v>https://www.teliacompany.com</v>
+        <v>https://www.sec.in.tum.de/i20/</v>
       </c>
       <c r="F5" t="str">
-        <v>Solna, SE</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -592,39 +592,39 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K5" t="str">
-        <v>Security,Systems</v>
+        <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B6" t="str">
-        <v>Telenor</v>
+        <v>TU Berlin SecT</v>
       </c>
       <c r="C6" t="str">
         <v>Researching</v>
       </c>
       <c r="D6" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Security in Telecommunications chair covering hardware security, secure embedded systems, and side-channel attacks. Initiative application.</v>
       </c>
       <c r="E6" t="str">
-        <v>https://www.telenor.com</v>
+        <v>https://www.tu.berlin/en/sect</v>
       </c>
       <c r="F6" t="str">
-        <v>Fornebu, NO</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -633,39 +633,39 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K6" t="str">
-        <v>Security,Systems</v>
+        <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B7" t="str">
-        <v>Axis Communications</v>
+        <v>KIT Chair of Dependable Nano Computing (CDNC)</v>
       </c>
       <c r="C7" t="str">
         <v>Researching</v>
       </c>
       <c r="D7" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Hardware security lab known for FPGA side-channel and fault-attack research with active student thesis opportunities. Initiative application.</v>
       </c>
       <c r="E7" t="str">
-        <v>https://www.axis.com</v>
+        <v>https://cdnc.itec.kit.edu/</v>
       </c>
       <c r="F7" t="str">
-        <v>Lund, SE</v>
+        <v>Karlsruhe, DE</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -677,36 +677,36 @@
         <v>High</v>
       </c>
       <c r="K7" t="str">
-        <v>Embedded,Hardware,Security</v>
+        <v>Hardware,Security,Embedded,Systems,Firmware</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B8" t="str">
-        <v>Saab</v>
+        <v>TU Darmstadt ImpSec</v>
       </c>
       <c r="C8" t="str">
         <v>Researching</v>
       </c>
       <c r="D8" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Implementation security chair focused on side-channel and fault attacks, ASICs, FPGAs, and microprocessor security. Initiative application.</v>
       </c>
       <c r="E8" t="str">
-        <v>https://www.saab.com</v>
+        <v>https://www.informatik.tu-darmstadt.de/impsec/start_impsec/index.en.jsp</v>
       </c>
       <c r="F8" t="str">
-        <v>Stockholm, SE</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -718,36 +718,36 @@
         <v>High</v>
       </c>
       <c r="K8" t="str">
-        <v>Embedded,Hardware,Security</v>
+        <v>Hardware,Security,Embedded,Firmware,Systems</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B9" t="str">
-        <v>Scania</v>
+        <v>Fraunhofer FKIE</v>
       </c>
       <c r="C9" t="str">
         <v>Researching</v>
       </c>
       <c r="D9" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Applied security institute doing firmware reverse engineering, vulnerability analysis, and embedded-device forensics. Initiative application.</v>
       </c>
       <c r="E9" t="str">
-        <v>https://www.scania.com</v>
+        <v>https://www.fkie.fraunhofer.de/en.html</v>
       </c>
       <c r="F9" t="str">
-        <v>Södertälje, SE</v>
+        <v>Bonn, DE</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -759,36 +759,36 @@
         <v>High</v>
       </c>
       <c r="K9" t="str">
-        <v>Embedded,Hardware,Systems</v>
+        <v>Firmware,Security,Embedded,Systems,Hardware</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B10" t="str">
-        <v>Volvo Group</v>
+        <v>Fraunhofer IIS</v>
       </c>
       <c r="C10" t="str">
         <v>Researching</v>
       </c>
       <c r="D10" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Secure system-on-chip research around secure RISC-V, secure boot, firmware updates, and crypto accelerators. Initiative application.</v>
       </c>
       <c r="E10" t="str">
-        <v>https://www.volvogroup.com</v>
+        <v>https://www.iis.fraunhofer.de/en.html</v>
       </c>
       <c r="F10" t="str">
-        <v>Gothenburg, SE</v>
+        <v>Erlangen, DE</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -800,36 +800,36 @@
         <v>High</v>
       </c>
       <c r="K10" t="str">
-        <v>Embedded,Hardware,Systems</v>
+        <v>Hardware,Embedded,Firmware,Security,Systems</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B11" t="str">
-        <v>Nokia</v>
+        <v>Fraunhofer IPMS</v>
       </c>
       <c r="C11" t="str">
         <v>Researching</v>
       </c>
       <c r="D11" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Trusted electronics work on secure manufacturing, PUF trust anchors, encrypted firmware, and secure embedded devices. Initiative application.</v>
       </c>
       <c r="E11" t="str">
-        <v>https://www.nokia.com</v>
+        <v>https://www.ipms.fraunhofer.de/en.html</v>
       </c>
       <c r="F11" t="str">
-        <v>Espoo, FI</v>
+        <v>Dresden, DE</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -841,36 +841,36 @@
         <v>High</v>
       </c>
       <c r="K11" t="str">
-        <v>Systems,Hardware,Embedded</v>
+        <v>Hardware,Embedded,Firmware,Security,Systems</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="B12" t="str">
-        <v>STMicroelectronics</v>
+        <v>CARIAD Information and Automotive Security</v>
       </c>
       <c r="C12" t="str">
         <v>Researching</v>
       </c>
       <c r="D12" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Automotive security organization covering OTA, digital keys, connected vehicles, and end-to-end platform security. Initiative application.</v>
       </c>
       <c r="E12" t="str">
-        <v>https://www.st.com</v>
+        <v>https://cariad.technology/de/en/</v>
       </c>
       <c r="F12" t="str">
-        <v>Geneva, CH</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -882,36 +882,36 @@
         <v>High</v>
       </c>
       <c r="K12" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v>Security,Embedded,Firmware,Systems,IoT</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="B13" t="str">
-        <v>KUKA</v>
+        <v>AIT Center for Digital Safety &amp; Security</v>
       </c>
       <c r="C13" t="str">
         <v>Researching</v>
       </c>
       <c r="D13" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Applied research center covering secure IoT, industrial control systems, dependable systems, and wireless security. Initiative application.</v>
       </c>
       <c r="E13" t="str">
-        <v>https://www.kuka.com</v>
+        <v>https://www.ait.ac.at/en/about-the-ait/center/center-for-digital-safety-security/</v>
       </c>
       <c r="F13" t="str">
-        <v>Augsburg, DE</v>
+        <v>Vienna, AT</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -923,36 +923,36 @@
         <v>High</v>
       </c>
       <c r="K13" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v>Security,IoT,Systems,Embedded,Hardware</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="B14" t="str">
-        <v>ZF Friedrichshafen</v>
+        <v>RWTH Aachen ICE</v>
       </c>
       <c r="C14" t="str">
         <v>Researching</v>
       </c>
       <c r="D14" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Systems-on-silicon chair working on SoC design, virtual prototyping, and embedded cybersecurity-adjacent research. Initiative application.</v>
       </c>
       <c r="E14" t="str">
-        <v>https://www.zf.com</v>
+        <v>https://www.ice.rwth-aachen.de/</v>
       </c>
       <c r="F14" t="str">
-        <v>Friedrichshafen, DE</v>
+        <v>Aachen, DE</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -964,36 +964,36 @@
         <v>High</v>
       </c>
       <c r="K14" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v>Embedded,Hardware,Systems,Security,Firmware</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="B15" t="str">
-        <v>Continental</v>
+        <v>TU Darmstadt SEEMOO</v>
       </c>
       <c r="C15" t="str">
         <v>Researching</v>
       </c>
       <c r="D15" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Secure mobile networking lab with hands-on IoT, wireless security, and resilient embedded prototype work. Initiative application.</v>
       </c>
       <c r="E15" t="str">
-        <v>https://www.continental.com</v>
+        <v>https://www.seemoo.tu-darmstadt.de/</v>
       </c>
       <c r="F15" t="str">
-        <v>Hanover, DE</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1005,36 +1005,36 @@
         <v>High</v>
       </c>
       <c r="K15" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v>IoT,Security,Embedded,Systems,Firmware</v>
       </c>
       <c r="L15" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="B16" t="str">
-        <v>Mimecast</v>
+        <v>TUM Embedded Systems and IoT</v>
       </c>
       <c r="C16" t="str">
         <v>Researching</v>
       </c>
       <c r="D16" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Embedded systems chair focused on secure and reliable cyber-physical, autonomous, and IoT platforms. Initiative application.</v>
       </c>
       <c r="E16" t="str">
-        <v>https://www.mimecast.com</v>
+        <v>https://www.ce.cit.tum.de/en/esi/staff/steinhorst/</v>
       </c>
       <c r="F16" t="str">
-        <v>London, UK</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1043,36 +1043,36 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K16" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,IoT,Systems,Security,Hardware</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-03-31</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-03-31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B17" t="str">
-        <v>Bitdefender</v>
+        <v>Vestas</v>
       </c>
       <c r="C17" t="str">
-        <v>Researching</v>
+        <v>Applied</v>
       </c>
       <c r="D17" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ; systems/embedded fit. Initiative application.</v>
       </c>
       <c r="E17" t="str">
-        <v>https://www.bitdefender.com</v>
+        <v>https://www.vestas.com</v>
       </c>
       <c r="F17" t="str">
-        <v>Bucharest, RO</v>
+        <v>Aarhus, DK</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1084,36 +1084,36 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K17" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Systems,Hardware</v>
       </c>
       <c r="L17" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:59:49</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-03-26 20:11:30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B18" t="str">
-        <v>Darktrace</v>
+        <v>Nordic Semiconductor</v>
       </c>
       <c r="C18" t="str">
         <v>Researching</v>
       </c>
       <c r="D18" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E18" t="str">
-        <v>https://www.darktrace.com</v>
+        <v>https://www.nordicsemi.com</v>
       </c>
       <c r="F18" t="str">
-        <v>Cambridge, UK</v>
+        <v>Trondheim, NO</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1125,36 +1125,36 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K18" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Hardware,IoT</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B19" t="str">
-        <v>Sophos</v>
+        <v>Kongsberg Gruppen</v>
       </c>
       <c r="C19" t="str">
         <v>Researching</v>
       </c>
       <c r="D19" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E19" t="str">
-        <v>https://www.sophos.com</v>
+        <v>https://www.kongsberg.com</v>
       </c>
       <c r="F19" t="str">
-        <v>Abingdon, UK</v>
+        <v>Kongsberg, NO</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1166,36 +1166,36 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K19" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Hardware,Security</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B20" t="str">
-        <v>Panda Security</v>
+        <v>Telia Company</v>
       </c>
       <c r="C20" t="str">
         <v>Researching</v>
       </c>
       <c r="D20" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E20" t="str">
-        <v>https://www.pandasecurity.com</v>
+        <v>https://www.teliacompany.com</v>
       </c>
       <c r="F20" t="str">
-        <v>Bilbao, ES</v>
+        <v>Solna, SE</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1213,30 +1213,30 @@
         <v>Security,Systems</v>
       </c>
       <c r="L20" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B21" t="str">
-        <v>G DATA</v>
+        <v>Telenor</v>
       </c>
       <c r="C21" t="str">
         <v>Researching</v>
       </c>
       <c r="D21" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E21" t="str">
-        <v>https://www.gdatasoftware.com</v>
+        <v>https://www.telenor.com</v>
       </c>
       <c r="F21" t="str">
-        <v>Bochum, DE</v>
+        <v>Fornebu, NO</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1254,30 +1254,30 @@
         <v>Security,Systems</v>
       </c>
       <c r="L21" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B22" t="str">
-        <v>Avira</v>
+        <v>Axis Communications</v>
       </c>
       <c r="C22" t="str">
         <v>Researching</v>
       </c>
       <c r="D22" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E22" t="str">
-        <v>https://www.avira.com</v>
+        <v>https://www.axis.com</v>
       </c>
       <c r="F22" t="str">
-        <v>Tettnang, DE</v>
+        <v>Lund, SE</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1289,36 +1289,36 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K22" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Hardware,Security</v>
       </c>
       <c r="L22" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B23" t="str">
-        <v>ESET</v>
+        <v>Saab</v>
       </c>
       <c r="C23" t="str">
         <v>Researching</v>
       </c>
       <c r="D23" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E23" t="str">
-        <v>https://www.eset.com</v>
+        <v>https://www.saab.com</v>
       </c>
       <c r="F23" t="str">
-        <v>Bratislava, SK</v>
+        <v>Stockholm, SE</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1330,36 +1330,36 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K23" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Hardware,Security</v>
       </c>
       <c r="L23" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B24" t="str">
-        <v>NCC Group</v>
+        <v>Scania</v>
       </c>
       <c r="C24" t="str">
         <v>Researching</v>
       </c>
       <c r="D24" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E24" t="str">
-        <v>https://www.nccgroupplc.com</v>
+        <v>https://www.scania.com</v>
       </c>
       <c r="F24" t="str">
-        <v>Manchester, UK</v>
+        <v>Södertälje, SE</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1371,36 +1371,36 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K24" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Hardware,Systems</v>
       </c>
       <c r="L24" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B25" t="str">
-        <v>WithSecure</v>
+        <v>Volvo Group</v>
       </c>
       <c r="C25" t="str">
         <v>Researching</v>
       </c>
       <c r="D25" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E25" t="str">
-        <v>https://www.withsecure.com</v>
+        <v>https://www.volvogroup.com</v>
       </c>
       <c r="F25" t="str">
-        <v>Helsinki, FI</v>
+        <v>Gothenburg, SE</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1412,36 +1412,36 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K25" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Hardware,Systems</v>
       </c>
       <c r="L25" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B26" t="str">
-        <v>ABB</v>
+        <v>Nokia</v>
       </c>
       <c r="C26" t="str">
         <v>Researching</v>
       </c>
       <c r="D26" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E26" t="str">
-        <v>https://www.abb.com</v>
+        <v>https://www.nokia.com</v>
       </c>
       <c r="F26" t="str">
-        <v>Zurich, CH</v>
+        <v>Espoo, FI</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1456,21 +1456,21 @@
         <v>High</v>
       </c>
       <c r="K26" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v>Systems,Hardware,Embedded</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B27" t="str">
-        <v>Rohde &amp; Schwarz</v>
+        <v>STMicroelectronics</v>
       </c>
       <c r="C27" t="str">
         <v>Researching</v>
@@ -1479,10 +1479,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E27" t="str">
-        <v>https://www.rohde-schwarz.com</v>
+        <v>https://www.st.com</v>
       </c>
       <c r="F27" t="str">
-        <v>Munich, DE</v>
+        <v>Geneva, CH</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1500,18 +1500,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L27" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B28" t="str">
-        <v>Ericsson</v>
+        <v>KUKA</v>
       </c>
       <c r="C28" t="str">
         <v>Researching</v>
@@ -1520,10 +1520,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E28" t="str">
-        <v>https://www.ericsson.com</v>
+        <v>https://www.kuka.com</v>
       </c>
       <c r="F28" t="str">
-        <v>Stockholm, SE</v>
+        <v>Augsburg, DE</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1541,18 +1541,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B29" t="str">
-        <v>Siemens</v>
+        <v>ZF Friedrichshafen</v>
       </c>
       <c r="C29" t="str">
         <v>Researching</v>
@@ -1561,10 +1561,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E29" t="str">
-        <v>https://www.siemens.com</v>
+        <v>https://www.zf.com</v>
       </c>
       <c r="F29" t="str">
-        <v>Munich, DE</v>
+        <v>Friedrichshafen, DE</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1582,18 +1582,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L29" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B30" t="str">
-        <v>Bosch</v>
+        <v>Continental</v>
       </c>
       <c r="C30" t="str">
         <v>Researching</v>
@@ -1602,10 +1602,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E30" t="str">
-        <v>https://www.bosch.com</v>
+        <v>https://www.continental.com</v>
       </c>
       <c r="F30" t="str">
-        <v>Gerlingen, DE</v>
+        <v>Hanover, DE</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1623,18 +1623,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L30" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B31" t="str">
-        <v>Infineon Technologies</v>
+        <v>Mimecast</v>
       </c>
       <c r="C31" t="str">
         <v>Researching</v>
@@ -1643,10 +1643,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E31" t="str">
-        <v>https://www.infineon.com</v>
+        <v>https://www.mimecast.com</v>
       </c>
       <c r="F31" t="str">
-        <v>Neubiberg, DE</v>
+        <v>London, UK</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1658,10 +1658,10 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K31" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v>Security,Systems</v>
       </c>
       <c r="L31" t="str">
         <v>2026-02-04 22:48:04</v>
@@ -1672,22 +1672,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B32" t="str">
-        <v>Microsoft</v>
+        <v>Bitdefender</v>
       </c>
       <c r="C32" t="str">
         <v>Researching</v>
       </c>
       <c r="D32" t="str">
-        <v>2026 Summer | Microsoft Switzerland office; systems &amp; security-adjacent.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E32" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.bitdefender.com</v>
       </c>
       <c r="F32" t="str">
-        <v>Zurich, CH</v>
+        <v>Bucharest, RO</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1702,33 +1702,33 @@
         <v>Medium</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L32" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B33" t="str">
-        <v>Microsoft</v>
+        <v>Darktrace</v>
       </c>
       <c r="C33" t="str">
         <v>Researching</v>
       </c>
       <c r="D33" t="str">
-        <v>2026 Summer | Microsoft Sweden office; systems &amp; security-adjacent.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E33" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.darktrace.com</v>
       </c>
       <c r="F33" t="str">
-        <v>Stockholm, SE</v>
+        <v>Cambridge, UK</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1743,33 +1743,33 @@
         <v>Medium</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L33" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B34" t="str">
-        <v>Microsoft</v>
+        <v>Sophos</v>
       </c>
       <c r="C34" t="str">
         <v>Researching</v>
       </c>
       <c r="D34" t="str">
-        <v>2026 Summer | Microsoft Spain office; systems &amp; cloud security-adjacent.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E34" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.sophos.com</v>
       </c>
       <c r="F34" t="str">
-        <v>Madrid, ES</v>
+        <v>Abingdon, UK</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1784,33 +1784,33 @@
         <v>Medium</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L34" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B35" t="str">
-        <v>Microsoft</v>
+        <v>Panda Security</v>
       </c>
       <c r="C35" t="str">
         <v>Researching</v>
       </c>
       <c r="D35" t="str">
-        <v>2026 Summer | Microsoft Poland office; systems &amp; security-adjacent.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E35" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.pandasecurity.com</v>
       </c>
       <c r="F35" t="str">
-        <v>Warsaw, PL</v>
+        <v>Bilbao, ES</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1825,33 +1825,33 @@
         <v>Medium</v>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L35" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B36" t="str">
-        <v>Microsoft</v>
+        <v>G DATA</v>
       </c>
       <c r="C36" t="str">
         <v>Researching</v>
       </c>
       <c r="D36" t="str">
-        <v>2026 Summer | Microsoft Campus (Thames Valley Park); systems &amp; security-adjacent.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E36" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.gdatasoftware.com</v>
       </c>
       <c r="F36" t="str">
-        <v>Reading, UK</v>
+        <v>Bochum, DE</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1866,33 +1866,33 @@
         <v>Medium</v>
       </c>
       <c r="K36" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L36" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B37" t="str">
-        <v>SAP</v>
+        <v>Avira</v>
       </c>
       <c r="C37" t="str">
         <v>Researching</v>
       </c>
       <c r="D37" t="str">
-        <v>2026 Summer | SAP Frankfurt office (Eschborn); enterprise systems roles.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E37" t="str">
-        <v>https://www.sap.com</v>
+        <v>https://www.avira.com</v>
       </c>
       <c r="F37" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Tettnang, DE</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1907,33 +1907,33 @@
         <v>Medium</v>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L37" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B38" t="str">
-        <v>SAP</v>
+        <v>ESET</v>
       </c>
       <c r="C38" t="str">
         <v>Researching</v>
       </c>
       <c r="D38" t="str">
-        <v>2026 Summer | SAP Berlin office; enterprise systems &amp; security-adjacent roles.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E38" t="str">
-        <v>https://www.sap.com</v>
+        <v>https://www.eset.com</v>
       </c>
       <c r="F38" t="str">
-        <v>Berlin, DE</v>
+        <v>Bratislava, SK</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1948,33 +1948,33 @@
         <v>Medium</v>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L38" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B39" t="str">
-        <v>SAP</v>
+        <v>NCC Group</v>
       </c>
       <c r="C39" t="str">
         <v>Researching</v>
       </c>
       <c r="D39" t="str">
-        <v>2026 Summer | Global HQ; large-scale systems &amp; security-adjacent roles.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E39" t="str">
-        <v>https://www.sap.com</v>
+        <v>https://www.nccgroupplc.com</v>
       </c>
       <c r="F39" t="str">
-        <v>Walldorf, DE</v>
+        <v>Manchester, UK</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -1989,33 +1989,33 @@
         <v>Medium</v>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L39" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B40" t="str">
-        <v>Arm</v>
+        <v>WithSecure</v>
       </c>
       <c r="C40" t="str">
         <v>Researching</v>
       </c>
       <c r="D40" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E40" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.withsecure.com</v>
       </c>
       <c r="F40" t="str">
-        <v>Oslo, NO</v>
+        <v>Helsinki, FI</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2030,33 +2030,33 @@
         <v>Medium</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>Security,Systems</v>
       </c>
       <c r="L40" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B41" t="str">
-        <v>Arm</v>
+        <v>ABB</v>
       </c>
       <c r="C41" t="str">
         <v>Researching</v>
       </c>
       <c r="D41" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E41" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.abb.com</v>
       </c>
       <c r="F41" t="str">
-        <v>Lund, SE</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -2068,36 +2068,36 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L41" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B42" t="str">
-        <v>Arm</v>
+        <v>Rohde &amp; Schwarz</v>
       </c>
       <c r="C42" t="str">
         <v>Researching</v>
       </c>
       <c r="D42" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E42" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.rohde-schwarz.com</v>
       </c>
       <c r="F42" t="str">
-        <v>Galway, IE</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2109,39 +2109,39 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K42" t="str">
-        <v/>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L42" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M42" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B43" t="str">
-        <v>Arm</v>
+        <v>Ericsson</v>
       </c>
       <c r="C43" t="str">
         <v>Researching</v>
       </c>
       <c r="D43" t="str">
-        <v>2026 Summer | Engineering office; embedded focus.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E43" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.ericsson.com</v>
       </c>
       <c r="F43" t="str">
-        <v>Aschheim, DE</v>
+        <v>Stockholm, SE</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2150,36 +2150,36 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L43" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M43" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B44" t="str">
-        <v>Arm</v>
+        <v>Siemens</v>
       </c>
       <c r="C44" t="str">
         <v>Researching</v>
       </c>
       <c r="D44" t="str">
-        <v>2026 Summer | Engineering office; systems + security-adjacent roles.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E44" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.siemens.com</v>
       </c>
       <c r="F44" t="str">
-        <v>Sophia Antipolis, FR</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2191,36 +2191,36 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L44" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M44" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B45" t="str">
-        <v>Arm</v>
+        <v>Bosch</v>
       </c>
       <c r="C45" t="str">
         <v>Researching</v>
       </c>
       <c r="D45" t="str">
-        <v>2026 Summer | Engineering office; firmware/embedded fit.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E45" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.bosch.com</v>
       </c>
       <c r="F45" t="str">
-        <v>Bristol, UK</v>
+        <v>Gerlingen, DE</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2232,36 +2232,36 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L45" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M45" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B46" t="str">
-        <v>Arm</v>
+        <v>Infineon Technologies</v>
       </c>
       <c r="C46" t="str">
         <v>Researching</v>
       </c>
       <c r="D46" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E46" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.infineon.com</v>
       </c>
       <c r="F46" t="str">
-        <v>Manchester, UK</v>
+        <v>Neubiberg, DE</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -2273,39 +2273,39 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="L46" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="M46" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B47" t="str">
-        <v>Arm</v>
+        <v>Microsoft</v>
       </c>
       <c r="C47" t="str">
         <v>Researching</v>
       </c>
       <c r="D47" t="str">
-        <v>2026 Summer | Global HQ; embedded systems &amp; security focus.</v>
+        <v>2026 Summer | Microsoft Switzerland office; systems &amp; security-adjacent.</v>
       </c>
       <c r="E47" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F47" t="str">
-        <v>Cambridge, UK</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -2328,22 +2328,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B48" t="str">
-        <v>NVIDIA</v>
+        <v>Microsoft</v>
       </c>
       <c r="C48" t="str">
         <v>Researching</v>
       </c>
       <c r="D48" t="str">
-        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
+        <v>2026 Summer | Microsoft Sweden office; systems &amp; security-adjacent.</v>
       </c>
       <c r="E48" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F48" t="str">
-        <v>Cambridge, UK</v>
+        <v>Stockholm, SE</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2369,25 +2369,25 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B49" t="str">
-        <v>NVIDIA</v>
+        <v>Microsoft</v>
       </c>
       <c r="C49" t="str">
         <v>Researching</v>
       </c>
       <c r="D49" t="str">
-        <v>2026 Summer | EU office; engineering &amp; security-adjacent roles.</v>
+        <v>2026 Summer | Microsoft Spain office; systems &amp; cloud security-adjacent.</v>
       </c>
       <c r="E49" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F49" t="str">
-        <v>London, UK</v>
+        <v>Madrid, ES</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -2410,22 +2410,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B50" t="str">
-        <v>NVIDIA</v>
+        <v>Microsoft</v>
       </c>
       <c r="C50" t="str">
         <v>Researching</v>
       </c>
       <c r="D50" t="str">
-        <v>2026 Summer | EU office; systems &amp; security fit.</v>
+        <v>2026 Summer | Microsoft Poland office; systems &amp; security-adjacent.</v>
       </c>
       <c r="E50" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F50" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Warsaw, PL</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B51" t="str">
-        <v>NVIDIA</v>
+        <v>Microsoft</v>
       </c>
       <c r="C51" t="str">
         <v>Researching</v>
       </c>
       <c r="D51" t="str">
-        <v>2026 Summer | EU office; systems/embedded adjacent roles.</v>
+        <v>2026 Summer | Microsoft Campus (Thames Valley Park); systems &amp; security-adjacent.</v>
       </c>
       <c r="E51" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F51" t="str">
-        <v>Helsinki, FI</v>
+        <v>Reading, UK</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2492,22 +2492,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B52" t="str">
-        <v>NVIDIA</v>
+        <v>SAP</v>
       </c>
       <c r="C52" t="str">
         <v>Researching</v>
       </c>
       <c r="D52" t="str">
-        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
+        <v>2026 Summer | SAP Frankfurt office (Eschborn); enterprise systems roles.</v>
       </c>
       <c r="E52" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.sap.com</v>
       </c>
       <c r="F52" t="str">
-        <v>Warsaw, PL</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G52">
         <v>2</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B53" t="str">
-        <v>NVIDIA</v>
+        <v>SAP</v>
       </c>
       <c r="C53" t="str">
         <v>Researching</v>
       </c>
       <c r="D53" t="str">
-        <v>2026 Summer | EU office; advanced systems and security-adjacent teams.</v>
+        <v>2026 Summer | SAP Berlin office; enterprise systems &amp; security-adjacent roles.</v>
       </c>
       <c r="E53" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.sap.com</v>
       </c>
       <c r="F53" t="str">
-        <v>Zurich, CH</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2574,22 +2574,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B54" t="str">
-        <v>NVIDIA</v>
+        <v>SAP</v>
       </c>
       <c r="C54" t="str">
         <v>Researching</v>
       </c>
       <c r="D54" t="str">
-        <v>2026 Summer | EU engineering hub; systems + embedded focus fit.</v>
+        <v>2026 Summer | Global HQ; large-scale systems &amp; security-adjacent roles.</v>
       </c>
       <c r="E54" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.sap.com</v>
       </c>
       <c r="F54" t="str">
-        <v>Munich, DE</v>
+        <v>Walldorf, DE</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B55" t="str">
-        <v>NVIDIA</v>
+        <v>Arm</v>
       </c>
       <c r="C55" t="str">
         <v>Researching</v>
       </c>
       <c r="D55" t="str">
-        <v>2026 Summer | EU engineering presence; compute &amp; security-adjacent systems.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E55" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F55" t="str">
-        <v>Berlin, DE</v>
+        <v>Oslo, NO</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -2656,25 +2656,25 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B56" t="str">
-        <v>Netflix</v>
+        <v>Arm</v>
       </c>
       <c r="C56" t="str">
         <v>Researching</v>
       </c>
       <c r="D56" t="str">
-        <v>2026 Summer | Paris office; global teams and compliance/security-adjacent work.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E56" t="str">
-        <v>https://www.netflix.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F56" t="str">
-        <v>Paris, FR</v>
+        <v>Lund, SE</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2697,25 +2697,25 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B57" t="str">
-        <v>Netflix</v>
+        <v>Arm</v>
       </c>
       <c r="C57" t="str">
         <v>Researching</v>
       </c>
       <c r="D57" t="str">
-        <v>2026 Summer | UK office connected to EMEA HQ; cross-functional tech &amp; ops teams.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E57" t="str">
-        <v>https://www.netflix.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F57" t="str">
-        <v>London, UK</v>
+        <v>Galway, IE</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2730,7 +2730,7 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M57" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -2738,22 +2738,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B58" t="str">
-        <v>Netflix</v>
+        <v>Arm</v>
       </c>
       <c r="C58" t="str">
         <v>Researching</v>
       </c>
       <c r="D58" t="str">
-        <v>2026 Summer | EMEA HQ; global teams across content, legal, finance, security-adjacent.</v>
+        <v>2026 Summer | Engineering office; embedded focus.</v>
       </c>
       <c r="E58" t="str">
-        <v>https://www.netflix.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F58" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Aschheim, DE</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2771,7 +2771,7 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M58" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -2779,25 +2779,25 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B59" t="str">
-        <v>Apple</v>
+        <v>Arm</v>
       </c>
       <c r="C59" t="str">
         <v>Researching</v>
       </c>
       <c r="D59" t="str">
-        <v>2026 Summer | Operations &amp; engineering teams in Ireland.</v>
+        <v>2026 Summer | Engineering office; systems + security-adjacent roles.</v>
       </c>
       <c r="E59" t="str">
-        <v>https://www.apple.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F59" t="str">
-        <v>Cork, IE</v>
+        <v>Sophia Antipolis, FR</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -2812,30 +2812,30 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M59" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B60" t="str">
-        <v>Google</v>
+        <v>Arm</v>
       </c>
       <c r="C60" t="str">
         <v>Researching</v>
       </c>
       <c r="D60" t="str">
-        <v>2026 Summer | Major European engineering hub; systems &amp; security fit.</v>
+        <v>2026 Summer | Engineering office; firmware/embedded fit.</v>
       </c>
       <c r="E60" t="str">
-        <v>https://www.google.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F60" t="str">
-        <v>Zurich, CH</v>
+        <v>Bristol, UK</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -2853,30 +2853,30 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M60" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B61" t="str">
-        <v>Meta</v>
+        <v>Arm</v>
       </c>
       <c r="C61" t="str">
         <v>Researching</v>
       </c>
       <c r="D61" t="str">
-        <v>2026 Summer | International HQ in Ireland; security &amp; systems-adjacent roles.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E61" t="str">
-        <v>https://www.meta.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F61" t="str">
-        <v>Dublin, IE</v>
+        <v>Manchester, UK</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -2894,7 +2894,7 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M61" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -2902,25 +2902,25 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B62" t="str">
-        <v>Amazon</v>
+        <v>Arm</v>
       </c>
       <c r="C62" t="str">
         <v>Researching</v>
       </c>
       <c r="D62" t="str">
-        <v>2026 Summer | EU hub (Germany). Initiative application.</v>
+        <v>2026 Summer | Global HQ; embedded systems &amp; security focus.</v>
       </c>
       <c r="E62" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F62" t="str">
-        <v>Berlin, DE</v>
+        <v>Cambridge, UK</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -2935,33 +2935,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M62" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B63" t="str">
-        <v>Amazon</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C63" t="str">
         <v>Researching</v>
       </c>
       <c r="D63" t="str">
-        <v>2026 Summer | EU hub (France). Initiative application.</v>
+        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
       </c>
       <c r="E63" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F63" t="str">
-        <v>Paris, FR</v>
+        <v>Cambridge, UK</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2976,30 +2976,30 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M63" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B64" t="str">
-        <v>Amazon</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C64" t="str">
         <v>Researching</v>
       </c>
       <c r="D64" t="str">
-        <v>2026 Summer | EU tech hub (Germany). Initiative application.</v>
+        <v>2026 Summer | EU office; engineering &amp; security-adjacent roles.</v>
       </c>
       <c r="E64" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F64" t="str">
-        <v>Munich, DE</v>
+        <v>London, UK</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3017,33 +3017,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M64" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B65" t="str">
-        <v>Amazon</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C65" t="str">
         <v>Researching</v>
       </c>
       <c r="D65" t="str">
-        <v>2026 Summer | EU tech &amp; business hub. Initiative application.</v>
+        <v>2026 Summer | EU office; systems &amp; security fit.</v>
       </c>
       <c r="E65" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F65" t="str">
-        <v>London, UK</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -3058,30 +3058,30 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M65" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B66" t="str">
-        <v>Amazon</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C66" t="str">
         <v>Researching</v>
       </c>
       <c r="D66" t="str">
-        <v>2026 Summer | EU HQ in Luxembourg; large-scale systems, security-adjacent teams. Initiative application.</v>
+        <v>2026 Summer | EU office; systems/embedded adjacent roles.</v>
       </c>
       <c r="E66" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F66" t="str">
-        <v>Luxembourg, LU</v>
+        <v>Helsinki, FI</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -3099,7 +3099,7 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M66" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -3107,25 +3107,25 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B67" t="str">
-        <v>HSP Technology Global</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C67" t="str">
         <v>Researching</v>
       </c>
       <c r="D67" t="str">
-        <v>2026 Summer | Engineering &amp; tech; Antalya Technokent address.</v>
+        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
       </c>
       <c r="E67" t="str">
-        <v>https://www.hsptechglobal.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F67" t="str">
-        <v>Antalya, TR</v>
+        <v>Warsaw, PL</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -3140,33 +3140,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M67" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B68" t="str">
-        <v>Savhatek Defence Industries</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C68" t="str">
         <v>Researching</v>
       </c>
       <c r="D68" t="str">
-        <v>2026 Summer | Defense &amp; embedded systems; Antalya Technokent HQ.</v>
+        <v>2026 Summer | EU office; advanced systems and security-adjacent teams.</v>
       </c>
       <c r="E68" t="str">
-        <v>https://savhatek.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F68" t="str">
-        <v>Antalya, TR</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -3181,33 +3181,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M68" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B69" t="str">
-        <v>SANTSG</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C69" t="str">
         <v>Researching</v>
       </c>
       <c r="D69" t="str">
-        <v>2026 Summer | Head office in Antalya Technokent; engineering &amp; R&amp;D.</v>
+        <v>2026 Summer | EU engineering hub; systems + embedded focus fit.</v>
       </c>
       <c r="E69" t="str">
-        <v>https://www.santsg.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F69" t="str">
-        <v>Antalya, TR</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -3222,33 +3222,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M69" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B70" t="str">
-        <v>CRS CAM</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C70" t="str">
         <v>Researching</v>
       </c>
       <c r="D70" t="str">
-        <v>2026 Summer | Camera/vision hardware; R&amp;D office in Antalya Technokent.</v>
+        <v>2026 Summer | EU engineering presence; compute &amp; security-adjacent systems.</v>
       </c>
       <c r="E70" t="str">
-        <v>https://www.crscam.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F70" t="str">
-        <v>Antalya, TR</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -3263,30 +3263,30 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M70" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B71" t="str">
-        <v>Evant Teknoloji A.S.</v>
+        <v>Netflix</v>
       </c>
       <c r="C71" t="str">
         <v>Researching</v>
       </c>
       <c r="D71" t="str">
-        <v>2026 Summer | System integrator with Antalya branch; security partnerships.</v>
+        <v>2026 Summer | Paris office; global teams and compliance/security-adjacent work.</v>
       </c>
       <c r="E71" t="str">
-        <v>https://evant.com.tr/en</v>
+        <v>https://www.netflix.com</v>
       </c>
       <c r="F71" t="str">
-        <v>Antalya, TR</v>
+        <v>Paris, FR</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3304,33 +3304,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="M71" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B72" t="str">
-        <v>EPAM Systems Türkiye</v>
+        <v>Netflix</v>
       </c>
       <c r="C72" t="str">
         <v>Researching</v>
       </c>
       <c r="D72" t="str">
-        <v>2026 Summer | Global engineering firm; Antalya OSB Technopark R&amp;D presence.</v>
+        <v>2026 Summer | UK office connected to EMEA HQ; cross-functional tech &amp; ops teams.</v>
       </c>
       <c r="E72" t="str">
-        <v>https://www.epam.com</v>
+        <v>https://www.netflix.com</v>
       </c>
       <c r="F72" t="str">
-        <v>Antalya, TR</v>
+        <v>London, UK</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -3345,33 +3345,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M72" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B73" t="str">
-        <v>STM Savunma Teknolojileri</v>
+        <v>Netflix</v>
       </c>
       <c r="C73" t="str">
         <v>Researching</v>
       </c>
       <c r="D73" t="str">
-        <v>2026 Summer | Cybersecurity, command-control ve embedded sistemler.</v>
+        <v>2026 Summer | EMEA HQ; global teams across content, legal, finance, security-adjacent.</v>
       </c>
       <c r="E73" t="str">
-        <v>https://www.stm.com.tr</v>
+        <v>https://www.netflix.com</v>
       </c>
       <c r="F73" t="str">
-        <v>Turkey, TR</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -3386,33 +3386,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M73" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B74" t="str">
-        <v>Turkish Aerospace (TUSAŞ)</v>
+        <v>Apple</v>
       </c>
       <c r="C74" t="str">
         <v>Researching</v>
       </c>
       <c r="D74" t="str">
-        <v>2026 Summer | Aerospace + embedded systems, secure systems ve avionics odakli ekipler.</v>
+        <v>2026 Summer | Operations &amp; engineering teams in Ireland.</v>
       </c>
       <c r="E74" t="str">
-        <v>https://www.tusas.com</v>
+        <v>https://www.apple.com</v>
       </c>
       <c r="F74" t="str">
-        <v>Turkey, TR</v>
+        <v>Cork, IE</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -3427,33 +3427,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M74" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B75" t="str">
-        <v>TOPIC Embedded Systems</v>
+        <v>Google</v>
       </c>
       <c r="C75" t="str">
         <v>Researching</v>
       </c>
       <c r="D75" t="str">
-        <v>2026 Summer | Embedded systems consultancy; firmware ve low-level sistemler.</v>
+        <v>2026 Summer | Major European engineering hub; systems &amp; security fit.</v>
       </c>
       <c r="E75" t="str">
-        <v>https://www.topic.nl</v>
+        <v>https://www.google.com</v>
       </c>
       <c r="F75" t="str">
-        <v>Eindhoven, NL</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -3468,33 +3468,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M75" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B76" t="str">
-        <v>TomTom</v>
+        <v>Meta</v>
       </c>
       <c r="C76" t="str">
         <v>Researching</v>
       </c>
       <c r="D76" t="str">
-        <v>2026 Summer | Automotive navigation &amp; location tech; embedded/vehicle systems odakli ekipler.</v>
+        <v>2026 Summer | International HQ in Ireland; security &amp; systems-adjacent roles.</v>
       </c>
       <c r="E76" t="str">
-        <v>https://www.tomtom.com</v>
+        <v>https://www.meta.com</v>
       </c>
       <c r="F76" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Dublin, IE</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -3509,30 +3509,30 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B77" t="str">
-        <v>Eye Security</v>
+        <v>Amazon</v>
       </c>
       <c r="C77" t="str">
         <v>Researching</v>
       </c>
       <c r="D77" t="str">
-        <v>2026 Summer | Managed detection &amp; response; security operations mindset odakli ekipler.</v>
+        <v>2026 Summer | EU hub (Germany). Initiative application.</v>
       </c>
       <c r="E77" t="str">
-        <v>https://www.eye.security</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F77" t="str">
-        <v>The Hague, NL</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3550,30 +3550,30 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B78" t="str">
-        <v>Fox-IT</v>
+        <v>Amazon</v>
       </c>
       <c r="C78" t="str">
         <v>Researching</v>
       </c>
       <c r="D78" t="str">
-        <v>2026 Summer | Blue-team &amp; incident-response kültürü; security engineering odakli ekipler.</v>
+        <v>2026 Summer | EU hub (France). Initiative application.</v>
       </c>
       <c r="E78" t="str">
-        <v>https://www.fox-it.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F78" t="str">
-        <v>Delft, NL</v>
+        <v>Paris, FR</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3591,33 +3591,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B79" t="str">
-        <v>ASM International</v>
+        <v>Amazon</v>
       </c>
       <c r="C79" t="str">
         <v>Researching</v>
       </c>
       <c r="D79" t="str">
-        <v>2026 Summer | Semiconductor manufacturing equipment; systems/embedded odakli ekipler.</v>
+        <v>2026 Summer | EU tech hub (Germany). Initiative application.</v>
       </c>
       <c r="E79" t="str">
-        <v>https://www.asm.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F79" t="str">
-        <v>Almere, NL</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3632,30 +3632,30 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B80" t="str">
-        <v>Nexperia</v>
+        <v>Amazon</v>
       </c>
       <c r="C80" t="str">
         <v>Researching</v>
       </c>
       <c r="D80" t="str">
-        <v>2026 Summer | Semiconductor; embedded güvenlik ve donanim-odakli ekipler.</v>
+        <v>2026 Summer | EU tech &amp; business hub. Initiative application.</v>
       </c>
       <c r="E80" t="str">
-        <v>https://www.nexperia.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F80" t="str">
-        <v>Nijmegen, NL</v>
+        <v>London, UK</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3673,33 +3673,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B81" t="str">
-        <v>Thales Nederland</v>
+        <v>Amazon</v>
       </c>
       <c r="C81" t="str">
         <v>Researching</v>
       </c>
       <c r="D81" t="str">
-        <v>2026 Summer | Defense &amp; cybersecurity; secure systems ve embedded güvenlik odakli ekipler.</v>
+        <v>2026 Summer | EU HQ in Luxembourg; large-scale systems, security-adjacent teams. Initiative application.</v>
       </c>
       <c r="E81" t="str">
-        <v>https://www.thalesgroup.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F81" t="str">
-        <v>Hengelo, NL</v>
+        <v>Luxembourg, LU</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -3714,30 +3714,30 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="B82" t="str">
-        <v>Philips</v>
+        <v>HSP Technology Global</v>
       </c>
       <c r="C82" t="str">
         <v>Researching</v>
       </c>
       <c r="D82" t="str">
-        <v>2026 Summer | Medical/health-tech sistemler; embedded + güvenlik odakli ekipler.</v>
+        <v>2026 Summer | Engineering &amp; tech; Antalya Technokent address.</v>
       </c>
       <c r="E82" t="str">
-        <v>https://www.philips.com</v>
+        <v>https://www.hsptechglobal.com</v>
       </c>
       <c r="F82" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3755,30 +3755,30 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="B83" t="str">
-        <v>ASML</v>
+        <v>Savhatek Defence Industries</v>
       </c>
       <c r="C83" t="str">
         <v>Researching</v>
       </c>
       <c r="D83" t="str">
-        <v>2026 Summer | Semiconductor tooling; embedded + systems security odakli ekipler. Initiative application.</v>
+        <v>2026 Summer | Defense &amp; embedded systems; Antalya Technokent HQ.</v>
       </c>
       <c r="E83" t="str">
-        <v>https://www.asml.com</v>
+        <v>https://savhatek.com</v>
       </c>
       <c r="F83" t="str">
-        <v>Veldhoven, NL</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -3796,33 +3796,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B84" t="str">
-        <v>Rheinmetall</v>
+        <v>SANTSG</v>
       </c>
       <c r="C84" t="str">
         <v>Researching</v>
       </c>
       <c r="D84" t="str">
-        <v>2026 Summer | Guvenlik ve savunma teknolojileri, embedded/secure systems.</v>
+        <v>2026 Summer | Head office in Antalya Technokent; engineering &amp; R&amp;D.</v>
       </c>
       <c r="E84" t="str">
-        <v>https://www.rheinmetall.com</v>
+        <v>https://www.santsg.com</v>
       </c>
       <c r="F84" t="str">
-        <v>Dusseldorf, DE</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -3837,30 +3837,30 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B85" t="str">
-        <v>Henkel</v>
+        <v>CRS CAM</v>
       </c>
       <c r="C85" t="str">
         <v>Researching</v>
       </c>
       <c r="D85" t="str">
-        <v>2026 Summer | Endustriyel IT/OT ve guvenlik odakli ekipler.</v>
+        <v>2026 Summer | Camera/vision hardware; R&amp;D office in Antalya Technokent.</v>
       </c>
       <c r="E85" t="str">
-        <v>https://www.henkel.com</v>
+        <v>https://www.crscam.com</v>
       </c>
       <c r="F85" t="str">
-        <v>Dusseldorf, DE</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3878,30 +3878,30 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B86" t="str">
-        <v>DZ BANK</v>
+        <v>Evant Teknoloji A.S.</v>
       </c>
       <c r="C86" t="str">
         <v>Researching</v>
       </c>
       <c r="D86" t="str">
-        <v>2026 Summer | Finansal altyapi ve bilgi guvenligi odakli ekipler.</v>
+        <v>2026 Summer | System integrator with Antalya branch; security partnerships.</v>
       </c>
       <c r="E86" t="str">
-        <v>https://www.dzbank.com</v>
+        <v>https://evant.com.tr/en</v>
       </c>
       <c r="F86" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3919,33 +3919,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="B87" t="str">
-        <v>Deutsche Boerse Group</v>
+        <v>EPAM Systems Türkiye</v>
       </c>
       <c r="C87" t="str">
         <v>Researching</v>
       </c>
       <c r="D87" t="str">
-        <v>2026 Summer | Piyasa altyapisi, cyber protection ve sistem guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Global engineering firm; Antalya OSB Technopark R&amp;D presence.</v>
       </c>
       <c r="E87" t="str">
-        <v>https://www.deutsche-boerse.com</v>
+        <v>https://www.epam.com</v>
       </c>
       <c r="F87" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -3960,33 +3960,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B88" t="str">
-        <v>DekaBank</v>
+        <v>STM Savunma Teknolojileri</v>
       </c>
       <c r="C88" t="str">
         <v>Researching</v>
       </c>
       <c r="D88" t="str">
-        <v>2026 Summer | Finans ve altyapi guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Cybersecurity, command-control ve embedded sistemler.</v>
       </c>
       <c r="E88" t="str">
-        <v>https://www.deka.de</v>
+        <v>https://www.stm.com.tr</v>
       </c>
       <c r="F88" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -4001,33 +4001,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B89" t="str">
-        <v>Commerzbank</v>
+        <v>Turkish Aerospace (TUSAŞ)</v>
       </c>
       <c r="C89" t="str">
         <v>Researching</v>
       </c>
       <c r="D89" t="str">
-        <v>2026 Summer | Finansal sistemler ve bilgi guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Aerospace + embedded systems, secure systems ve avionics odakli ekipler.</v>
       </c>
       <c r="E89" t="str">
-        <v>https://www.commerzbank.de</v>
+        <v>https://www.tusas.com</v>
       </c>
       <c r="F89" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -4042,33 +4042,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B90" t="str">
-        <v>Deutsche Bank</v>
+        <v>TOPIC Embedded Systems</v>
       </c>
       <c r="C90" t="str">
         <v>Researching</v>
       </c>
       <c r="D90" t="str">
-        <v>2026 Summer | Banka altyapisi ve siber guvenlik odakli ekipler.</v>
+        <v>2026 Summer | Embedded systems consultancy; firmware ve low-level sistemler.</v>
       </c>
       <c r="E90" t="str">
-        <v>https://www.db.com</v>
+        <v>https://www.topic.nl</v>
       </c>
       <c r="F90" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Eindhoven, NL</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -4083,30 +4083,30 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B91" t="str">
-        <v>Giesecke+Devrient</v>
+        <v>TomTom</v>
       </c>
       <c r="C91" t="str">
         <v>Researching</v>
       </c>
       <c r="D91" t="str">
-        <v>2026 Summer | SecurityTech, kimlik ve secure hardware/embedded alanlari.</v>
+        <v>2026 Summer | Automotive navigation &amp; location tech; embedded/vehicle systems odakli ekipler.</v>
       </c>
       <c r="E91" t="str">
-        <v>https://www.gi-de.com</v>
+        <v>https://www.tomtom.com</v>
       </c>
       <c r="F91" t="str">
-        <v>Bayern, DE</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G91">
         <v>3</v>
@@ -4124,30 +4124,30 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B92" t="str">
-        <v>BMW Group</v>
+        <v>Eye Security</v>
       </c>
       <c r="C92" t="str">
         <v>Researching</v>
       </c>
       <c r="D92" t="str">
-        <v>2026 Summer | Otomotiv embedded, sistem guvenligi ve yazilim ekipleri.</v>
+        <v>2026 Summer | Managed detection &amp; response; security operations mindset odakli ekipler.</v>
       </c>
       <c r="E92" t="str">
-        <v>https://www.bmwgroup.com</v>
+        <v>https://www.eye.security</v>
       </c>
       <c r="F92" t="str">
-        <v>Bayern, DE</v>
+        <v>The Hague, NL</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -4165,33 +4165,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B93" t="str">
-        <v>Siemens AG</v>
+        <v>Fox-IT</v>
       </c>
       <c r="C93" t="str">
         <v>Researching</v>
       </c>
       <c r="D93" t="str">
-        <v>2026 Summer | Endustriyel sistemler, OT/ICS guvenligi ve embedded odakli ekipler.</v>
+        <v>2026 Summer | Blue-team &amp; incident-response kültürü; security engineering odakli ekipler.</v>
       </c>
       <c r="E93" t="str">
-        <v>https://www.siemens.com</v>
+        <v>https://www.fox-it.com</v>
       </c>
       <c r="F93" t="str">
-        <v>Bayern, DE</v>
+        <v>Delft, NL</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -4206,30 +4206,30 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B94" t="str">
-        <v>Mercedes-Benz Group AG</v>
+        <v>ASM International</v>
       </c>
       <c r="C94" t="str">
         <v>Researching</v>
       </c>
       <c r="D94" t="str">
-        <v>2026 Summer | Otomotiv embedded/vehicle security odakli ekipler. Initiative application.</v>
+        <v>2026 Summer | Semiconductor manufacturing equipment; systems/embedded odakli ekipler.</v>
       </c>
       <c r="E94" t="str">
-        <v>https://group.mercedes-benz.com</v>
+        <v>https://www.asm.com</v>
       </c>
       <c r="F94" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Almere, NL</v>
       </c>
       <c r="G94">
         <v>2</v>
@@ -4247,33 +4247,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B95" t="str">
-        <v>ubisys technologies</v>
+        <v>Nexperia</v>
       </c>
       <c r="C95" t="str">
         <v>Researching</v>
       </c>
       <c r="D95" t="str">
-        <v>2026 Summer | IoT/embedded systems (Zigbee smart home).</v>
+        <v>2026 Summer | Semiconductor; embedded güvenlik ve donanim-odakli ekipler.</v>
       </c>
       <c r="E95" t="str">
-        <v>https://www.ubisys.de</v>
+        <v>https://www.nexperia.com</v>
       </c>
       <c r="F95" t="str">
-        <v>Düsseldorf, DE</v>
+        <v>Nijmegen, NL</v>
       </c>
       <c r="G95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -4288,33 +4288,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B96" t="str">
-        <v>Vodafone GmbH</v>
+        <v>Thales Nederland</v>
       </c>
       <c r="C96" t="str">
         <v>Researching</v>
       </c>
       <c r="D96" t="str">
-        <v>2026 Summer | Telecom network security ve sistem guvenligi ekipleri.</v>
+        <v>2026 Summer | Defense &amp; cybersecurity; secure systems ve embedded güvenlik odakli ekipler.</v>
       </c>
       <c r="E96" t="str">
-        <v>https://www.vodafone.de</v>
+        <v>https://www.thalesgroup.com</v>
       </c>
       <c r="F96" t="str">
-        <v>Dusseldorf, DE</v>
+        <v>Hengelo, NL</v>
       </c>
       <c r="G96">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -4329,33 +4329,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="B97" t="str">
-        <v>Deutsche Börse Group</v>
+        <v>Philips</v>
       </c>
       <c r="C97" t="str">
         <v>Researching</v>
       </c>
       <c r="D97" t="str">
-        <v>2026 Summer | Large-scale systems; security &amp; reliability-focused roles.</v>
+        <v>2026 Summer | Medical/health-tech sistemler; embedded + güvenlik odakli ekipler.</v>
       </c>
       <c r="E97" t="str">
-        <v>https://www.deutsche-boerse.com</v>
+        <v>https://www.philips.com</v>
       </c>
       <c r="F97" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -4370,33 +4370,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B98" t="str">
-        <v>Adva Network Security</v>
+        <v>ASML</v>
       </c>
       <c r="C98" t="str">
         <v>Researching</v>
       </c>
       <c r="D98" t="str">
-        <v>2026 Summer | Network security, encryption ve kritik altyapi guvenligi.</v>
+        <v>2026 Summer | Semiconductor tooling; embedded + systems security odakli ekipler. Initiative application.</v>
       </c>
       <c r="E98" t="str">
-        <v>https://www.advasecurity.com</v>
+        <v>https://www.asml.com</v>
       </c>
       <c r="F98" t="str">
-        <v>Berlin, DE</v>
+        <v>Veldhoven, NL</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -4411,33 +4411,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B99" t="str">
-        <v>WebID Solutions</v>
+        <v>Rheinmetall</v>
       </c>
       <c r="C99" t="str">
         <v>Researching</v>
       </c>
       <c r="D99" t="str">
-        <v>2026 Summer | Kimlik dogrulama ve guvenlik odakli sistemler.</v>
+        <v>2026 Summer | Guvenlik ve savunma teknolojileri, embedded/secure systems.</v>
       </c>
       <c r="E99" t="str">
-        <v>https://webid-solutions.com</v>
+        <v>https://www.rheinmetall.com</v>
       </c>
       <c r="F99" t="str">
-        <v>Berlin, DE</v>
+        <v>Dusseldorf, DE</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M99" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4460,25 +4460,25 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B100" t="str">
-        <v>Rohde &amp; Schwarz</v>
+        <v>Henkel</v>
       </c>
       <c r="C100" t="str">
         <v>Researching</v>
       </c>
       <c r="D100" t="str">
-        <v>2026 Summer | Guvenli haberlesme, test/measurement, cybersecurity ekipleri.</v>
+        <v>2026 Summer | Endustriyel IT/OT ve guvenlik odakli ekipler.</v>
       </c>
       <c r="E100" t="str">
-        <v>https://www.rohde-schwarz.com</v>
+        <v>https://www.henkel.com</v>
       </c>
       <c r="F100" t="str">
-        <v>Bayern, DE</v>
+        <v>Dusseldorf, DE</v>
       </c>
       <c r="G100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" t="str">
         <v/>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M100" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4501,25 +4501,25 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B101" t="str">
-        <v>NXP Semiconductors</v>
+        <v>DZ BANK</v>
       </c>
       <c r="C101" t="str">
         <v>Researching</v>
       </c>
       <c r="D101" t="str">
-        <v>2026 Summer | Embedded security, hardware-backed systems, SoC ve firmware odakli ekipler.</v>
+        <v>2026 Summer | Finansal altyapi ve bilgi guvenligi odakli ekipler.</v>
       </c>
       <c r="E101" t="str">
-        <v>https://www.nxp.com</v>
+        <v>https://www.dzbank.com</v>
       </c>
       <c r="F101" t="str">
-        <v>Eindhoven, NL</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H101" t="str">
         <v/>
@@ -4534,33 +4534,33 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B102" t="str">
-        <v>Infineon Technologies</v>
+        <v>Deutsche Boerse Group</v>
       </c>
       <c r="C102" t="str">
         <v>Researching</v>
       </c>
       <c r="D102" t="str">
-        <v>2026 Summer | Semiconductor, embedded security ve hardware-backed systems.</v>
+        <v>2026 Summer | Piyasa altyapisi, cyber protection ve sistem guvenligi odakli ekipler.</v>
       </c>
       <c r="E102" t="str">
-        <v>https://www.infineon.com</v>
+        <v>https://www.deutsche-boerse.com</v>
       </c>
       <c r="F102" t="str">
-        <v>Bayern, DE</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H102" t="str">
         <v/>
@@ -4575,7 +4575,7 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M102" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4583,25 +4583,25 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B103" t="str">
-        <v>Porsche AG</v>
+        <v>DekaBank</v>
       </c>
       <c r="C103" t="str">
         <v>Researching</v>
       </c>
       <c r="D103" t="str">
-        <v>2026 Summer | Embedded systems, firmware ve otomotiv guvenligi odakli roller. Initiative application.</v>
+        <v>2026 Summer | Finans ve altyapi guvenligi odakli ekipler.</v>
       </c>
       <c r="E103" t="str">
-        <v>https://www.porsche.com</v>
+        <v>https://www.deka.de</v>
       </c>
       <c r="F103" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H103" t="str">
         <v/>
@@ -4616,7 +4616,7 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M103" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4624,22 +4624,22 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B104" t="str">
-        <v>Bosch Rexroth</v>
+        <v>Commerzbank</v>
       </c>
       <c r="C104" t="str">
         <v>Researching</v>
       </c>
       <c r="D104" t="str">
-        <v>2026 Summer | Endustriyel otomasyon, kontrol sistemleri ve embedded guvenlik.</v>
+        <v>2026 Summer | Finansal sistemler ve bilgi guvenligi odakli ekipler.</v>
       </c>
       <c r="E104" t="str">
-        <v>https://www.boschrexroth.com</v>
+        <v>https://www.commerzbank.de</v>
       </c>
       <c r="F104" t="str">
-        <v>Bayern, DE</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -4657,7 +4657,7 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M104" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B105" t="str">
-        <v>Vector Informatik</v>
+        <v>Deutsche Bank</v>
       </c>
       <c r="C105" t="str">
         <v>Researching</v>
       </c>
       <c r="D105" t="str">
-        <v>2026 Summer | Embedded software tooling, ECU ve sistem guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Banka altyapisi ve siber guvenlik odakli ekipler.</v>
       </c>
       <c r="E105" t="str">
-        <v>https://www.vector.com</v>
+        <v>https://www.db.com</v>
       </c>
       <c r="F105" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -4698,7 +4698,7 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M105" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4706,22 +4706,22 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B106" t="str">
-        <v>ETAS GmbH</v>
+        <v>Giesecke+Devrient</v>
       </c>
       <c r="C106" t="str">
         <v>Researching</v>
       </c>
       <c r="D106" t="str">
-        <v>2026 Summer | Embedded tooling, ECU ve embedded security odakli ekipler.</v>
+        <v>2026 Summer | SecurityTech, kimlik ve secure hardware/embedded alanlari.</v>
       </c>
       <c r="E106" t="str">
-        <v>https://www.etas.com</v>
+        <v>https://www.gi-de.com</v>
       </c>
       <c r="F106" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -4739,7 +4739,7 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M106" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4747,25 +4747,25 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B107" t="str">
-        <v>Robert Bosch GmbH</v>
+        <v>BMW Group</v>
       </c>
       <c r="C107" t="str">
         <v>Researching</v>
       </c>
       <c r="D107" t="str">
-        <v>2026 Summer | Embedded systems + security odakli ekipler. Initiative application.</v>
+        <v>2026 Summer | Otomotiv embedded, sistem guvenligi ve yazilim ekipleri.</v>
       </c>
       <c r="E107" t="str">
-        <v>https://www.bosch.com</v>
+        <v>https://www.bmwgroup.com</v>
       </c>
       <c r="F107" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H107" t="str">
         <v/>
@@ -4780,7 +4780,7 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M107" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -4788,25 +4788,25 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B108" t="str">
-        <v>VTT Teknik Arastirma Merkezi</v>
+        <v>Siemens AG</v>
       </c>
       <c r="C108" t="str">
         <v>Researching</v>
       </c>
       <c r="D108" t="str">
-        <v/>
+        <v>2026 Summer | Endustriyel sistemler, OT/ICS guvenligi ve embedded odakli ekipler.</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>https://www.siemens.com</v>
       </c>
       <c r="F108" t="str">
-        <v/>
+        <v>Bayern, DE</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" t="str">
         <v/>
@@ -4821,33 +4821,33 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B109" t="str">
-        <v>Nordic Semiconductor</v>
+        <v>Mercedes-Benz Group AG</v>
       </c>
       <c r="C109" t="str">
         <v>Researching</v>
       </c>
       <c r="D109" t="str">
-        <v/>
+        <v>2026 Summer | Otomotiv embedded/vehicle security odakli ekipler. Initiative application.</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>https://group.mercedes-benz.com</v>
       </c>
       <c r="F109" t="str">
-        <v/>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" t="str">
         <v/>
@@ -4862,33 +4862,33 @@
         <v/>
       </c>
       <c r="L109" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B110" t="str">
-        <v>SINTEF</v>
+        <v>ubisys technologies</v>
       </c>
       <c r="C110" t="str">
         <v>Researching</v>
       </c>
       <c r="D110" t="str">
-        <v/>
+        <v>2026 Summer | IoT/embedded systems (Zigbee smart home).</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>https://www.ubisys.de</v>
       </c>
       <c r="F110" t="str">
-        <v/>
+        <v>Düsseldorf, DE</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H110" t="str">
         <v/>
@@ -4903,33 +4903,33 @@
         <v/>
       </c>
       <c r="L110" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B111" t="str">
-        <v>RISE Araştirma Enstitileri</v>
+        <v>Vodafone GmbH</v>
       </c>
       <c r="C111" t="str">
         <v>Researching</v>
       </c>
       <c r="D111" t="str">
-        <v/>
+        <v>2026 Summer | Telecom network security ve sistem guvenligi ekipleri.</v>
       </c>
       <c r="E111" t="str">
-        <v/>
+        <v>https://www.vodafone.de</v>
       </c>
       <c r="F111" t="str">
-        <v/>
+        <v>Dusseldorf, DE</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" t="str">
         <v/>
@@ -4944,33 +4944,33 @@
         <v/>
       </c>
       <c r="L111" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B112" t="str">
-        <v>Prodrive Technologies</v>
+        <v>Deutsche Börse Group</v>
       </c>
       <c r="C112" t="str">
         <v>Researching</v>
       </c>
       <c r="D112" t="str">
-        <v/>
+        <v>2026 Summer | Large-scale systems; security &amp; reliability-focused roles.</v>
       </c>
       <c r="E112" t="str">
-        <v/>
+        <v>https://www.deutsche-boerse.com</v>
       </c>
       <c r="F112" t="str">
-        <v/>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112" t="str">
         <v/>
@@ -4985,30 +4985,30 @@
         <v/>
       </c>
       <c r="L112" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>Holst Centre</v>
+        <v>Adva Network Security</v>
       </c>
       <c r="C113" t="str">
         <v>Researching</v>
       </c>
       <c r="D113" t="str">
-        <v/>
+        <v>2026 Summer | Network security, encryption ve kritik altyapi guvenligi.</v>
       </c>
       <c r="E113" t="str">
-        <v/>
+        <v>https://www.advasecurity.com</v>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>Berlin, DE</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -5026,33 +5026,33 @@
         <v/>
       </c>
       <c r="L113" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B114" t="str">
-        <v>TNO Embedded Systems Innovation (ESI)</v>
+        <v>WebID Solutions</v>
       </c>
       <c r="C114" t="str">
         <v>Researching</v>
       </c>
       <c r="D114" t="str">
-        <v/>
+        <v>2026 Summer | Kimlik dogrulama ve guvenlik odakli sistemler.</v>
       </c>
       <c r="E114" t="str">
-        <v/>
+        <v>https://webid-solutions.com</v>
       </c>
       <c r="F114" t="str">
-        <v/>
+        <v>Berlin, DE</v>
       </c>
       <c r="G114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" t="str">
         <v/>
@@ -5067,33 +5067,33 @@
         <v/>
       </c>
       <c r="L114" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B115" t="str">
-        <v>Roke Manor Research</v>
+        <v>Rohde &amp; Schwarz</v>
       </c>
       <c r="C115" t="str">
         <v>Researching</v>
       </c>
       <c r="D115" t="str">
-        <v>Videantis Hannover merkezli derin öğrenme, bilgisayarla görme ve video işleme çözümleri sağlayan bir şirkettir.</v>
+        <v>2026 Summer | Guvenli haberlesme, test/measurement, cybersecurity ekipleri.</v>
       </c>
       <c r="E115" t="str">
-        <v>https://www.videantis.com</v>
+        <v>https://www.rohde-schwarz.com</v>
       </c>
       <c r="F115" t="str">
-        <v>Hannover, DE</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" t="str">
         <v/>
@@ -5108,7 +5108,7 @@
         <v/>
       </c>
       <c r="L115" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M115" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5116,25 +5116,25 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B116" t="str">
-        <v>Cambridge Consultants</v>
+        <v>NXP Semiconductors</v>
       </c>
       <c r="C116" t="str">
         <v>Researching</v>
       </c>
       <c r="D116" t="str">
-        <v/>
+        <v>2026 Summer | Embedded security, hardware-backed systems, SoC ve firmware odakli ekipler.</v>
       </c>
       <c r="E116" t="str">
-        <v/>
+        <v>https://www.nxp.com</v>
       </c>
       <c r="F116" t="str">
-        <v/>
+        <v>Eindhoven, NL</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H116" t="str">
         <v/>
@@ -5149,33 +5149,33 @@
         <v/>
       </c>
       <c r="L116" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B117" t="str">
-        <v>Videantis</v>
+        <v>Infineon Technologies</v>
       </c>
       <c r="C117" t="str">
         <v>Researching</v>
       </c>
       <c r="D117" t="str">
-        <v/>
+        <v>2026 Summer | Semiconductor, embedded security ve hardware-backed systems.</v>
       </c>
       <c r="E117" t="str">
-        <v/>
+        <v>https://www.infineon.com</v>
       </c>
       <c r="F117" t="str">
-        <v/>
+        <v>Bayern, DE</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H117" t="str">
         <v/>
@@ -5190,33 +5190,33 @@
         <v/>
       </c>
       <c r="L117" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B118" t="str">
-        <v>FZI</v>
+        <v>Porsche AG</v>
       </c>
       <c r="C118" t="str">
         <v>Researching</v>
       </c>
       <c r="D118" t="str">
-        <v/>
+        <v>2026 Summer | Embedded systems, firmware ve otomotiv guvenligi odakli roller. Initiative application.</v>
       </c>
       <c r="E118" t="str">
-        <v/>
+        <v>https://www.porsche.com</v>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H118" t="str">
         <v/>
@@ -5231,30 +5231,30 @@
         <v/>
       </c>
       <c r="L118" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B119" t="str">
-        <v>DLR Robotik &amp; Mekatronik Enstitüsü</v>
+        <v>Bosch Rexroth</v>
       </c>
       <c r="C119" t="str">
         <v>Researching</v>
       </c>
       <c r="D119" t="str">
-        <v/>
+        <v>2026 Summer | Endustriyel otomasyon, kontrol sistemleri ve embedded guvenlik.</v>
       </c>
       <c r="E119" t="str">
-        <v/>
+        <v>https://www.boschrexroth.com</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>Bayern, DE</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -5272,30 +5272,30 @@
         <v/>
       </c>
       <c r="L119" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B120" t="str">
-        <v>Sematicon AG</v>
+        <v>Vector Informatik</v>
       </c>
       <c r="C120" t="str">
-        <v>Applied</v>
+        <v>Researching</v>
       </c>
       <c r="D120" t="str">
-        <v>Akıllı sensörler; elektronik ve mekanik sistem entegrasyonu; endüstriyel gömülü çözümler</v>
+        <v>2026 Summer | Embedded software tooling, ECU ve sistem guvenligi odakli ekipler.</v>
       </c>
       <c r="E120" t="str">
-        <v>https://www.lbf.fraunhofer.de</v>
+        <v>https://www.vector.com</v>
       </c>
       <c r="F120" t="str">
-        <v>Darmstadt</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -5313,33 +5313,33 @@
         <v/>
       </c>
       <c r="L120" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-04 15:44:52</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B121" t="str">
-        <v>VDE Prüf- und Zertifizierungsinstitut</v>
+        <v>ETAS GmbH</v>
       </c>
       <c r="C121" t="str">
         <v>Researching</v>
       </c>
       <c r="D121" t="str">
-        <v>Elektronik ve gömülü sistem testleri; güvenlik, EMC ve donanım doğrulaması; sertifikasyon öncesi teknik analiz</v>
+        <v>2026 Summer | Embedded tooling, ECU ve embedded security odakli ekipler.</v>
       </c>
       <c r="E121" t="str">
-        <v>https://www.vde.com</v>
+        <v>https://www.etas.com</v>
       </c>
       <c r="F121" t="str">
-        <v>Offenbach</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H121" t="str">
         <v/>
@@ -5354,33 +5354,33 @@
         <v/>
       </c>
       <c r="L121" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B122" t="str">
-        <v>ESCRYPT</v>
+        <v>Robert Bosch GmbH</v>
       </c>
       <c r="C122" t="str">
         <v>Researching</v>
       </c>
       <c r="D122" t="str">
-        <v>Otomotiv siber güvenliği; ECU, firmware ve gömülü güvenlik; güvenli yaşam döngüsü ve tehdit modelleme</v>
+        <v>2026 Summer | Embedded systems + security odakli ekipler. Initiative application.</v>
       </c>
       <c r="E122" t="str">
-        <v>https://www.escrypt.com</v>
+        <v>https://www.bosch.com</v>
       </c>
       <c r="F122" t="str">
-        <v>Frankfurt</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H122" t="str">
         <v/>
@@ -5395,30 +5395,30 @@
         <v/>
       </c>
       <c r="L122" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B123" t="str">
-        <v>ATHENE</v>
+        <v>VTT Teknik Arastirma Merkezi</v>
       </c>
       <c r="C123" t="str">
         <v>Researching</v>
       </c>
       <c r="D123" t="str">
-        <v>Donanım destekli güvenlik; gömülü ve siber-fiziksel sistem güvenliği; endüstriyel ve kritik altyapı güvenliği</v>
+        <v/>
       </c>
       <c r="E123" t="str">
-        <v>https://www.athene-center.de</v>
+        <v/>
       </c>
       <c r="F123" t="str">
-        <v>Darmstadt</v>
+        <v/>
       </c>
       <c r="G123">
         <v>1</v>
@@ -5444,22 +5444,22 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B124" t="str">
-        <v>Fraunhofer IGD</v>
+        <v>Nordic Semiconductor</v>
       </c>
       <c r="C124" t="str">
         <v>Researching</v>
       </c>
       <c r="D124" t="str">
-        <v>Güvenli görselleştirme; endüstriyel yazılım-donanım entegrasyonu; sistem güvenliği + insan–makine etkileşimi</v>
+        <v/>
       </c>
       <c r="E124" t="str">
-        <v>https://www.igd.fraunhofer.de</v>
+        <v/>
       </c>
       <c r="F124" t="str">
-        <v>Darmstadt</v>
+        <v/>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="B125" t="str">
-        <v>Rovenma</v>
+        <v>SINTEF</v>
       </c>
       <c r="C125" t="str">
         <v>Researching</v>
       </c>
       <c r="D125" t="str">
-        <v>FPGA kripto</v>
+        <v/>
       </c>
       <c r="E125" t="str">
-        <v>https://www.rovenma.com</v>
+        <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ankara</v>
+        <v/>
       </c>
       <c r="G125">
         <v>1</v>
@@ -5526,22 +5526,22 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B126" t="str">
-        <v>TÜBİTAK BİLGEM</v>
+        <v>RISE Araştirma Enstitileri</v>
       </c>
       <c r="C126" t="str">
         <v>Researching</v>
       </c>
       <c r="D126" t="str">
-        <v>Kriptoloji/Elektronik</v>
+        <v/>
       </c>
       <c r="E126" t="str">
-        <v>https://bilgem.tubitak.gov.tr</v>
+        <v/>
       </c>
       <c r="F126" t="str">
-        <v>Gebze</v>
+        <v/>
       </c>
       <c r="G126">
         <v>1</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B127" t="str">
-        <v>ProvenRun</v>
+        <v>Prodrive Technologies</v>
       </c>
       <c r="C127" t="str">
         <v>Researching</v>
       </c>
       <c r="D127" t="str">
-        <v>Güvenli OS/TEE</v>
+        <v/>
       </c>
       <c r="E127" t="str">
-        <v>https://provenrun.com</v>
+        <v/>
       </c>
       <c r="F127" t="str">
-        <v>Paris</v>
+        <v/>
       </c>
       <c r="G127">
         <v>1</v>
@@ -5608,25 +5608,25 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="B128" t="str">
-        <v>Secure-IC</v>
+        <v>Holst Centre</v>
       </c>
       <c r="C128" t="str">
         <v>Researching</v>
       </c>
       <c r="D128" t="str">
-        <v>SoC/FPGA IP</v>
+        <v/>
       </c>
       <c r="E128" t="str">
-        <v>https://www.secure-ic.com</v>
+        <v/>
       </c>
       <c r="F128" t="str">
-        <v>Rennes</v>
+        <v/>
       </c>
       <c r="G128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" t="str">
         <v/>
@@ -5649,25 +5649,25 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B129" t="str">
-        <v>Emproof</v>
+        <v>TNO Embedded Systems Innovation (ESI)</v>
       </c>
       <c r="C129" t="str">
         <v>Researching</v>
       </c>
       <c r="D129" t="str">
-        <v>Anti-RE araçları</v>
+        <v/>
       </c>
       <c r="E129" t="str">
-        <v>https://www.emproof.com</v>
+        <v/>
       </c>
       <c r="F129" t="str">
-        <v>Bochum</v>
+        <v/>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" t="str">
         <v/>
@@ -5690,22 +5690,22 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B130" t="str">
-        <v>Riscure</v>
+        <v>Roke Manor Research</v>
       </c>
       <c r="C130" t="str">
         <v>Researching</v>
       </c>
       <c r="D130" t="str">
-        <v>Güvenlik testleri</v>
+        <v>Videantis Hannover merkezli derin öğrenme, bilgisayarla görme ve video işleme çözümleri sağlayan bir şirkettir.</v>
       </c>
       <c r="E130" t="str">
-        <v>https://www.riscure.com</v>
+        <v>https://www.videantis.com</v>
       </c>
       <c r="F130" t="str">
-        <v>Delft</v>
+        <v>Hannover, DE</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -5726,27 +5726,27 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B131" t="str">
-        <v>IMEC</v>
+        <v>Cambridge Consultants</v>
       </c>
       <c r="C131" t="str">
         <v>Researching</v>
       </c>
       <c r="D131" t="str">
-        <v>Yarıiletken Ar-Ge</v>
+        <v/>
       </c>
       <c r="E131" t="str">
-        <v>https://www.imec-int.com</v>
+        <v/>
       </c>
       <c r="F131" t="str">
-        <v>Leuven</v>
+        <v/>
       </c>
       <c r="G131">
         <v>1</v>
@@ -5772,22 +5772,22 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B132" t="str">
-        <v>KU Leuven</v>
+        <v>Videantis</v>
       </c>
       <c r="C132" t="str">
         <v>Researching</v>
       </c>
       <c r="D132" t="str">
-        <v>Physical attacks</v>
+        <v/>
       </c>
       <c r="E132" t="str">
-        <v>https://www.esat.kuleuven.be</v>
+        <v/>
       </c>
       <c r="F132" t="str">
-        <v>Leuven</v>
+        <v/>
       </c>
       <c r="G132">
         <v>1</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B133" t="str">
-        <v>TU Graz - IAIK</v>
+        <v>FZI</v>
       </c>
       <c r="C133" t="str">
         <v>Researching</v>
       </c>
       <c r="D133" t="str">
-        <v>RISC-V güvenliği</v>
+        <v/>
       </c>
       <c r="E133" t="str">
-        <v>https://www.iaik.tugraz.at</v>
+        <v/>
       </c>
       <c r="F133" t="str">
-        <v>Graz</v>
+        <v/>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5854,22 +5854,22 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="B134" t="str">
-        <v>UniBW Münih</v>
+        <v>DLR Robotik &amp; Mekatronik Enstitüsü</v>
       </c>
       <c r="C134" t="str">
         <v>Researching</v>
       </c>
       <c r="D134" t="str">
-        <v>Gömülü kriptografi</v>
+        <v/>
       </c>
       <c r="E134" t="str">
-        <v>https://www.unibw.de</v>
+        <v/>
       </c>
       <c r="F134" t="str">
-        <v>Münih</v>
+        <v/>
       </c>
       <c r="G134">
         <v>1</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B135" t="str">
-        <v>HGI / MPI-SP</v>
+        <v>Sematicon AG</v>
       </c>
       <c r="C135" t="str">
-        <v>Researching</v>
+        <v>Applied</v>
       </c>
       <c r="D135" t="str">
-        <v>Donanım Trojan</v>
+        <v>Akıllı sensörler; elektronik ve mekanik sistem entegrasyonu; endüstriyel gömülü çözümler</v>
       </c>
       <c r="E135" t="str">
-        <v>https://hgi.rub.de</v>
+        <v>https://www.lbf.fraunhofer.de</v>
       </c>
       <c r="F135" t="str">
-        <v>Bochum</v>
+        <v>Darmstadt</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -5931,27 +5931,27 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 15:44:52</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B136" t="str">
-        <v>CISPA</v>
+        <v>VDE Prüf- und Zertifizierungsinstitut</v>
       </c>
       <c r="C136" t="str">
         <v>Researching</v>
       </c>
       <c r="D136" t="str">
-        <v>Firmware güvenliği</v>
+        <v>Elektronik ve gömülü sistem testleri; güvenlik, EMC ve donanım doğrulaması; sertifikasyon öncesi teknik analiz</v>
       </c>
       <c r="E136" t="str">
-        <v>https://cispa.de</v>
+        <v>https://www.vde.com</v>
       </c>
       <c r="F136" t="str">
-        <v>Saarbrücken</v>
+        <v>Offenbach</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B137" t="str">
-        <v>Fraunhofer AISEC</v>
+        <v>ESCRYPT</v>
       </c>
       <c r="C137" t="str">
         <v>Researching</v>
       </c>
       <c r="D137" t="str">
-        <v>Donanım güvenliği</v>
+        <v>Otomotiv siber güvenliği; ECU, firmware ve gömülü güvenlik; güvenli yaşam döngüsü ve tehdit modelleme</v>
       </c>
       <c r="E137" t="str">
-        <v>https://www.aisec.fraunhofer.de</v>
+        <v>https://www.escrypt.com</v>
       </c>
       <c r="F137" t="str">
-        <v>Münih</v>
+        <v>Frankfurt</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -6018,22 +6018,22 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B138" t="str">
-        <v>Digital Worx</v>
+        <v>ATHENE</v>
       </c>
       <c r="C138" t="str">
         <v>Researching</v>
       </c>
       <c r="D138" t="str">
-        <v>Mobil/IoT</v>
+        <v>Donanım destekli güvenlik; gömülü ve siber-fiziksel sistem güvenliği; endüstriyel ve kritik altyapı güvenliği</v>
       </c>
       <c r="E138" t="str">
-        <v>https://digital-worx.de</v>
+        <v>https://www.athene-center.de</v>
       </c>
       <c r="F138" t="str">
-        <v>Stuttgart</v>
+        <v>Darmstadt</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B139" t="str">
-        <v>diconium</v>
+        <v>Fraunhofer IGD</v>
       </c>
       <c r="C139" t="str">
         <v>Researching</v>
       </c>
       <c r="D139" t="str">
-        <v>Dijital dönüşüm</v>
+        <v>Güvenli görselleştirme; endüstriyel yazılım-donanım entegrasyonu; sistem güvenliği + insan–makine etkileşimi</v>
       </c>
       <c r="E139" t="str">
-        <v>https://diconium.com</v>
+        <v>https://www.igd.fraunhofer.de</v>
       </c>
       <c r="F139" t="str">
-        <v>Stuttgart</v>
+        <v>Darmstadt</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -6100,22 +6100,22 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B140" t="str">
-        <v>Zoi</v>
+        <v>Rovenma</v>
       </c>
       <c r="C140" t="str">
         <v>Researching</v>
       </c>
       <c r="D140" t="str">
-        <v>Bulut/IoT</v>
+        <v>FPGA kripto</v>
       </c>
       <c r="E140" t="str">
-        <v>https://zoi.de</v>
+        <v>https://www.rovenma.com</v>
       </c>
       <c r="F140" t="str">
-        <v>Stuttgart</v>
+        <v>Ankara</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B141" t="str">
-        <v>tsenso</v>
+        <v>TÜBİTAK BİLGEM</v>
       </c>
       <c r="C141" t="str">
         <v>Researching</v>
       </c>
       <c r="D141" t="str">
-        <v>Gıda takip</v>
+        <v>Kriptoloji/Elektronik</v>
       </c>
       <c r="E141" t="str">
-        <v>https://tsenso.com</v>
+        <v>https://bilgem.tubitak.gov.tr</v>
       </c>
       <c r="F141" t="str">
-        <v>Stuttgart</v>
+        <v>Gebze</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -6182,22 +6182,22 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B142" t="str">
-        <v>vialytics</v>
+        <v>ProvenRun</v>
       </c>
       <c r="C142" t="str">
         <v>Researching</v>
       </c>
       <c r="D142" t="str">
-        <v>Yol denetimi</v>
+        <v>Güvenli OS/TEE</v>
       </c>
       <c r="E142" t="str">
-        <v>https://vialytics.com</v>
+        <v>https://provenrun.com</v>
       </c>
       <c r="F142" t="str">
-        <v>Stuttgart</v>
+        <v>Paris</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -6223,25 +6223,25 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B143" t="str">
-        <v>BABLE</v>
+        <v>Secure-IC</v>
       </c>
       <c r="C143" t="str">
         <v>Researching</v>
       </c>
       <c r="D143" t="str">
-        <v>Akıllı şehirler</v>
+        <v>SoC/FPGA IP</v>
       </c>
       <c r="E143" t="str">
-        <v>https://bable-smartcities.eu</v>
+        <v>https://www.secure-ic.com</v>
       </c>
       <c r="F143" t="str">
-        <v>Stuttgart</v>
+        <v>Rennes</v>
       </c>
       <c r="G143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H143" t="str">
         <v/>
@@ -6264,22 +6264,22 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B144" t="str">
-        <v>asvin</v>
+        <v>Emproof</v>
       </c>
       <c r="C144" t="str">
         <v>Researching</v>
       </c>
       <c r="D144" t="str">
-        <v>IoT tedarik zinciri</v>
+        <v>Anti-RE araçları</v>
       </c>
       <c r="E144" t="str">
-        <v>https://asvin.io</v>
+        <v>https://www.emproof.com</v>
       </c>
       <c r="F144" t="str">
-        <v>Stuttgart</v>
+        <v>Bochum</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B145" t="str">
-        <v>DevsUnity</v>
+        <v>Riscure</v>
       </c>
       <c r="C145" t="str">
         <v>Researching</v>
       </c>
       <c r="D145" t="str">
-        <v>Yazılım danışmanlık</v>
+        <v>Güvenlik testleri</v>
       </c>
       <c r="E145" t="str">
-        <v>https://devsunity.com</v>
+        <v>https://www.riscure.com</v>
       </c>
       <c r="F145" t="str">
-        <v>Berlin</v>
+        <v>Delft</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -6346,22 +6346,22 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B146" t="str">
-        <v>ProSec</v>
+        <v>IMEC</v>
       </c>
       <c r="C146" t="str">
         <v>Researching</v>
       </c>
       <c r="D146" t="str">
-        <v>OT ağ koruması</v>
+        <v>Yarıiletken Ar-Ge</v>
       </c>
       <c r="E146" t="str">
-        <v>https://www.prosec-networks.com</v>
+        <v>https://www.imec-int.com</v>
       </c>
       <c r="F146" t="str">
-        <v>Stuttgart</v>
+        <v>Leuven</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B147" t="str">
-        <v>Wire</v>
+        <v>KU Leuven</v>
       </c>
       <c r="C147" t="str">
         <v>Researching</v>
       </c>
       <c r="D147" t="str">
-        <v>Güvenli mesajlaşma</v>
+        <v>Physical attacks</v>
       </c>
       <c r="E147" t="str">
-        <v>https://wire.com</v>
+        <v>https://www.esat.kuleuven.be</v>
       </c>
       <c r="F147" t="str">
-        <v>Berlin</v>
+        <v>Leuven</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -6428,22 +6428,22 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B148" t="str">
-        <v>Spyrosoft</v>
+        <v>TU Graz - IAIK</v>
       </c>
       <c r="C148" t="str">
         <v>Researching</v>
       </c>
       <c r="D148" t="str">
-        <v>Gömülü/Otomotiv</v>
+        <v>RISC-V güvenliği</v>
       </c>
       <c r="E148" t="str">
-        <v>https://spyro-soft.com</v>
+        <v>https://www.iaik.tugraz.at</v>
       </c>
       <c r="F148" t="str">
-        <v>Stuttgart</v>
+        <v>Graz</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B149" t="str">
-        <v>IT Designers</v>
+        <v>UniBW Münih</v>
       </c>
       <c r="C149" t="str">
         <v>Researching</v>
       </c>
       <c r="D149" t="str">
-        <v>IoT yazılım</v>
+        <v>Gömülü kriptografi</v>
       </c>
       <c r="E149" t="str">
-        <v>https://www.itdesigners.de</v>
+        <v>https://www.unibw.de</v>
       </c>
       <c r="F149" t="str">
-        <v>Frankfurt</v>
+        <v>Münih</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -6510,22 +6510,22 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B150" t="str">
-        <v>Phoenix Contact</v>
+        <v>HGI / MPI-SP</v>
       </c>
       <c r="C150" t="str">
         <v>Researching</v>
       </c>
       <c r="D150" t="str">
-        <v>Siber güvenlik</v>
+        <v>Donanım Trojan</v>
       </c>
       <c r="E150" t="str">
-        <v>https://www.phoenixcontact.com</v>
+        <v>https://hgi.rub.de</v>
       </c>
       <c r="F150" t="str">
-        <v>Frankfurt</v>
+        <v>Bochum</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="151">
       <c r="A151">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B151" t="str">
-        <v>Fraunhofer IZM</v>
+        <v>CISPA</v>
       </c>
       <c r="C151" t="str">
         <v>Researching</v>
       </c>
       <c r="D151" t="str">
-        <v>Mikroelektronik</v>
+        <v>Firmware güvenliği</v>
       </c>
       <c r="E151" t="str">
-        <v>https://www.izm.fraunhofer.de</v>
+        <v>https://cispa.de</v>
       </c>
       <c r="F151" t="str">
-        <v>Berlin</v>
+        <v>Saarbrücken</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -6592,22 +6592,22 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B152" t="str">
-        <v>Continental</v>
+        <v>Fraunhofer AISEC</v>
       </c>
       <c r="C152" t="str">
         <v>Researching</v>
       </c>
       <c r="D152" t="str">
-        <v>Otomotiv</v>
+        <v>Donanım güvenliği</v>
       </c>
       <c r="E152" t="str">
-        <v>https://www.continental.com</v>
+        <v>https://www.aisec.fraunhofer.de</v>
       </c>
       <c r="F152" t="str">
-        <v>Türkiye</v>
+        <v>Münih</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B153" t="str">
-        <v>Bosch</v>
+        <v>Digital Worx</v>
       </c>
       <c r="C153" t="str">
         <v>Researching</v>
       </c>
       <c r="D153" t="str">
-        <v>Otomotiv</v>
+        <v>Mobil/IoT</v>
       </c>
       <c r="E153" t="str">
-        <v>https://www.bosch.com</v>
+        <v>https://digital-worx.de</v>
       </c>
       <c r="F153" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -6674,22 +6674,22 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B154" t="str">
-        <v>Infineon</v>
+        <v>diconium</v>
       </c>
       <c r="C154" t="str">
         <v>Researching</v>
       </c>
       <c r="D154" t="str">
-        <v>Çip</v>
+        <v>Dijital dönüşüm</v>
       </c>
       <c r="E154" t="str">
-        <v>https://www.infineon.com</v>
+        <v>https://diconium.com</v>
       </c>
       <c r="F154" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B155" t="str">
-        <v>STMicro</v>
+        <v>Zoi</v>
       </c>
       <c r="C155" t="str">
         <v>Researching</v>
       </c>
       <c r="D155" t="str">
-        <v>Çip</v>
+        <v>Bulut/IoT</v>
       </c>
       <c r="E155" t="str">
-        <v>https://www.st.com</v>
+        <v>https://zoi.de</v>
       </c>
       <c r="F155" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -6756,22 +6756,22 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B156" t="str">
-        <v>NXP</v>
+        <v>tsenso</v>
       </c>
       <c r="C156" t="str">
         <v>Researching</v>
       </c>
       <c r="D156" t="str">
-        <v>Çip</v>
+        <v>Gıda takip</v>
       </c>
       <c r="E156" t="str">
-        <v>https://www.nxp.com</v>
+        <v>https://tsenso.com</v>
       </c>
       <c r="F156" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -6797,25 +6797,25 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B157" t="str">
-        <v>Qualcomm</v>
+        <v>vialytics</v>
       </c>
       <c r="C157" t="str">
         <v>Researching</v>
       </c>
       <c r="D157" t="str">
-        <v>SoC/çip</v>
+        <v>Yol denetimi</v>
       </c>
       <c r="E157" t="str">
-        <v>https://www.qualcomm.com</v>
+        <v>https://vialytics.com</v>
       </c>
       <c r="F157" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" t="str">
         <v/>
@@ -6838,22 +6838,22 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B158" t="str">
-        <v>ARM</v>
+        <v>BABLE</v>
       </c>
       <c r="C158" t="str">
         <v>Researching</v>
       </c>
       <c r="D158" t="str">
-        <v>Çekirdek IP</v>
+        <v>Akıllı şehirler</v>
       </c>
       <c r="E158" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://bable-smartcities.eu</v>
       </c>
       <c r="F158" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B159" t="str">
-        <v>Intel</v>
+        <v>asvin</v>
       </c>
       <c r="C159" t="str">
         <v>Researching</v>
       </c>
       <c r="D159" t="str">
-        <v>Yarıiletken</v>
+        <v>IoT tedarik zinciri</v>
       </c>
       <c r="E159" t="str">
-        <v>https://www.intel.com</v>
+        <v>https://asvin.io</v>
       </c>
       <c r="F159" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -6920,22 +6920,22 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B160" t="str">
-        <v>Xiaomi</v>
+        <v>DevsUnity</v>
       </c>
       <c r="C160" t="str">
         <v>Researching</v>
       </c>
       <c r="D160" t="str">
-        <v>Elektronik</v>
+        <v>Yazılım danışmanlık</v>
       </c>
       <c r="E160" t="str">
-        <v>https://www.mi.com/tr</v>
+        <v>https://devsunity.com</v>
       </c>
       <c r="F160" t="str">
-        <v>Türkiye</v>
+        <v>Berlin</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B161" t="str">
-        <v>LG</v>
+        <v>ProSec</v>
       </c>
       <c r="C161" t="str">
         <v>Researching</v>
       </c>
       <c r="D161" t="str">
-        <v>Elektronik</v>
+        <v>OT ağ koruması</v>
       </c>
       <c r="E161" t="str">
-        <v>https://www.lg.com/tr</v>
+        <v>https://www.prosec-networks.com</v>
       </c>
       <c r="F161" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -7002,22 +7002,22 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B162" t="str">
-        <v>Samsung</v>
+        <v>Wire</v>
       </c>
       <c r="C162" t="str">
         <v>Researching</v>
       </c>
       <c r="D162" t="str">
-        <v>Elektronik</v>
+        <v>Güvenli mesajlaşma</v>
       </c>
       <c r="E162" t="str">
-        <v>https://www.samsung.com/tr</v>
+        <v>https://wire.com</v>
       </c>
       <c r="F162" t="str">
-        <v>Türkiye</v>
+        <v>Berlin</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B163" t="str">
-        <v>Apple</v>
+        <v>Spyrosoft</v>
       </c>
       <c r="C163" t="str">
         <v>Researching</v>
       </c>
       <c r="D163" t="str">
-        <v>Tüketici teknoloji</v>
+        <v>Gömülü/Otomotiv</v>
       </c>
       <c r="E163" t="str">
-        <v>https://www.apple.com/tr</v>
+        <v>https://spyro-soft.com</v>
       </c>
       <c r="F163" t="str">
-        <v>Türkiye</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -7084,22 +7084,22 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B164" t="str">
-        <v>Amazon</v>
+        <v>IT Designers</v>
       </c>
       <c r="C164" t="str">
         <v>Researching</v>
       </c>
       <c r="D164" t="str">
-        <v>E-ticaret</v>
+        <v>IoT yazılım</v>
       </c>
       <c r="E164" t="str">
-        <v>https://www.amazon.com.tr</v>
+        <v>https://www.itdesigners.de</v>
       </c>
       <c r="F164" t="str">
-        <v>Türkiye</v>
+        <v>Frankfurt</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B165" t="str">
-        <v>Google</v>
+        <v>Phoenix Contact</v>
       </c>
       <c r="C165" t="str">
         <v>Researching</v>
       </c>
       <c r="D165" t="str">
-        <v>Teknoloji</v>
+        <v>Siber güvenlik</v>
       </c>
       <c r="E165" t="str">
-        <v>https://www.google.com</v>
+        <v>https://www.phoenixcontact.com</v>
       </c>
       <c r="F165" t="str">
-        <v>Türkiye</v>
+        <v>Frankfurt</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -7166,22 +7166,22 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B166" t="str">
-        <v>Microsoft</v>
+        <v>Fraunhofer IZM</v>
       </c>
       <c r="C166" t="str">
         <v>Researching</v>
       </c>
       <c r="D166" t="str">
-        <v>Teknoloji</v>
+        <v>Mikroelektronik</v>
       </c>
       <c r="E166" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.izm.fraunhofer.de</v>
       </c>
       <c r="F166" t="str">
-        <v>Türkiye</v>
+        <v>Berlin</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -7207,19 +7207,19 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B167" t="str">
-        <v>SAP</v>
+        <v>Continental</v>
       </c>
       <c r="C167" t="str">
         <v>Researching</v>
       </c>
       <c r="D167" t="str">
-        <v>Kurumsal yazılım</v>
+        <v>Otomotiv</v>
       </c>
       <c r="E167" t="str">
-        <v>https://www.sap.com/turkey</v>
+        <v>https://www.continental.com</v>
       </c>
       <c r="F167" t="str">
         <v>Türkiye</v>
@@ -7248,19 +7248,19 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B168" t="str">
-        <v>Huawei</v>
+        <v>Bosch</v>
       </c>
       <c r="C168" t="str">
         <v>Researching</v>
       </c>
       <c r="D168" t="str">
-        <v>Telekom altyapı</v>
+        <v>Otomotiv</v>
       </c>
       <c r="E168" t="str">
-        <v>https://www.huawei.com/tr</v>
+        <v>https://www.bosch.com</v>
       </c>
       <c r="F168" t="str">
         <v>Türkiye</v>
@@ -7289,19 +7289,19 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B169" t="str">
-        <v>Nokia</v>
+        <v>Infineon</v>
       </c>
       <c r="C169" t="str">
         <v>Researching</v>
       </c>
       <c r="D169" t="str">
-        <v>Telekom altyapı</v>
+        <v>Çip</v>
       </c>
       <c r="E169" t="str">
-        <v>https://www.nokia.com</v>
+        <v>https://www.infineon.com</v>
       </c>
       <c r="F169" t="str">
         <v>Türkiye</v>
@@ -7330,19 +7330,19 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B170" t="str">
-        <v>Ericsson</v>
+        <v>STMicro</v>
       </c>
       <c r="C170" t="str">
         <v>Researching</v>
       </c>
       <c r="D170" t="str">
-        <v>Telekom altyapı</v>
+        <v>Çip</v>
       </c>
       <c r="E170" t="str">
-        <v>https://www.ericsson.com/tr</v>
+        <v>https://www.st.com</v>
       </c>
       <c r="F170" t="str">
         <v>Türkiye</v>
@@ -7371,19 +7371,19 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B171" t="str">
-        <v>Vodafone</v>
+        <v>NXP</v>
       </c>
       <c r="C171" t="str">
         <v>Researching</v>
       </c>
       <c r="D171" t="str">
-        <v>Telekom</v>
+        <v>Çip</v>
       </c>
       <c r="E171" t="str">
-        <v>https://www.vodafone.com.tr</v>
+        <v>https://www.nxp.com</v>
       </c>
       <c r="F171" t="str">
         <v>Türkiye</v>
@@ -7412,22 +7412,22 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B172" t="str">
-        <v>Turkcell</v>
+        <v>Qualcomm</v>
       </c>
       <c r="C172" t="str">
         <v>Researching</v>
       </c>
       <c r="D172" t="str">
-        <v>2026 Summer | Telecom-scale systems, security engineering ve detection odakli ekipler.</v>
+        <v>SoC/çip</v>
       </c>
       <c r="E172" t="str">
-        <v>https://www.turkcell.com.tr</v>
+        <v>https://www.qualcomm.com</v>
       </c>
       <c r="F172" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G172">
         <v>2</v>
@@ -7448,24 +7448,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M172" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B173" t="str">
-        <v>Mavi Jeans</v>
+        <v>ARM</v>
       </c>
       <c r="C173" t="str">
         <v>Researching</v>
       </c>
       <c r="D173" t="str">
-        <v>Perakende</v>
+        <v>Çekirdek IP</v>
       </c>
       <c r="E173" t="str">
-        <v>https://www.mavi.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F173" t="str">
         <v>Türkiye</v>
@@ -7494,19 +7494,19 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B174" t="str">
-        <v>Obsidian</v>
+        <v>Intel</v>
       </c>
       <c r="C174" t="str">
         <v>Researching</v>
       </c>
       <c r="D174" t="str">
-        <v>Genel yazılım</v>
+        <v>Yarıiletken</v>
       </c>
       <c r="E174" t="str">
-        <v>https://obsidian.md</v>
+        <v>https://www.intel.com</v>
       </c>
       <c r="F174" t="str">
         <v>Türkiye</v>
@@ -7535,19 +7535,19 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B175" t="str">
-        <v>KoçSistem</v>
+        <v>Xiaomi</v>
       </c>
       <c r="C175" t="str">
         <v>Researching</v>
       </c>
       <c r="D175" t="str">
-        <v>BT hizmetleri</v>
+        <v>Elektronik</v>
       </c>
       <c r="E175" t="str">
-        <v>https://www.kocsistem.com.tr</v>
+        <v>https://www.mi.com/tr</v>
       </c>
       <c r="F175" t="str">
         <v>Türkiye</v>
@@ -7576,19 +7576,19 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B176" t="str">
-        <v>Martı</v>
+        <v>LG</v>
       </c>
       <c r="C176" t="str">
         <v>Researching</v>
       </c>
       <c r="D176" t="str">
-        <v>Mikromobilite</v>
+        <v>Elektronik</v>
       </c>
       <c r="E176" t="str">
-        <v>https://www.marti.tech</v>
+        <v>https://www.lg.com/tr</v>
       </c>
       <c r="F176" t="str">
         <v>Türkiye</v>
@@ -7617,19 +7617,19 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B177" t="str">
-        <v>BiTaksi</v>
+        <v>Samsung</v>
       </c>
       <c r="C177" t="str">
         <v>Researching</v>
       </c>
       <c r="D177" t="str">
-        <v>Ulaşım</v>
+        <v>Elektronik</v>
       </c>
       <c r="E177" t="str">
-        <v>https://bitaksi.com</v>
+        <v>https://www.samsung.com/tr</v>
       </c>
       <c r="F177" t="str">
         <v>Türkiye</v>
@@ -7658,19 +7658,19 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B178" t="str">
-        <v>Peak Games</v>
+        <v>Apple</v>
       </c>
       <c r="C178" t="str">
         <v>Researching</v>
       </c>
       <c r="D178" t="str">
-        <v>Oyun</v>
+        <v>Tüketici teknoloji</v>
       </c>
       <c r="E178" t="str">
-        <v>https://peak.com</v>
+        <v>https://www.apple.com/tr</v>
       </c>
       <c r="F178" t="str">
         <v>Türkiye</v>
@@ -7699,19 +7699,19 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B179" t="str">
-        <v>Getir</v>
+        <v>Amazon</v>
       </c>
       <c r="C179" t="str">
         <v>Researching</v>
       </c>
       <c r="D179" t="str">
-        <v>Tüketici uygulaması</v>
+        <v>E-ticaret</v>
       </c>
       <c r="E179" t="str">
-        <v>https://getir.com</v>
+        <v>https://www.amazon.com.tr</v>
       </c>
       <c r="F179" t="str">
         <v>Türkiye</v>
@@ -7740,19 +7740,19 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B180" t="str">
-        <v>Hepsiburada</v>
+        <v>Google</v>
       </c>
       <c r="C180" t="str">
         <v>Researching</v>
       </c>
       <c r="D180" t="str">
-        <v>E-ticaret</v>
+        <v>Teknoloji</v>
       </c>
       <c r="E180" t="str">
-        <v>https://www.hepsiburada.com</v>
+        <v>https://www.google.com</v>
       </c>
       <c r="F180" t="str">
         <v>Türkiye</v>
@@ -7781,19 +7781,19 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B181" t="str">
-        <v>Trendyol</v>
+        <v>Microsoft</v>
       </c>
       <c r="C181" t="str">
         <v>Researching</v>
       </c>
       <c r="D181" t="str">
-        <v>E-ticaret</v>
+        <v>Teknoloji</v>
       </c>
       <c r="E181" t="str">
-        <v>https://www.trendyol.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F181" t="str">
         <v>Türkiye</v>
@@ -7822,19 +7822,19 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B182" t="str">
-        <v>Sahibinden.com</v>
+        <v>SAP</v>
       </c>
       <c r="C182" t="str">
         <v>Researching</v>
       </c>
       <c r="D182" t="str">
-        <v>İnternet platformu</v>
+        <v>Kurumsal yazılım</v>
       </c>
       <c r="E182" t="str">
-        <v>https://www.sahibinden.com</v>
+        <v>https://www.sap.com/turkey</v>
       </c>
       <c r="F182" t="str">
         <v>Türkiye</v>
@@ -7863,19 +7863,19 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B183" t="str">
-        <v>Logo Yazılım</v>
+        <v>Huawei</v>
       </c>
       <c r="C183" t="str">
         <v>Researching</v>
       </c>
       <c r="D183" t="str">
-        <v>Kurumsal yazılım</v>
+        <v>Telekom altyapı</v>
       </c>
       <c r="E183" t="str">
-        <v>https://www.logo.com.tr</v>
+        <v>https://www.huawei.com/tr</v>
       </c>
       <c r="F183" t="str">
         <v>Türkiye</v>
@@ -7904,19 +7904,19 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B184" t="str">
-        <v>ASELSANNET</v>
+        <v>Nokia</v>
       </c>
       <c r="C184" t="str">
         <v>Researching</v>
       </c>
       <c r="D184" t="str">
-        <v>Ağ çözümleri</v>
+        <v>Telekom altyapı</v>
       </c>
       <c r="E184" t="str">
-        <v>https://www.aselsannet.com.tr</v>
+        <v>https://www.nokia.com</v>
       </c>
       <c r="F184" t="str">
         <v>Türkiye</v>
@@ -7945,25 +7945,25 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B185" t="str">
-        <v>Roketsan</v>
+        <v>Ericsson</v>
       </c>
       <c r="C185" t="str">
         <v>Researching</v>
       </c>
       <c r="D185" t="str">
-        <v>2026 Summer | Embedded systems, guidance/control ve güvenlik odakli ekipler.</v>
+        <v>Telekom altyapı</v>
       </c>
       <c r="E185" t="str">
-        <v>https://www.roketsan.com.tr</v>
+        <v>https://www.ericsson.com/tr</v>
       </c>
       <c r="F185" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H185" t="str">
         <v/>
@@ -7981,24 +7981,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M185" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B186" t="str">
-        <v>Baykar</v>
+        <v>Vodafone</v>
       </c>
       <c r="C186" t="str">
         <v>Researching</v>
       </c>
       <c r="D186" t="str">
-        <v>İHA sistemleri</v>
+        <v>Telekom</v>
       </c>
       <c r="E186" t="str">
-        <v>https://www.baykartech.com</v>
+        <v>https://www.vodafone.com.tr</v>
       </c>
       <c r="F186" t="str">
         <v>Türkiye</v>
@@ -8027,25 +8027,25 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B187" t="str">
-        <v>TOGG</v>
+        <v>Turkcell</v>
       </c>
       <c r="C187" t="str">
         <v>Researching</v>
       </c>
       <c r="D187" t="str">
-        <v>Elektrikli araç</v>
+        <v>2026 Summer | Telecom-scale systems, security engineering ve detection odakli ekipler.</v>
       </c>
       <c r="E187" t="str">
-        <v>https://www.togg.com.tr</v>
+        <v>https://www.turkcell.com.tr</v>
       </c>
       <c r="F187" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187" t="str">
         <v/>
@@ -8063,30 +8063,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M187" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B188" t="str">
-        <v>Ford Otosan</v>
+        <v>Mavi Jeans</v>
       </c>
       <c r="C188" t="str">
         <v>Researching</v>
       </c>
       <c r="D188" t="str">
-        <v>2026 Summer | Otomotiv embedded, vehicle security ve sistem engineering odakli ekipler.</v>
+        <v>Perakende</v>
       </c>
       <c r="E188" t="str">
-        <v>https://www.fordotosan.com.tr</v>
+        <v>https://www.mavi.com</v>
       </c>
       <c r="F188" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H188" t="str">
         <v/>
@@ -8104,30 +8104,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M188" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B189" t="str">
-        <v>Vestel</v>
+        <v>Obsidian</v>
       </c>
       <c r="C189" t="str">
         <v>Researching</v>
       </c>
       <c r="D189" t="str">
-        <v>2026 Summer | IoT/embedded cihazlar ve güvenli ürün geliştirme odakli ekipler.</v>
+        <v>Genel yazılım</v>
       </c>
       <c r="E189" t="str">
-        <v>https://www.vestel.com</v>
+        <v>https://obsidian.md</v>
       </c>
       <c r="F189" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" t="str">
         <v/>
@@ -8145,24 +8145,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M189" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B190" t="str">
-        <v>Yıldız Holding</v>
+        <v>KoçSistem</v>
       </c>
       <c r="C190" t="str">
         <v>Researching</v>
       </c>
       <c r="D190" t="str">
-        <v>Genel holding</v>
+        <v>BT hizmetleri</v>
       </c>
       <c r="E190" t="str">
-        <v>https://www.yildizholding.com.tr</v>
+        <v>https://www.kocsistem.com.tr</v>
       </c>
       <c r="F190" t="str">
         <v>Türkiye</v>
@@ -8191,19 +8191,19 @@
     </row>
     <row r="191">
       <c r="A191">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B191" t="str">
-        <v>TÜBİTAK SAGE</v>
+        <v>Martı</v>
       </c>
       <c r="C191" t="str">
         <v>Researching</v>
       </c>
       <c r="D191" t="str">
-        <v>Savunma Ar-Ge</v>
+        <v>Mikromobilite</v>
       </c>
       <c r="E191" t="str">
-        <v>https://www.sage.tubitak.gov.tr</v>
+        <v>https://www.marti.tech</v>
       </c>
       <c r="F191" t="str">
         <v>Türkiye</v>
@@ -8232,25 +8232,25 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B192" t="str">
-        <v>Havelsan</v>
+        <v>BiTaksi</v>
       </c>
       <c r="C192" t="str">
         <v>Researching</v>
       </c>
       <c r="D192" t="str">
-        <v>2026 Summer | Cybersecurity, command-control, simulation ve secure software odakli ekipler.</v>
+        <v>Ulaşım</v>
       </c>
       <c r="E192" t="str">
-        <v>https://www.havelsan.com</v>
+        <v>https://bitaksi.com</v>
       </c>
       <c r="F192" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G192">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H192" t="str">
         <v/>
@@ -8268,24 +8268,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M192" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B193" t="str">
-        <v>Beko</v>
+        <v>Peak Games</v>
       </c>
       <c r="C193" t="str">
         <v>Researching</v>
       </c>
       <c r="D193" t="str">
-        <v>Tüketici elektroniği</v>
+        <v>Oyun</v>
       </c>
       <c r="E193" t="str">
-        <v>https://www.beko.com/tr-tr</v>
+        <v>https://peak.com</v>
       </c>
       <c r="F193" t="str">
         <v>Türkiye</v>
@@ -8314,19 +8314,19 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B194" t="str">
-        <v>STM</v>
+        <v>Getir</v>
       </c>
       <c r="C194" t="str">
         <v>Researching</v>
       </c>
       <c r="D194" t="str">
-        <v>Savunma ve siber güvenlik</v>
+        <v>Tüketici uygulaması</v>
       </c>
       <c r="E194" t="str">
-        <v>https://www.stm.com.tr</v>
+        <v>https://getir.com</v>
       </c>
       <c r="F194" t="str">
         <v>Türkiye</v>
@@ -8355,19 +8355,19 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B195" t="str">
-        <v>Ansys</v>
+        <v>Hepsiburada</v>
       </c>
       <c r="C195" t="str">
         <v>Researching</v>
       </c>
       <c r="D195" t="str">
-        <v>Emniyet-kritik gömülü sistem</v>
+        <v>E-ticaret</v>
       </c>
       <c r="E195" t="str">
-        <v>https://www.numesys.com.tr</v>
+        <v>https://www.hepsiburada.com</v>
       </c>
       <c r="F195" t="str">
         <v>Türkiye</v>
@@ -8396,25 +8396,25 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B196" t="str">
-        <v>Türk Telekom</v>
+        <v>Trendyol</v>
       </c>
       <c r="C196" t="str">
         <v>Researching</v>
       </c>
       <c r="D196" t="str">
-        <v>2026 Summer | Network/security ve large-scale systems odakli ekipler.</v>
+        <v>E-ticaret</v>
       </c>
       <c r="E196" t="str">
-        <v>https://www.turktelekom.com.tr/en</v>
+        <v>https://www.trendyol.com</v>
       </c>
       <c r="F196" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H196" t="str">
         <v/>
@@ -8432,30 +8432,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M196" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B197" t="str">
-        <v>Arçelik</v>
+        <v>Sahibinden.com</v>
       </c>
       <c r="C197" t="str">
         <v>Researching</v>
       </c>
       <c r="D197" t="str">
-        <v>2026 Summer | Embedded/IoT cihazlar, secure firmware ve product security odakli ekipler.</v>
+        <v>İnternet platformu</v>
       </c>
       <c r="E197" t="str">
-        <v>https://www.arcelikglobal.com/en</v>
+        <v>https://www.sahibinden.com</v>
       </c>
       <c r="F197" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H197" t="str">
         <v/>
@@ -8473,24 +8473,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M197" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B198" t="str">
-        <v>AET Elektronik</v>
+        <v>Logo Yazılım</v>
       </c>
       <c r="C198" t="str">
         <v>Researching</v>
       </c>
       <c r="D198" t="str">
-        <v>Elektronik ve telekom</v>
+        <v>Kurumsal yazılım</v>
       </c>
       <c r="E198" t="str">
-        <v>https://www.aetelectronics.com</v>
+        <v>https://www.logo.com.tr</v>
       </c>
       <c r="F198" t="str">
         <v>Türkiye</v>
@@ -8519,19 +8519,19 @@
     </row>
     <row r="199">
       <c r="A199">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B199" t="str">
-        <v>Infrasis</v>
+        <v>ASELSANNET</v>
       </c>
       <c r="C199" t="str">
         <v>Researching</v>
       </c>
       <c r="D199" t="str">
-        <v>Siber mühendislik</v>
+        <v>Ağ çözümleri</v>
       </c>
       <c r="E199" t="str">
-        <v>https://infrasis.com.tr</v>
+        <v>https://www.aselsannet.com.tr</v>
       </c>
       <c r="F199" t="str">
         <v>Türkiye</v>
@@ -8560,25 +8560,25 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B200" t="str">
-        <v>Seccops</v>
+        <v>Roketsan</v>
       </c>
       <c r="C200" t="str">
         <v>Researching</v>
       </c>
       <c r="D200" t="str">
-        <v>Kurumsal siber güvenlik</v>
+        <v>2026 Summer | Embedded systems, guidance/control ve güvenlik odakli ekipler.</v>
       </c>
       <c r="E200" t="str">
-        <v>https://seccops.com</v>
+        <v>https://www.roketsan.com.tr</v>
       </c>
       <c r="F200" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H200" t="str">
         <v/>
@@ -8596,24 +8596,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M200" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B201" t="str">
-        <v>Onex Yazılım</v>
+        <v>Baykar</v>
       </c>
       <c r="C201" t="str">
         <v>Researching</v>
       </c>
       <c r="D201" t="str">
-        <v>M2M ve gömülü yazılım</v>
+        <v>İHA sistemleri</v>
       </c>
       <c r="E201" t="str">
-        <v>https://onexyazilim.com</v>
+        <v>https://www.baykartech.com</v>
       </c>
       <c r="F201" t="str">
         <v>Türkiye</v>
@@ -8642,19 +8642,19 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B202" t="str">
-        <v>Inventra</v>
+        <v>TOGG</v>
       </c>
       <c r="C202" t="str">
         <v>Researching</v>
       </c>
       <c r="D202" t="str">
-        <v>Gömülü sistemler</v>
+        <v>Elektrikli araç</v>
       </c>
       <c r="E202" t="str">
-        <v>https://www.inventra.com.tr</v>
+        <v>https://www.togg.com.tr</v>
       </c>
       <c r="F202" t="str">
         <v>Türkiye</v>
@@ -8683,25 +8683,25 @@
     </row>
     <row r="203">
       <c r="A203">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B203" t="str">
-        <v>Cyberwise</v>
+        <v>Ford Otosan</v>
       </c>
       <c r="C203" t="str">
         <v>Researching</v>
       </c>
       <c r="D203" t="str">
-        <v>Entegre siber güvenlik</v>
+        <v>2026 Summer | Otomotiv embedded, vehicle security ve sistem engineering odakli ekipler.</v>
       </c>
       <c r="E203" t="str">
-        <v>https://cyberwise.com</v>
+        <v>https://www.fordotosan.com.tr</v>
       </c>
       <c r="F203" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H203" t="str">
         <v/>
@@ -8719,30 +8719,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M203" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B204" t="str">
-        <v>Desird Tasarım</v>
+        <v>Vestel</v>
       </c>
       <c r="C204" t="str">
         <v>Researching</v>
       </c>
       <c r="D204" t="str">
-        <v>Mikrokontrol ve gömülü yazılım</v>
+        <v>2026 Summer | IoT/embedded cihazlar ve güvenli ürün geliştirme odakli ekipler.</v>
       </c>
       <c r="E204" t="str">
-        <v>https://desird.com</v>
+        <v>https://www.vestel.com</v>
       </c>
       <c r="F204" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H204" t="str">
         <v/>
@@ -8760,24 +8760,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M204" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B205" t="str">
-        <v>Siemens</v>
+        <v>Yıldız Holding</v>
       </c>
       <c r="C205" t="str">
         <v>Researching</v>
       </c>
       <c r="D205" t="str">
-        <v>Enerji ve otomasyon stajı</v>
+        <v>Genel holding</v>
       </c>
       <c r="E205" t="str">
-        <v>https://www.siemens.com/tr</v>
+        <v>https://www.yildizholding.com.tr</v>
       </c>
       <c r="F205" t="str">
         <v>Türkiye</v>
@@ -8806,25 +8806,25 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B206" t="str">
-        <v>Aselsan</v>
+        <v>TÜBİTAK SAGE</v>
       </c>
       <c r="C206" t="str">
         <v>Researching</v>
       </c>
       <c r="D206" t="str">
-        <v>2026 Summer | Embedded systems, defense tech and secure systems odakli ekipler.</v>
+        <v>Savunma Ar-Ge</v>
       </c>
       <c r="E206" t="str">
-        <v>https://www.aselsan.com/en</v>
+        <v>https://www.sage.tubitak.gov.tr</v>
       </c>
       <c r="F206" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G206">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H206" t="str">
         <v/>
@@ -8842,30 +8842,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M206" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B207" t="str">
-        <v>ePati</v>
+        <v>Havelsan</v>
       </c>
       <c r="C207" t="str">
         <v>Researching</v>
       </c>
       <c r="D207" t="str">
-        <v>Yerli siber güvenlik ürünleri geliştiriyor</v>
+        <v>2026 Summer | Cybersecurity, command-control, simulation ve secure software odakli ekipler.</v>
       </c>
       <c r="E207" t="str">
-        <v>https://www.technoscope.com.tr</v>
+        <v>https://www.havelsan.com</v>
       </c>
       <c r="F207" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H207" t="str">
         <v/>
@@ -8883,24 +8883,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="M207" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B208" t="str">
-        <v>Barikat</v>
+        <v>Beko</v>
       </c>
       <c r="C208" t="str">
         <v>Researching</v>
       </c>
       <c r="D208" t="str">
-        <v>Siber güvenlik çözümleri sağlayıcısı</v>
+        <v>Tüketici elektroniği</v>
       </c>
       <c r="E208" t="str">
-        <v>Barikat</v>
+        <v>https://www.beko.com/tr-tr</v>
       </c>
       <c r="F208" t="str">
         <v>Türkiye</v>
@@ -8929,19 +8929,19 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B209" t="str">
-        <v>MELSiS</v>
+        <v>STM</v>
       </c>
       <c r="C209" t="str">
         <v>Researching</v>
       </c>
       <c r="D209" t="str">
-        <v>Elektronik tasarım ve gömülü sistem çözümleri</v>
+        <v>Savunma ve siber güvenlik</v>
       </c>
       <c r="E209" t="str">
-        <v>MELSİS</v>
+        <v>https://www.stm.com.tr</v>
       </c>
       <c r="F209" t="str">
         <v>Türkiye</v>
@@ -8968,9 +8968,624 @@
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210">
+        <v>15</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Ansys</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Emniyet-kritik gömülü sistem</v>
+      </c>
+      <c r="E210" t="str">
+        <v>https://www.numesys.com.tr</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K210" t="str">
+        <v/>
+      </c>
+      <c r="L210" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M210" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>14</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Türk Telekom</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026 Summer | Network/security ve large-scale systems odakli ekipler.</v>
+      </c>
+      <c r="E211" t="str">
+        <v>https://www.turktelekom.com.tr/en</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Turkey, TR</v>
+      </c>
+      <c r="G211">
+        <v>2</v>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K211" t="str">
+        <v/>
+      </c>
+      <c r="L211" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M211" t="str">
+        <v>2026-02-04 16:19:45</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>13</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Arçelik</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026 Summer | Embedded/IoT cihazlar, secure firmware ve product security odakli ekipler.</v>
+      </c>
+      <c r="E212" t="str">
+        <v>https://www.arcelikglobal.com/en</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Turkey, TR</v>
+      </c>
+      <c r="G212">
+        <v>3</v>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K212" t="str">
+        <v/>
+      </c>
+      <c r="L212" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M212" t="str">
+        <v>2026-02-04 16:19:45</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>12</v>
+      </c>
+      <c r="B213" t="str">
+        <v>AET Elektronik</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Elektronik ve telekom</v>
+      </c>
+      <c r="E213" t="str">
+        <v>https://www.aetelectronics.com</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
+      <c r="J213" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K213" t="str">
+        <v/>
+      </c>
+      <c r="L213" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M213" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>11</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Infrasis</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Siber mühendislik</v>
+      </c>
+      <c r="E214" t="str">
+        <v>https://infrasis.com.tr</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
+      <c r="J214" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K214" t="str">
+        <v/>
+      </c>
+      <c r="L214" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M214" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>10</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Seccops</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Kurumsal siber güvenlik</v>
+      </c>
+      <c r="E215" t="str">
+        <v>https://seccops.com</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
+      <c r="J215" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K215" t="str">
+        <v/>
+      </c>
+      <c r="L215" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M215" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>9</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Onex Yazılım</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D216" t="str">
+        <v>M2M ve gömülü yazılım</v>
+      </c>
+      <c r="E216" t="str">
+        <v>https://onexyazilim.com</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+      <c r="I216" t="str">
+        <v/>
+      </c>
+      <c r="J216" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K216" t="str">
+        <v/>
+      </c>
+      <c r="L216" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M216" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>8</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Inventra</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Gömülü sistemler</v>
+      </c>
+      <c r="E217" t="str">
+        <v>https://www.inventra.com.tr</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K217" t="str">
+        <v/>
+      </c>
+      <c r="L217" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M217" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>7</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Cyberwise</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Entegre siber güvenlik</v>
+      </c>
+      <c r="E218" t="str">
+        <v>https://cyberwise.com</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
+      <c r="J218" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K218" t="str">
+        <v/>
+      </c>
+      <c r="L218" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M218" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>6</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Desird Tasarım</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Mikrokontrol ve gömülü yazılım</v>
+      </c>
+      <c r="E219" t="str">
+        <v>https://desird.com</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <v/>
+      </c>
+      <c r="J219" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K219" t="str">
+        <v/>
+      </c>
+      <c r="L219" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M219" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>5</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Siemens</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Enerji ve otomasyon stajı</v>
+      </c>
+      <c r="E220" t="str">
+        <v>https://www.siemens.com/tr</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
+      <c r="J220" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K220" t="str">
+        <v/>
+      </c>
+      <c r="L220" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M220" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>4</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Aselsan</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D221" t="str">
+        <v>2026 Summer | Embedded systems, defense tech and secure systems odakli ekipler.</v>
+      </c>
+      <c r="E221" t="str">
+        <v>https://www.aselsan.com/en</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Turkey, TR</v>
+      </c>
+      <c r="G221">
+        <v>4</v>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
+      <c r="J221" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K221" t="str">
+        <v/>
+      </c>
+      <c r="L221" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M221" t="str">
+        <v>2026-02-04 16:19:45</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>3</v>
+      </c>
+      <c r="B222" t="str">
+        <v>ePati</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Yerli siber güvenlik ürünleri geliştiriyor</v>
+      </c>
+      <c r="E222" t="str">
+        <v>https://www.technoscope.com.tr</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
+      <c r="J222" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K222" t="str">
+        <v/>
+      </c>
+      <c r="L222" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M222" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>2</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Barikat</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Siber güvenlik çözümleri sağlayıcısı</v>
+      </c>
+      <c r="E223" t="str">
+        <v>Barikat</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G223">
+        <v>1</v>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
+      <c r="J223" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K223" t="str">
+        <v/>
+      </c>
+      <c r="L223" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M223" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>1</v>
+      </c>
+      <c r="B224" t="str">
+        <v>MELSiS</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Elektronik tasarım ve gömülü sistem çözümleri</v>
+      </c>
+      <c r="E224" t="str">
+        <v>MELSİS</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Türkiye</v>
+      </c>
+      <c r="G224">
+        <v>1</v>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
+      <c r="J224" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K224" t="str">
+        <v/>
+      </c>
+      <c r="L224" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="M224" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M224"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -609,19 +609,19 @@
         <v>213</v>
       </c>
       <c r="B6" t="str">
-        <v>TU Berlin SecT</v>
+        <v>KIT Chair of Dependable Nano Computing (CDNC)</v>
       </c>
       <c r="C6" t="str">
         <v>Researching</v>
       </c>
       <c r="D6" t="str">
-        <v>2026 Summer | Security in Telecommunications chair covering hardware security, secure embedded systems, and side-channel attacks. Initiative application.</v>
+        <v>2026 Summer | Hardware security lab known for FPGA side-channel and fault-attack research with active student thesis opportunities. Initiative application.</v>
       </c>
       <c r="E6" t="str">
-        <v>https://www.tu.berlin/en/sect</v>
+        <v>https://cdnc.itec.kit.edu/</v>
       </c>
       <c r="F6" t="str">
-        <v>Berlin, DE</v>
+        <v>Karlsruhe, DE</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -636,7 +636,7 @@
         <v>High</v>
       </c>
       <c r="K6" t="str">
-        <v>Security,Hardware,Embedded,Firmware,Systems</v>
+        <v>Hardware,Security,Embedded,Systems,Firmware</v>
       </c>
       <c r="L6" t="str">
         <v>2026-03-31</v>
@@ -650,19 +650,19 @@
         <v>214</v>
       </c>
       <c r="B7" t="str">
-        <v>KIT Chair of Dependable Nano Computing (CDNC)</v>
+        <v>TU Darmstadt ImpSec</v>
       </c>
       <c r="C7" t="str">
         <v>Researching</v>
       </c>
       <c r="D7" t="str">
-        <v>2026 Summer | Hardware security lab known for FPGA side-channel and fault-attack research with active student thesis opportunities. Initiative application.</v>
+        <v>2026 Summer | Implementation security chair focused on side-channel and fault attacks, ASICs, FPGAs, and microprocessor security. Initiative application.</v>
       </c>
       <c r="E7" t="str">
-        <v>https://cdnc.itec.kit.edu/</v>
+        <v>https://www.informatik.tu-darmstadt.de/impsec/start_impsec/index.en.jsp</v>
       </c>
       <c r="F7" t="str">
-        <v>Karlsruhe, DE</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -677,7 +677,7 @@
         <v>High</v>
       </c>
       <c r="K7" t="str">
-        <v>Hardware,Security,Embedded,Systems,Firmware</v>
+        <v>Hardware,Security,Embedded,Firmware,Systems</v>
       </c>
       <c r="L7" t="str">
         <v>2026-03-31</v>
@@ -691,16 +691,16 @@
         <v>215</v>
       </c>
       <c r="B8" t="str">
-        <v>TU Darmstadt ImpSec</v>
+        <v>TU Darmstadt System Security Lab</v>
       </c>
       <c r="C8" t="str">
         <v>Researching</v>
       </c>
       <c r="D8" t="str">
-        <v>2026 Summer | Implementation security chair focused on side-channel and fault attacks, ASICs, FPGAs, and microprocessor security. Initiative application.</v>
+        <v>2026 Summer | Hardware-assisted security lab covering secure processors, IoT security, and practical system hardening. Initiative application.</v>
       </c>
       <c r="E8" t="str">
-        <v>https://www.informatik.tu-darmstadt.de/impsec/start_impsec/index.en.jsp</v>
+        <v>https://www.informatik.tu-darmstadt.de/systemsecurity/system_security_lab_sys/index.en.jsp</v>
       </c>
       <c r="F8" t="str">
         <v>Darmstadt, DE</v>
@@ -718,7 +718,7 @@
         <v>High</v>
       </c>
       <c r="K8" t="str">
-        <v>Hardware,Security,Embedded,Firmware,Systems</v>
+        <v>Security,Hardware,Embedded,IoT,Systems</v>
       </c>
       <c r="L8" t="str">
         <v>2026-03-31</v>
@@ -732,22 +732,22 @@
         <v>216</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraunhofer FKIE</v>
+        <v>CASA / Chair for Embedded Security</v>
       </c>
       <c r="C9" t="str">
         <v>Researching</v>
       </c>
       <c r="D9" t="str">
-        <v>2026 Summer | Applied security institute doing firmware reverse engineering, vulnerability analysis, and embedded-device forensics. Initiative application.</v>
+        <v>2026 Summer | Embedded security chair focused on secure chips, cryptographic implementations, and side-channel or fault analysis. Initiative application.</v>
       </c>
       <c r="E9" t="str">
-        <v>https://www.fkie.fraunhofer.de/en.html</v>
+        <v>https://casa.rub.de/en/</v>
       </c>
       <c r="F9" t="str">
-        <v>Bonn, DE</v>
+        <v>Bochum, DE</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -759,7 +759,7 @@
         <v>High</v>
       </c>
       <c r="K9" t="str">
-        <v>Firmware,Security,Embedded,Systems,Hardware</v>
+        <v>Hardware,Embedded,Security,Firmware,Systems</v>
       </c>
       <c r="L9" t="str">
         <v>2026-03-31</v>
@@ -773,22 +773,22 @@
         <v>217</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraunhofer IIS</v>
+        <v>TU Berlin SecT</v>
       </c>
       <c r="C10" t="str">
         <v>Researching</v>
       </c>
       <c r="D10" t="str">
-        <v>2026 Summer | Secure system-on-chip research around secure RISC-V, secure boot, firmware updates, and crypto accelerators. Initiative application.</v>
+        <v>2026 Summer | Security in Telecommunications chair covering hardware security, secure embedded systems, and side-channel attacks. Initiative application.</v>
       </c>
       <c r="E10" t="str">
-        <v>https://www.iis.fraunhofer.de/en.html</v>
+        <v>https://www.tu.berlin/en/sect</v>
       </c>
       <c r="F10" t="str">
-        <v>Erlangen, DE</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -800,7 +800,7 @@
         <v>High</v>
       </c>
       <c r="K10" t="str">
-        <v>Hardware,Embedded,Firmware,Security,Systems</v>
+        <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
       <c r="L10" t="str">
         <v>2026-03-31</v>
@@ -814,22 +814,22 @@
         <v>218</v>
       </c>
       <c r="B11" t="str">
-        <v>Fraunhofer IPMS</v>
+        <v>ETH Zurich COMSEC</v>
       </c>
       <c r="C11" t="str">
         <v>Researching</v>
       </c>
       <c r="D11" t="str">
-        <v>2026 Summer | Trusted electronics work on secure manufacturing, PUF trust anchors, encrypted firmware, and secure embedded devices. Initiative application.</v>
+        <v>2026 Summer | Computer security group doing hardware-bound attack and defense research with open thesis-style student pathways. Initiative application.</v>
       </c>
       <c r="E11" t="str">
-        <v>https://www.ipms.fraunhofer.de/en.html</v>
+        <v>https://comsec.ethz.ch/</v>
       </c>
       <c r="F11" t="str">
-        <v>Dresden, DE</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -841,7 +841,7 @@
         <v>High</v>
       </c>
       <c r="K11" t="str">
-        <v>Hardware,Embedded,Firmware,Security,Systems</v>
+        <v>Security,Hardware,Systems,Embedded,Firmware</v>
       </c>
       <c r="L11" t="str">
         <v>2026-03-31</v>
@@ -937,19 +937,19 @@
         <v>221</v>
       </c>
       <c r="B14" t="str">
-        <v>RWTH Aachen ICE</v>
+        <v>Fraunhofer FKIE</v>
       </c>
       <c r="C14" t="str">
         <v>Researching</v>
       </c>
       <c r="D14" t="str">
-        <v>2026 Summer | Systems-on-silicon chair working on SoC design, virtual prototyping, and embedded cybersecurity-adjacent research. Initiative application.</v>
+        <v>2026 Summer | Applied security institute doing firmware reverse engineering, vulnerability analysis, and embedded-device forensics. Initiative application.</v>
       </c>
       <c r="E14" t="str">
-        <v>https://www.ice.rwth-aachen.de/</v>
+        <v>https://www.fkie.fraunhofer.de/en.html</v>
       </c>
       <c r="F14" t="str">
-        <v>Aachen, DE</v>
+        <v>Bonn, DE</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -964,7 +964,7 @@
         <v>High</v>
       </c>
       <c r="K14" t="str">
-        <v>Embedded,Hardware,Systems,Security,Firmware</v>
+        <v>Firmware,Security,Embedded,Systems,Hardware</v>
       </c>
       <c r="L14" t="str">
         <v>2026-03-31</v>
@@ -978,19 +978,19 @@
         <v>222</v>
       </c>
       <c r="B15" t="str">
-        <v>TU Darmstadt SEEMOO</v>
+        <v>TUM Embedded Systems and IoT</v>
       </c>
       <c r="C15" t="str">
         <v>Researching</v>
       </c>
       <c r="D15" t="str">
-        <v>2026 Summer | Secure mobile networking lab with hands-on IoT, wireless security, and resilient embedded prototype work. Initiative application.</v>
+        <v>2026 Summer | Embedded systems chair focused on secure and reliable cyber-physical, autonomous, and IoT platforms. Initiative application.</v>
       </c>
       <c r="E15" t="str">
-        <v>https://www.seemoo.tu-darmstadt.de/</v>
+        <v>https://www.ce.cit.tum.de/en/esi/staff/steinhorst/</v>
       </c>
       <c r="F15" t="str">
-        <v>Darmstadt, DE</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G15">
         <v>4</v>
@@ -1005,7 +1005,7 @@
         <v>High</v>
       </c>
       <c r="K15" t="str">
-        <v>IoT,Security,Embedded,Systems,Firmware</v>
+        <v>Embedded,IoT,Systems,Security,Hardware</v>
       </c>
       <c r="L15" t="str">
         <v>2026-03-31</v>
@@ -1019,19 +1019,19 @@
         <v>223</v>
       </c>
       <c r="B16" t="str">
-        <v>TUM Embedded Systems and IoT</v>
+        <v>TU Eindhoven Security Group</v>
       </c>
       <c r="C16" t="str">
         <v>Researching</v>
       </c>
       <c r="D16" t="str">
-        <v>2026 Summer | Embedded systems chair focused on secure and reliable cyber-physical, autonomous, and IoT platforms. Initiative application.</v>
+        <v>2026 Summer | Security group researching embedded systems security, PUFs, and smart-card side-channel topics. Initiative application.</v>
       </c>
       <c r="E16" t="str">
-        <v>https://www.ce.cit.tum.de/en/esi/staff/steinhorst/</v>
+        <v>https://research.tue.nl/en/organisations/security</v>
       </c>
       <c r="F16" t="str">
-        <v>Munich, DE</v>
+        <v>Eindhoven, NL</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -1046,7 +1046,7 @@
         <v>High</v>
       </c>
       <c r="K16" t="str">
-        <v>Embedded,IoT,Systems,Security,Hardware</v>
+        <v>Security,Hardware,Embedded,Systems,Firmware</v>
       </c>
       <c r="L16" t="str">
         <v>2026-03-31</v>

--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -442,25 +442,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B2" t="str">
-        <v>Fraunhofer SIT</v>
+        <v>TU Eindhoven Security Group</v>
       </c>
       <c r="C2" t="str">
         <v>Researching</v>
       </c>
       <c r="D2" t="str">
-        <v>2026 Summer | Embedded and IoT security institute working on protocol security, trusted computing, and secure firmware updates. Initiative application.</v>
+        <v>2026 Summer | Security group researching embedded systems security, PUFs, and smart-card side-channel topics. Initiative application.</v>
       </c>
       <c r="E2" t="str">
-        <v>https://www.sit.fraunhofer.de/en/</v>
+        <v>https://research.tue.nl/en/organisations/security</v>
       </c>
       <c r="F2" t="str">
-        <v>Darmstadt, DE</v>
+        <v>Eindhoven, NL</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -472,7 +472,7 @@
         <v>High</v>
       </c>
       <c r="K2" t="str">
-        <v>Embedded,Firmware,Security,IoT,Systems</v>
+        <v>Security,Hardware,Embedded,Systems,Firmware</v>
       </c>
       <c r="L2" t="str">
         <v>2026-03-31</v>
@@ -483,25 +483,25 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B3" t="str">
-        <v>Fraunhofer EMFT</v>
+        <v>TUM Embedded Systems and IoT</v>
       </c>
       <c r="C3" t="str">
         <v>Researching</v>
       </c>
       <c r="D3" t="str">
-        <v>2026 Summer | Trusted electronics team focused on tamper protection, PUF-based key generation, and secure IoT hardware. Initiative application.</v>
+        <v>2026 Summer | Embedded systems chair focused on secure and reliable cyber-physical, autonomous, and IoT platforms. Initiative application.</v>
       </c>
       <c r="E3" t="str">
-        <v>https://www.emft.fraunhofer.de/en.html</v>
+        <v>https://www.ce.cit.tum.de/en/esi/staff/steinhorst/</v>
       </c>
       <c r="F3" t="str">
         <v>Munich, DE</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -513,7 +513,7 @@
         <v>High</v>
       </c>
       <c r="K3" t="str">
-        <v>Hardware,Embedded,Security,IoT,Firmware</v>
+        <v>Embedded,IoT,Systems,Security,Hardware</v>
       </c>
       <c r="L3" t="str">
         <v>2026-03-31</v>
@@ -524,25 +524,25 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B4" t="str">
-        <v>Fraunhofer IMS</v>
+        <v>Fraunhofer FKIE</v>
       </c>
       <c r="C4" t="str">
         <v>Researching</v>
       </c>
       <c r="D4" t="str">
-        <v>2026 Summer | Trusted electronics group researching secure key memory, PUFs, encrypted firmware storage, and secure RISC-V cores. Initiative application.</v>
+        <v>2026 Summer | Applied security institute doing firmware reverse engineering, vulnerability analysis, and embedded-device forensics. Initiative application.</v>
       </c>
       <c r="E4" t="str">
-        <v>https://www.ims.fraunhofer.de/en.html</v>
+        <v>https://www.fkie.fraunhofer.de/en.html</v>
       </c>
       <c r="F4" t="str">
-        <v>Duisburg, DE</v>
+        <v>Bonn, DE</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -554,7 +554,7 @@
         <v>High</v>
       </c>
       <c r="K4" t="str">
-        <v>Hardware,Embedded,Firmware,Security,Systems</v>
+        <v>Firmware,Security,Embedded,Systems,Hardware</v>
       </c>
       <c r="L4" t="str">
         <v>2026-03-31</v>
@@ -565,25 +565,25 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B5" t="str">
-        <v>TUM Chair of IT Security</v>
+        <v>AIT Center for Digital Safety &amp; Security</v>
       </c>
       <c r="C5" t="str">
         <v>Researching</v>
       </c>
       <c r="D5" t="str">
-        <v>2026 Summer | University chair with a strong hardware and embedded security track plus thesis and student project intake. Initiative application.</v>
+        <v>2026 Summer | Applied research center covering secure IoT, industrial control systems, dependable systems, and wireless security. Initiative application.</v>
       </c>
       <c r="E5" t="str">
-        <v>https://www.sec.in.tum.de/i20/</v>
+        <v>https://www.ait.ac.at/en/about-the-ait/center/center-for-digital-safety-security/</v>
       </c>
       <c r="F5" t="str">
-        <v>Munich, DE</v>
+        <v>Vienna, AT</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -595,7 +595,7 @@
         <v>High</v>
       </c>
       <c r="K5" t="str">
-        <v>Security,Hardware,Embedded,Firmware,Systems</v>
+        <v>Security,IoT,Systems,Embedded,Hardware</v>
       </c>
       <c r="L5" t="str">
         <v>2026-03-31</v>
@@ -606,25 +606,25 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B6" t="str">
-        <v>KIT Chair of Dependable Nano Computing (CDNC)</v>
+        <v>CARIAD Information and Automotive Security</v>
       </c>
       <c r="C6" t="str">
         <v>Researching</v>
       </c>
       <c r="D6" t="str">
-        <v>2026 Summer | Hardware security lab known for FPGA side-channel and fault-attack research with active student thesis opportunities. Initiative application.</v>
+        <v>2026 Summer | Automotive security organization covering OTA, digital keys, connected vehicles, and end-to-end platform security. Initiative application.</v>
       </c>
       <c r="E6" t="str">
-        <v>https://cdnc.itec.kit.edu/</v>
+        <v>https://cariad.technology/de/en/</v>
       </c>
       <c r="F6" t="str">
-        <v>Karlsruhe, DE</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -636,7 +636,7 @@
         <v>High</v>
       </c>
       <c r="K6" t="str">
-        <v>Hardware,Security,Embedded,Systems,Firmware</v>
+        <v>Security,Embedded,Firmware,Systems,IoT</v>
       </c>
       <c r="L6" t="str">
         <v>2026-03-31</v>
@@ -647,25 +647,25 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B7" t="str">
-        <v>TU Darmstadt ImpSec</v>
+        <v>ETH Zurich COMSEC</v>
       </c>
       <c r="C7" t="str">
         <v>Researching</v>
       </c>
       <c r="D7" t="str">
-        <v>2026 Summer | Implementation security chair focused on side-channel and fault attacks, ASICs, FPGAs, and microprocessor security. Initiative application.</v>
+        <v>2026 Summer | Computer security group doing hardware-bound attack and defense research with open thesis-style student pathways. Initiative application.</v>
       </c>
       <c r="E7" t="str">
-        <v>https://www.informatik.tu-darmstadt.de/impsec/start_impsec/index.en.jsp</v>
+        <v>https://comsec.ethz.ch/</v>
       </c>
       <c r="F7" t="str">
-        <v>Darmstadt, DE</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -677,7 +677,7 @@
         <v>High</v>
       </c>
       <c r="K7" t="str">
-        <v>Hardware,Security,Embedded,Firmware,Systems</v>
+        <v>Security,Hardware,Systems,Embedded,Firmware</v>
       </c>
       <c r="L7" t="str">
         <v>2026-03-31</v>
@@ -688,25 +688,25 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B8" t="str">
-        <v>TU Darmstadt System Security Lab</v>
+        <v>TU Berlin SecT</v>
       </c>
       <c r="C8" t="str">
         <v>Researching</v>
       </c>
       <c r="D8" t="str">
-        <v>2026 Summer | Hardware-assisted security lab covering secure processors, IoT security, and practical system hardening. Initiative application.</v>
+        <v>2026 Summer | Security in Telecommunications chair covering hardware security, secure embedded systems, and side-channel attacks. Initiative application.</v>
       </c>
       <c r="E8" t="str">
-        <v>https://www.informatik.tu-darmstadt.de/systemsecurity/system_security_lab_sys/index.en.jsp</v>
+        <v>https://www.tu.berlin/en/sect</v>
       </c>
       <c r="F8" t="str">
-        <v>Darmstadt, DE</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -718,7 +718,7 @@
         <v>High</v>
       </c>
       <c r="K8" t="str">
-        <v>Security,Hardware,Embedded,IoT,Systems</v>
+        <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
       <c r="L8" t="str">
         <v>2026-03-31</v>
@@ -747,7 +747,7 @@
         <v>Bochum, DE</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -770,25 +770,25 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B10" t="str">
-        <v>TU Berlin SecT</v>
+        <v>TU Darmstadt System Security Lab</v>
       </c>
       <c r="C10" t="str">
         <v>Researching</v>
       </c>
       <c r="D10" t="str">
-        <v>2026 Summer | Security in Telecommunications chair covering hardware security, secure embedded systems, and side-channel attacks. Initiative application.</v>
+        <v>2026 Summer | Hardware-assisted security lab covering secure processors, IoT security, and practical system hardening. Initiative application.</v>
       </c>
       <c r="E10" t="str">
-        <v>https://www.tu.berlin/en/sect</v>
+        <v>https://www.informatik.tu-darmstadt.de/systemsecurity/system_security_lab_sys/index.en.jsp</v>
       </c>
       <c r="F10" t="str">
-        <v>Berlin, DE</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -800,7 +800,7 @@
         <v>High</v>
       </c>
       <c r="K10" t="str">
-        <v>Security,Hardware,Embedded,Firmware,Systems</v>
+        <v>Security,Hardware,Embedded,IoT,Systems</v>
       </c>
       <c r="L10" t="str">
         <v>2026-03-31</v>
@@ -811,25 +811,25 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B11" t="str">
-        <v>ETH Zurich COMSEC</v>
+        <v>TU Darmstadt ImpSec</v>
       </c>
       <c r="C11" t="str">
         <v>Researching</v>
       </c>
       <c r="D11" t="str">
-        <v>2026 Summer | Computer security group doing hardware-bound attack and defense research with open thesis-style student pathways. Initiative application.</v>
+        <v>2026 Summer | Implementation security chair focused on side-channel and fault attacks, ASICs, FPGAs, and microprocessor security. Initiative application.</v>
       </c>
       <c r="E11" t="str">
-        <v>https://comsec.ethz.ch/</v>
+        <v>https://www.informatik.tu-darmstadt.de/impsec/start_impsec/index.en.jsp</v>
       </c>
       <c r="F11" t="str">
-        <v>Zurich, CH</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -841,7 +841,7 @@
         <v>High</v>
       </c>
       <c r="K11" t="str">
-        <v>Security,Hardware,Systems,Embedded,Firmware</v>
+        <v>Hardware,Security,Embedded,Firmware,Systems</v>
       </c>
       <c r="L11" t="str">
         <v>2026-03-31</v>
@@ -852,25 +852,25 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B12" t="str">
-        <v>CARIAD Information and Automotive Security</v>
+        <v>KIT Chair of Dependable Nano Computing (CDNC)</v>
       </c>
       <c r="C12" t="str">
         <v>Researching</v>
       </c>
       <c r="D12" t="str">
-        <v>2026 Summer | Automotive security organization covering OTA, digital keys, connected vehicles, and end-to-end platform security. Initiative application.</v>
+        <v>2026 Summer | Hardware security lab known for FPGA side-channel and fault-attack research with active student thesis opportunities. Initiative application.</v>
       </c>
       <c r="E12" t="str">
-        <v>https://cariad.technology/de/en/</v>
+        <v>https://cdnc.itec.kit.edu/</v>
       </c>
       <c r="F12" t="str">
-        <v>Berlin, DE</v>
+        <v>Karlsruhe, DE</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -882,7 +882,7 @@
         <v>High</v>
       </c>
       <c r="K12" t="str">
-        <v>Security,Embedded,Firmware,Systems,IoT</v>
+        <v>Hardware,Security,Embedded,Systems,Firmware</v>
       </c>
       <c r="L12" t="str">
         <v>2026-03-31</v>
@@ -893,25 +893,25 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B13" t="str">
-        <v>AIT Center for Digital Safety &amp; Security</v>
+        <v>TUM Chair of IT Security</v>
       </c>
       <c r="C13" t="str">
         <v>Researching</v>
       </c>
       <c r="D13" t="str">
-        <v>2026 Summer | Applied research center covering secure IoT, industrial control systems, dependable systems, and wireless security. Initiative application.</v>
+        <v>2026 Summer | University chair with a strong hardware and embedded security track plus thesis and student project intake. Initiative application.</v>
       </c>
       <c r="E13" t="str">
-        <v>https://www.ait.ac.at/en/about-the-ait/center/center-for-digital-safety-security/</v>
+        <v>https://www.sec.in.tum.de/i20/</v>
       </c>
       <c r="F13" t="str">
-        <v>Vienna, AT</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -923,7 +923,7 @@
         <v>High</v>
       </c>
       <c r="K13" t="str">
-        <v>Security,IoT,Systems,Embedded,Hardware</v>
+        <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
       <c r="L13" t="str">
         <v>2026-03-31</v>
@@ -934,25 +934,25 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B14" t="str">
-        <v>Fraunhofer FKIE</v>
+        <v>Fraunhofer IMS</v>
       </c>
       <c r="C14" t="str">
         <v>Researching</v>
       </c>
       <c r="D14" t="str">
-        <v>2026 Summer | Applied security institute doing firmware reverse engineering, vulnerability analysis, and embedded-device forensics. Initiative application.</v>
+        <v>2026 Summer | Trusted electronics group researching secure key memory, PUFs, encrypted firmware storage, and secure RISC-V cores. Initiative application.</v>
       </c>
       <c r="E14" t="str">
-        <v>https://www.fkie.fraunhofer.de/en.html</v>
+        <v>https://www.ims.fraunhofer.de/en.html</v>
       </c>
       <c r="F14" t="str">
-        <v>Bonn, DE</v>
+        <v>Duisburg, DE</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -964,7 +964,7 @@
         <v>High</v>
       </c>
       <c r="K14" t="str">
-        <v>Firmware,Security,Embedded,Systems,Hardware</v>
+        <v>Hardware,Embedded,Firmware,Security,Systems</v>
       </c>
       <c r="L14" t="str">
         <v>2026-03-31</v>
@@ -975,25 +975,25 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B15" t="str">
-        <v>TUM Embedded Systems and IoT</v>
+        <v>Fraunhofer EMFT</v>
       </c>
       <c r="C15" t="str">
         <v>Researching</v>
       </c>
       <c r="D15" t="str">
-        <v>2026 Summer | Embedded systems chair focused on secure and reliable cyber-physical, autonomous, and IoT platforms. Initiative application.</v>
+        <v>2026 Summer | Trusted electronics team focused on tamper protection, PUF-based key generation, and secure IoT hardware. Initiative application.</v>
       </c>
       <c r="E15" t="str">
-        <v>https://www.ce.cit.tum.de/en/esi/staff/steinhorst/</v>
+        <v>https://www.emft.fraunhofer.de/en.html</v>
       </c>
       <c r="F15" t="str">
         <v>Munich, DE</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1005,7 +1005,7 @@
         <v>High</v>
       </c>
       <c r="K15" t="str">
-        <v>Embedded,IoT,Systems,Security,Hardware</v>
+        <v>Hardware,Embedded,Security,IoT,Firmware</v>
       </c>
       <c r="L15" t="str">
         <v>2026-03-31</v>
@@ -1016,25 +1016,25 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B16" t="str">
-        <v>TU Eindhoven Security Group</v>
+        <v>Fraunhofer SIT</v>
       </c>
       <c r="C16" t="str">
         <v>Researching</v>
       </c>
       <c r="D16" t="str">
-        <v>2026 Summer | Security group researching embedded systems security, PUFs, and smart-card side-channel topics. Initiative application.</v>
+        <v>2026 Summer | Embedded and IoT security institute working on protocol security, trusted computing, and secure firmware updates. Initiative application.</v>
       </c>
       <c r="E16" t="str">
-        <v>https://research.tue.nl/en/organisations/security</v>
+        <v>https://www.sit.fraunhofer.de/en/</v>
       </c>
       <c r="F16" t="str">
-        <v>Eindhoven, NL</v>
+        <v>Darmstadt, DE</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1046,7 +1046,7 @@
         <v>High</v>
       </c>
       <c r="K16" t="str">
-        <v>Security,Hardware,Embedded,Systems,Firmware</v>
+        <v>Embedded,Firmware,Security,IoT,Systems</v>
       </c>
       <c r="L16" t="str">
         <v>2026-03-31</v>

--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M224"/>
+  <dimension ref="A1:O224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -428,15 +428,21 @@
         <v>Follow-up At</v>
       </c>
       <c r="J1" t="str">
+        <v>Reply Received At</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Reply Outcome</v>
+      </c>
+      <c r="L1" t="str">
         <v>Priority</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Focus Tags</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>Created At</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>Updated At</v>
       </c>
     </row>
@@ -469,15 +475,21 @@
         <v/>
       </c>
       <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>High</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>Security,Hardware,Embedded,Systems,Firmware</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -510,15 +522,21 @@
         <v/>
       </c>
       <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>High</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>Embedded,IoT,Systems,Security,Hardware</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -551,15 +569,21 @@
         <v/>
       </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>High</v>
       </c>
-      <c r="K4" t="str">
+      <c r="M4" t="str">
         <v>Firmware,Security,Embedded,Systems,Hardware</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -592,15 +616,21 @@
         <v/>
       </c>
       <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>High</v>
       </c>
-      <c r="K5" t="str">
+      <c r="M5" t="str">
         <v>Security,IoT,Systems,Embedded,Hardware</v>
       </c>
-      <c r="L5" t="str">
+      <c r="N5" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M5" t="str">
+      <c r="O5" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -633,15 +663,21 @@
         <v/>
       </c>
       <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>High</v>
       </c>
-      <c r="K6" t="str">
+      <c r="M6" t="str">
         <v>Security,Embedded,Firmware,Systems,IoT</v>
       </c>
-      <c r="L6" t="str">
+      <c r="N6" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M6" t="str">
+      <c r="O6" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -674,15 +710,21 @@
         <v/>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>High</v>
       </c>
-      <c r="K7" t="str">
+      <c r="M7" t="str">
         <v>Security,Hardware,Systems,Embedded,Firmware</v>
       </c>
-      <c r="L7" t="str">
+      <c r="N7" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M7" t="str">
+      <c r="O7" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -715,15 +757,21 @@
         <v/>
       </c>
       <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>High</v>
       </c>
-      <c r="K8" t="str">
+      <c r="M8" t="str">
         <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
-      <c r="L8" t="str">
+      <c r="N8" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M8" t="str">
+      <c r="O8" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -756,15 +804,21 @@
         <v/>
       </c>
       <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>High</v>
       </c>
-      <c r="K9" t="str">
+      <c r="M9" t="str">
         <v>Hardware,Embedded,Security,Firmware,Systems</v>
       </c>
-      <c r="L9" t="str">
+      <c r="N9" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M9" t="str">
+      <c r="O9" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -797,15 +851,21 @@
         <v/>
       </c>
       <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>High</v>
       </c>
-      <c r="K10" t="str">
+      <c r="M10" t="str">
         <v>Security,Hardware,Embedded,IoT,Systems</v>
       </c>
-      <c r="L10" t="str">
+      <c r="N10" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M10" t="str">
+      <c r="O10" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -838,15 +898,21 @@
         <v/>
       </c>
       <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>High</v>
       </c>
-      <c r="K11" t="str">
+      <c r="M11" t="str">
         <v>Hardware,Security,Embedded,Firmware,Systems</v>
       </c>
-      <c r="L11" t="str">
+      <c r="N11" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M11" t="str">
+      <c r="O11" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -879,15 +945,21 @@
         <v/>
       </c>
       <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>High</v>
       </c>
-      <c r="K12" t="str">
+      <c r="M12" t="str">
         <v>Hardware,Security,Embedded,Systems,Firmware</v>
       </c>
-      <c r="L12" t="str">
+      <c r="N12" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M12" t="str">
+      <c r="O12" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -920,15 +992,21 @@
         <v/>
       </c>
       <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>High</v>
       </c>
-      <c r="K13" t="str">
+      <c r="M13" t="str">
         <v>Security,Hardware,Embedded,Firmware,Systems</v>
       </c>
-      <c r="L13" t="str">
+      <c r="N13" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M13" t="str">
+      <c r="O13" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -961,15 +1039,21 @@
         <v/>
       </c>
       <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>High</v>
       </c>
-      <c r="K14" t="str">
+      <c r="M14" t="str">
         <v>Hardware,Embedded,Firmware,Security,Systems</v>
       </c>
-      <c r="L14" t="str">
+      <c r="N14" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M14" t="str">
+      <c r="O14" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -1002,15 +1086,21 @@
         <v/>
       </c>
       <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>High</v>
       </c>
-      <c r="K15" t="str">
+      <c r="M15" t="str">
         <v>Hardware,Embedded,Security,IoT,Firmware</v>
       </c>
-      <c r="L15" t="str">
+      <c r="N15" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M15" t="str">
+      <c r="O15" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -1043,15 +1133,21 @@
         <v/>
       </c>
       <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>High</v>
       </c>
-      <c r="K16" t="str">
+      <c r="M16" t="str">
         <v>Embedded,Firmware,Security,IoT,Systems</v>
       </c>
-      <c r="L16" t="str">
+      <c r="N16" t="str">
         <v>2026-03-31</v>
       </c>
-      <c r="M16" t="str">
+      <c r="O16" t="str">
         <v>2026-03-31</v>
       </c>
     </row>
@@ -1084,15 +1180,21 @@
         <v/>
       </c>
       <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>High</v>
       </c>
-      <c r="K17" t="str">
+      <c r="M17" t="str">
         <v>Embedded,Systems,Hardware</v>
       </c>
-      <c r="L17" t="str">
+      <c r="N17" t="str">
         <v>2026-02-04 22:59:49</v>
       </c>
-      <c r="M17" t="str">
+      <c r="O17" t="str">
         <v>2026-03-26 20:11:30</v>
       </c>
     </row>
@@ -1125,15 +1227,21 @@
         <v/>
       </c>
       <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>High</v>
       </c>
-      <c r="K18" t="str">
+      <c r="M18" t="str">
         <v>Embedded,Hardware,IoT</v>
       </c>
-      <c r="L18" t="str">
+      <c r="N18" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M18" t="str">
+      <c r="O18" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1166,15 +1274,21 @@
         <v/>
       </c>
       <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>High</v>
       </c>
-      <c r="K19" t="str">
+      <c r="M19" t="str">
         <v>Embedded,Hardware,Security</v>
       </c>
-      <c r="L19" t="str">
+      <c r="N19" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M19" t="str">
+      <c r="O19" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1207,15 +1321,21 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M20" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L20" t="str">
+      <c r="N20" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M20" t="str">
+      <c r="O20" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1248,15 +1368,21 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M21" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L21" t="str">
+      <c r="N21" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M21" t="str">
+      <c r="O21" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1289,15 +1415,21 @@
         <v/>
       </c>
       <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>High</v>
       </c>
-      <c r="K22" t="str">
+      <c r="M22" t="str">
         <v>Embedded,Hardware,Security</v>
       </c>
-      <c r="L22" t="str">
+      <c r="N22" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M22" t="str">
+      <c r="O22" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1330,15 +1462,21 @@
         <v/>
       </c>
       <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>High</v>
       </c>
-      <c r="K23" t="str">
+      <c r="M23" t="str">
         <v>Embedded,Hardware,Security</v>
       </c>
-      <c r="L23" t="str">
+      <c r="N23" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M23" t="str">
+      <c r="O23" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1371,15 +1509,21 @@
         <v/>
       </c>
       <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>High</v>
       </c>
-      <c r="K24" t="str">
+      <c r="M24" t="str">
         <v>Embedded,Hardware,Systems</v>
       </c>
-      <c r="L24" t="str">
+      <c r="N24" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M24" t="str">
+      <c r="O24" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1412,15 +1556,21 @@
         <v/>
       </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>High</v>
       </c>
-      <c r="K25" t="str">
+      <c r="M25" t="str">
         <v>Embedded,Hardware,Systems</v>
       </c>
-      <c r="L25" t="str">
+      <c r="N25" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M25" t="str">
+      <c r="O25" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1453,15 +1603,21 @@
         <v/>
       </c>
       <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>High</v>
       </c>
-      <c r="K26" t="str">
+      <c r="M26" t="str">
         <v>Systems,Hardware,Embedded</v>
       </c>
-      <c r="L26" t="str">
+      <c r="N26" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
-      <c r="M26" t="str">
+      <c r="O26" t="str">
         <v>2026-02-04 22:56:22</v>
       </c>
     </row>
@@ -1494,15 +1650,21 @@
         <v/>
       </c>
       <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>High</v>
       </c>
-      <c r="K27" t="str">
+      <c r="M27" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L27" t="str">
+      <c r="N27" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
-      <c r="M27" t="str">
+      <c r="O27" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
     </row>
@@ -1535,15 +1697,21 @@
         <v/>
       </c>
       <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>High</v>
       </c>
-      <c r="K28" t="str">
+      <c r="M28" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L28" t="str">
+      <c r="N28" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
-      <c r="M28" t="str">
+      <c r="O28" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
     </row>
@@ -1576,15 +1744,21 @@
         <v/>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>High</v>
       </c>
-      <c r="K29" t="str">
+      <c r="M29" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L29" t="str">
+      <c r="N29" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
-      <c r="M29" t="str">
+      <c r="O29" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
     </row>
@@ -1617,15 +1791,21 @@
         <v/>
       </c>
       <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>High</v>
       </c>
-      <c r="K30" t="str">
+      <c r="M30" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L30" t="str">
+      <c r="N30" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
-      <c r="M30" t="str">
+      <c r="O30" t="str">
         <v>2026-02-04 22:49:45</v>
       </c>
     </row>
@@ -1658,15 +1838,21 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M31" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L31" t="str">
+      <c r="N31" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M31" t="str">
+      <c r="O31" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1699,15 +1885,21 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M32" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L32" t="str">
+      <c r="N32" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M32" t="str">
+      <c r="O32" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1740,15 +1932,21 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M33" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L33" t="str">
+      <c r="N33" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M33" t="str">
+      <c r="O33" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1781,15 +1979,21 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M34" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L34" t="str">
+      <c r="N34" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M34" t="str">
+      <c r="O34" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1822,15 +2026,21 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M35" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L35" t="str">
+      <c r="N35" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M35" t="str">
+      <c r="O35" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1863,15 +2073,21 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M36" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L36" t="str">
+      <c r="N36" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M36" t="str">
+      <c r="O36" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1904,15 +2120,21 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M37" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L37" t="str">
+      <c r="N37" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M37" t="str">
+      <c r="O37" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1945,15 +2167,21 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M38" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L38" t="str">
+      <c r="N38" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M38" t="str">
+      <c r="O38" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -1986,15 +2214,21 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M39" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L39" t="str">
+      <c r="N39" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M39" t="str">
+      <c r="O39" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2027,15 +2261,21 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M40" t="str">
         <v>Security,Systems</v>
       </c>
-      <c r="L40" t="str">
+      <c r="N40" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M40" t="str">
+      <c r="O40" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2068,15 +2308,21 @@
         <v/>
       </c>
       <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v>High</v>
       </c>
-      <c r="K41" t="str">
+      <c r="M41" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L41" t="str">
+      <c r="N41" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M41" t="str">
+      <c r="O41" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2109,15 +2355,21 @@
         <v/>
       </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v>High</v>
       </c>
-      <c r="K42" t="str">
+      <c r="M42" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L42" t="str">
+      <c r="N42" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M42" t="str">
+      <c r="O42" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2150,15 +2402,21 @@
         <v/>
       </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v>High</v>
       </c>
-      <c r="K43" t="str">
+      <c r="M43" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L43" t="str">
+      <c r="N43" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M43" t="str">
+      <c r="O43" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2191,15 +2449,21 @@
         <v/>
       </c>
       <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
         <v>High</v>
       </c>
-      <c r="K44" t="str">
+      <c r="M44" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L44" t="str">
+      <c r="N44" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M44" t="str">
+      <c r="O44" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2232,15 +2496,21 @@
         <v/>
       </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v>High</v>
       </c>
-      <c r="K45" t="str">
+      <c r="M45" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L45" t="str">
+      <c r="N45" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M45" t="str">
+      <c r="O45" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2273,15 +2543,21 @@
         <v/>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v>High</v>
       </c>
-      <c r="K46" t="str">
+      <c r="M46" t="str">
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
-      <c r="L46" t="str">
+      <c r="N46" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
-      <c r="M46" t="str">
+      <c r="O46" t="str">
         <v>2026-02-04 22:48:04</v>
       </c>
     </row>
@@ -2314,15 +2590,21 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M47" t="str">
+      <c r="O47" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2355,15 +2637,21 @@
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K48" t="str">
         <v/>
       </c>
       <c r="L48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M48" t="str">
+      <c r="O48" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2396,15 +2684,21 @@
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K49" t="str">
         <v/>
       </c>
       <c r="L49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M49" t="str">
+      <c r="O49" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2437,15 +2731,21 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K50" t="str">
         <v/>
       </c>
       <c r="L50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M50" t="str">
+      <c r="O50" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2478,15 +2778,21 @@
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K51" t="str">
         <v/>
       </c>
       <c r="L51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M51" t="str">
+      <c r="O51" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2519,15 +2825,21 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K52" t="str">
         <v/>
       </c>
       <c r="L52" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M52" t="str">
+      <c r="O52" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2560,15 +2872,21 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K53" t="str">
         <v/>
       </c>
       <c r="L53" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M53" t="str">
+      <c r="O53" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2601,15 +2919,21 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K54" t="str">
         <v/>
       </c>
       <c r="L54" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M54" t="str">
+      <c r="O54" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2642,15 +2966,21 @@
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K55" t="str">
         <v/>
       </c>
       <c r="L55" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M55" t="str">
+      <c r="O55" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2683,15 +3013,21 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K56" t="str">
         <v/>
       </c>
       <c r="L56" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M56" t="str">
+      <c r="O56" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2724,15 +3060,21 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K57" t="str">
         <v/>
       </c>
       <c r="L57" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M57" t="str">
+      <c r="O57" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2765,15 +3107,21 @@
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K58" t="str">
         <v/>
       </c>
       <c r="L58" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M58" t="str">
+      <c r="O58" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2806,15 +3154,21 @@
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
       <c r="L59" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M59" t="str">
+      <c r="O59" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2847,15 +3201,21 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K60" t="str">
         <v/>
       </c>
       <c r="L60" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M60" t="str">
+      <c r="O60" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2888,15 +3248,21 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K61" t="str">
         <v/>
       </c>
       <c r="L61" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M61" t="str">
+      <c r="O61" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2929,15 +3295,21 @@
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K62" t="str">
         <v/>
       </c>
       <c r="L62" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M62" t="str">
+      <c r="O62" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -2970,15 +3342,21 @@
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K63" t="str">
         <v/>
       </c>
       <c r="L63" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M63" t="str">
+      <c r="O63" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3011,15 +3389,21 @@
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K64" t="str">
         <v/>
       </c>
       <c r="L64" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M64" t="str">
+      <c r="O64" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3052,15 +3436,21 @@
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K65" t="str">
         <v/>
       </c>
       <c r="L65" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M65" t="str">
+      <c r="O65" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3093,15 +3483,21 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K66" t="str">
         <v/>
       </c>
       <c r="L66" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M66" t="str">
+      <c r="O66" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3134,15 +3530,21 @@
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K67" t="str">
         <v/>
       </c>
       <c r="L67" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M67" t="str">
+      <c r="O67" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3175,15 +3577,21 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K68" t="str">
         <v/>
       </c>
       <c r="L68" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M68" t="str">
+      <c r="O68" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3216,15 +3624,21 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K69" t="str">
         <v/>
       </c>
       <c r="L69" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M69" t="str">
+      <c r="O69" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3257,15 +3671,21 @@
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K70" t="str">
         <v/>
       </c>
       <c r="L70" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M70" t="str">
+      <c r="O70" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3298,15 +3718,21 @@
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K71" t="str">
         <v/>
       </c>
       <c r="L71" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
-      <c r="M71" t="str">
+      <c r="O71" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3339,15 +3765,21 @@
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K72" t="str">
         <v/>
       </c>
       <c r="L72" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M72" t="str">
+      <c r="O72" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3380,15 +3812,21 @@
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K73" t="str">
         <v/>
       </c>
       <c r="L73" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M73" t="str">
+      <c r="O73" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3421,15 +3859,21 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K74" t="str">
         <v/>
       </c>
       <c r="L74" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M74" t="str">
+      <c r="O74" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
     </row>
@@ -3462,15 +3906,21 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M75" t="str">
+      <c r="O75" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
     </row>
@@ -3503,15 +3953,21 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K76" t="str">
         <v/>
       </c>
       <c r="L76" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M76" t="str">
+      <c r="O76" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3544,15 +4000,21 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K77" t="str">
         <v/>
       </c>
       <c r="L77" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M77" t="str">
+      <c r="O77" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
     </row>
@@ -3585,15 +4047,21 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K78" t="str">
         <v/>
       </c>
       <c r="L78" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M78" t="str">
+      <c r="O78" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
     </row>
@@ -3626,15 +4094,21 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M79" t="str">
+      <c r="O79" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
     </row>
@@ -3667,15 +4141,21 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K80" t="str">
         <v/>
       </c>
       <c r="L80" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M80" t="str">
+      <c r="O80" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
     </row>
@@ -3708,15 +4188,21 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K81" t="str">
         <v/>
       </c>
       <c r="L81" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
         <v>2026-02-04 16:37:28</v>
       </c>
-      <c r="M81" t="str">
+      <c r="O81" t="str">
         <v>2026-02-04 16:44:49</v>
       </c>
     </row>
@@ -3749,15 +4235,21 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K82" t="str">
         <v/>
       </c>
       <c r="L82" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
         <v>2026-02-04 16:33:31</v>
       </c>
-      <c r="M82" t="str">
+      <c r="O82" t="str">
         <v>2026-02-04 16:33:31</v>
       </c>
     </row>
@@ -3790,15 +4282,21 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K83" t="str">
         <v/>
       </c>
       <c r="L83" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
         <v>2026-02-04 16:33:31</v>
       </c>
-      <c r="M83" t="str">
+      <c r="O83" t="str">
         <v>2026-02-04 16:33:31</v>
       </c>
     </row>
@@ -3831,15 +4329,21 @@
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K84" t="str">
         <v/>
       </c>
       <c r="L84" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
-      <c r="M84" t="str">
+      <c r="O84" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
     </row>
@@ -3872,15 +4376,21 @@
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K85" t="str">
         <v/>
       </c>
       <c r="L85" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
-      <c r="M85" t="str">
+      <c r="O85" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
     </row>
@@ -3913,15 +4423,21 @@
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K86" t="str">
         <v/>
       </c>
       <c r="L86" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
-      <c r="M86" t="str">
+      <c r="O86" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
     </row>
@@ -3954,15 +4470,21 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K87" t="str">
         <v/>
       </c>
       <c r="L87" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
-      <c r="M87" t="str">
+      <c r="O87" t="str">
         <v>2026-02-04 16:32:01</v>
       </c>
     </row>
@@ -3995,15 +4517,21 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K88" t="str">
         <v/>
       </c>
       <c r="L88" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
-      <c r="M88" t="str">
+      <c r="O88" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -4036,15 +4564,21 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K89" t="str">
         <v/>
       </c>
       <c r="L89" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
-      <c r="M89" t="str">
+      <c r="O89" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -4077,15 +4611,21 @@
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K90" t="str">
         <v/>
       </c>
       <c r="L90" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M90" t="str">
+      <c r="O90" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4118,15 +4658,21 @@
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K91" t="str">
         <v/>
       </c>
       <c r="L91" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M91" t="str">
+      <c r="O91" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4159,15 +4705,21 @@
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K92" t="str">
         <v/>
       </c>
       <c r="L92" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M92" t="str">
+      <c r="O92" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4200,15 +4752,21 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K93" t="str">
         <v/>
       </c>
       <c r="L93" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M93" t="str">
+      <c r="O93" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4241,15 +4799,21 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M94" t="str">
+      <c r="O94" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4282,15 +4846,21 @@
         <v/>
       </c>
       <c r="J95" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K95" t="str">
         <v/>
       </c>
       <c r="L95" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M95" t="str">
+      <c r="O95" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4323,15 +4893,21 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K96" t="str">
         <v/>
       </c>
       <c r="L96" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M96" t="str">
+      <c r="O96" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4364,15 +4940,21 @@
         <v/>
       </c>
       <c r="J97" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K97" t="str">
         <v/>
       </c>
       <c r="L97" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M97" t="str">
+      <c r="O97" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4405,15 +4987,21 @@
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
-      <c r="M98" t="str">
+      <c r="O98" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -4446,15 +5034,21 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K99" t="str">
         <v/>
       </c>
       <c r="L99" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M99" t="str">
+      <c r="O99" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4487,15 +5081,21 @@
         <v/>
       </c>
       <c r="J100" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K100" t="str">
         <v/>
       </c>
       <c r="L100" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M100" t="str">
+      <c r="O100" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4528,15 +5128,21 @@
         <v/>
       </c>
       <c r="J101" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K101" t="str">
         <v/>
       </c>
       <c r="L101" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M101" t="str">
+      <c r="O101" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4569,15 +5175,21 @@
         <v/>
       </c>
       <c r="J102" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K102" t="str">
         <v/>
       </c>
       <c r="L102" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M102" t="str">
+      <c r="O102" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4610,15 +5222,21 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K103" t="str">
         <v/>
       </c>
       <c r="L103" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M103" t="str">
+      <c r="O103" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4651,15 +5269,21 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K104" t="str">
         <v/>
       </c>
       <c r="L104" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M104" t="str">
+      <c r="O104" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4692,15 +5316,21 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K105" t="str">
         <v/>
       </c>
       <c r="L105" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M105" t="str">
+      <c r="O105" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4733,15 +5363,21 @@
         <v/>
       </c>
       <c r="J106" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K106" t="str">
         <v/>
       </c>
       <c r="L106" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M106" t="str">
+      <c r="O106" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4774,15 +5410,21 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K107" t="str">
         <v/>
       </c>
       <c r="L107" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M107" t="str">
+      <c r="O107" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4815,15 +5457,21 @@
         <v/>
       </c>
       <c r="J108" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K108" t="str">
         <v/>
       </c>
       <c r="L108" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M108" t="str">
+      <c r="O108" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4856,15 +5504,21 @@
         <v/>
       </c>
       <c r="J109" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K109" t="str">
         <v/>
       </c>
       <c r="L109" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
-      <c r="M109" t="str">
+      <c r="O109" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4897,15 +5551,21 @@
         <v/>
       </c>
       <c r="J110" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K110" t="str">
         <v/>
       </c>
       <c r="L110" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M110" t="str">
+      <c r="O110" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4938,15 +5598,21 @@
         <v/>
       </c>
       <c r="J111" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K111" t="str">
         <v/>
       </c>
       <c r="L111" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M111" t="str">
+      <c r="O111" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -4979,15 +5645,21 @@
         <v/>
       </c>
       <c r="J112" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K112" t="str">
         <v/>
       </c>
       <c r="L112" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M112" t="str">
+      <c r="O112" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5020,15 +5692,21 @@
         <v/>
       </c>
       <c r="J113" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K113" t="str">
         <v/>
       </c>
       <c r="L113" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M113" t="str">
+      <c r="O113" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5061,15 +5739,21 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K114" t="str">
         <v/>
       </c>
       <c r="L114" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M114" t="str">
+      <c r="O114" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5102,15 +5786,21 @@
         <v/>
       </c>
       <c r="J115" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K115" t="str">
         <v/>
       </c>
       <c r="L115" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M115" t="str">
+      <c r="O115" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5143,15 +5833,21 @@
         <v/>
       </c>
       <c r="J116" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K116" t="str">
         <v/>
       </c>
       <c r="L116" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M116" t="str">
+      <c r="O116" t="str">
         <v>2026-02-04 16:17:32</v>
       </c>
     </row>
@@ -5184,15 +5880,21 @@
         <v/>
       </c>
       <c r="J117" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K117" t="str">
         <v/>
       </c>
       <c r="L117" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M117" t="str">
+      <c r="O117" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5225,15 +5927,21 @@
         <v/>
       </c>
       <c r="J118" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K118" t="str">
         <v/>
       </c>
       <c r="L118" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M118" t="str">
+      <c r="O118" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5266,15 +5974,21 @@
         <v/>
       </c>
       <c r="J119" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K119" t="str">
         <v/>
       </c>
       <c r="L119" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M119" t="str">
+      <c r="O119" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5307,15 +6021,21 @@
         <v/>
       </c>
       <c r="J120" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K120" t="str">
         <v/>
       </c>
       <c r="L120" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M120" t="str">
+      <c r="O120" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5348,15 +6068,21 @@
         <v/>
       </c>
       <c r="J121" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K121" t="str">
         <v/>
       </c>
       <c r="L121" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M121" t="str">
+      <c r="O121" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5389,15 +6115,21 @@
         <v/>
       </c>
       <c r="J122" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K122" t="str">
         <v/>
       </c>
       <c r="L122" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
         <v>2026-02-04 16:05:17</v>
       </c>
-      <c r="M122" t="str">
+      <c r="O122" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5430,15 +6162,21 @@
         <v/>
       </c>
       <c r="J123" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K123" t="str">
         <v/>
       </c>
       <c r="L123" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O123" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5471,15 +6209,21 @@
         <v/>
       </c>
       <c r="J124" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K124" t="str">
         <v/>
       </c>
       <c r="L124" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O124" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5512,15 +6256,21 @@
         <v/>
       </c>
       <c r="J125" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K125" t="str">
         <v/>
       </c>
       <c r="L125" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O125" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5553,15 +6303,21 @@
         <v/>
       </c>
       <c r="J126" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K126" t="str">
         <v/>
       </c>
       <c r="L126" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O126" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5594,15 +6350,21 @@
         <v/>
       </c>
       <c r="J127" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K127" t="str">
         <v/>
       </c>
       <c r="L127" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O127" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5635,15 +6397,21 @@
         <v/>
       </c>
       <c r="J128" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K128" t="str">
         <v/>
       </c>
       <c r="L128" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O128" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5676,15 +6444,21 @@
         <v/>
       </c>
       <c r="J129" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K129" t="str">
         <v/>
       </c>
       <c r="L129" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O129" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5717,15 +6491,21 @@
         <v/>
       </c>
       <c r="J130" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K130" t="str">
         <v/>
       </c>
       <c r="L130" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O130" t="str">
         <v>2026-02-04 16:14:09</v>
       </c>
     </row>
@@ -5758,15 +6538,21 @@
         <v/>
       </c>
       <c r="J131" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K131" t="str">
         <v/>
       </c>
       <c r="L131" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O131" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5799,15 +6585,21 @@
         <v/>
       </c>
       <c r="J132" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K132" t="str">
         <v/>
       </c>
       <c r="L132" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O132" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5840,15 +6632,21 @@
         <v/>
       </c>
       <c r="J133" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K133" t="str">
         <v/>
       </c>
       <c r="L133" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O133" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5881,15 +6679,21 @@
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K134" t="str">
         <v/>
       </c>
       <c r="L134" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O134" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -5922,15 +6726,21 @@
         <v/>
       </c>
       <c r="J135" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K135" t="str">
         <v/>
       </c>
       <c r="L135" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O135" t="str">
         <v>2026-02-04 15:44:52</v>
       </c>
     </row>
@@ -5963,15 +6773,21 @@
         <v/>
       </c>
       <c r="J136" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K136" t="str">
         <v/>
       </c>
       <c r="L136" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O136" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6004,15 +6820,21 @@
         <v/>
       </c>
       <c r="J137" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K137" t="str">
         <v/>
       </c>
       <c r="L137" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O137" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6045,15 +6867,21 @@
         <v/>
       </c>
       <c r="J138" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K138" t="str">
         <v/>
       </c>
       <c r="L138" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O138" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6086,15 +6914,21 @@
         <v/>
       </c>
       <c r="J139" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K139" t="str">
         <v/>
       </c>
       <c r="L139" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O139" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6127,15 +6961,21 @@
         <v/>
       </c>
       <c r="J140" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K140" t="str">
         <v/>
       </c>
       <c r="L140" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O140" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6168,15 +7008,21 @@
         <v/>
       </c>
       <c r="J141" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K141" t="str">
         <v/>
       </c>
       <c r="L141" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O141" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6209,15 +7055,21 @@
         <v/>
       </c>
       <c r="J142" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K142" t="str">
         <v/>
       </c>
       <c r="L142" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O142" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6250,15 +7102,21 @@
         <v/>
       </c>
       <c r="J143" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K143" t="str">
         <v/>
       </c>
       <c r="L143" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O143" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6291,15 +7149,21 @@
         <v/>
       </c>
       <c r="J144" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K144" t="str">
         <v/>
       </c>
       <c r="L144" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O144" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6332,15 +7196,21 @@
         <v/>
       </c>
       <c r="J145" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K145" t="str">
         <v/>
       </c>
       <c r="L145" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O145" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6373,15 +7243,21 @@
         <v/>
       </c>
       <c r="J146" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K146" t="str">
         <v/>
       </c>
       <c r="L146" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O146" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6414,15 +7290,21 @@
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K147" t="str">
         <v/>
       </c>
       <c r="L147" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O147" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6455,15 +7337,21 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K148" t="str">
         <v/>
       </c>
       <c r="L148" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O148" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6496,15 +7384,21 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K149" t="str">
         <v/>
       </c>
       <c r="L149" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O149" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6537,15 +7431,21 @@
         <v/>
       </c>
       <c r="J150" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K150" t="str">
         <v/>
       </c>
       <c r="L150" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O150" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6578,15 +7478,21 @@
         <v/>
       </c>
       <c r="J151" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K151" t="str">
         <v/>
       </c>
       <c r="L151" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O151" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6619,15 +7525,21 @@
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K152" t="str">
         <v/>
       </c>
       <c r="L152" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O152" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6660,15 +7572,21 @@
         <v/>
       </c>
       <c r="J153" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K153" t="str">
         <v/>
       </c>
       <c r="L153" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O153" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6701,15 +7619,21 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K154" t="str">
         <v/>
       </c>
       <c r="L154" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O154" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6742,15 +7666,21 @@
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K155" t="str">
         <v/>
       </c>
       <c r="L155" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O155" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6783,15 +7713,21 @@
         <v/>
       </c>
       <c r="J156" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K156" t="str">
         <v/>
       </c>
       <c r="L156" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O156" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6824,15 +7760,21 @@
         <v/>
       </c>
       <c r="J157" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K157" t="str">
         <v/>
       </c>
       <c r="L157" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O157" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6865,15 +7807,21 @@
         <v/>
       </c>
       <c r="J158" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K158" t="str">
         <v/>
       </c>
       <c r="L158" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O158" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6906,15 +7854,21 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K159" t="str">
         <v/>
       </c>
       <c r="L159" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O159" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6947,15 +7901,21 @@
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K160" t="str">
         <v/>
       </c>
       <c r="L160" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O160" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -6988,15 +7948,21 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K161" t="str">
         <v/>
       </c>
       <c r="L161" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O161" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7029,15 +7995,21 @@
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K162" t="str">
         <v/>
       </c>
       <c r="L162" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O162" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7070,15 +8042,21 @@
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K163" t="str">
         <v/>
       </c>
       <c r="L163" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O163" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7111,15 +8089,21 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K164" t="str">
         <v/>
       </c>
       <c r="L164" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O164" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7152,15 +8136,21 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K165" t="str">
         <v/>
       </c>
       <c r="L165" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O165" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7193,15 +8183,21 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K166" t="str">
         <v/>
       </c>
       <c r="L166" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O166" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7234,15 +8230,21 @@
         <v/>
       </c>
       <c r="J167" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K167" t="str">
         <v/>
       </c>
       <c r="L167" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O167" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7275,15 +8277,21 @@
         <v/>
       </c>
       <c r="J168" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K168" t="str">
         <v/>
       </c>
       <c r="L168" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O168" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7316,15 +8324,21 @@
         <v/>
       </c>
       <c r="J169" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K169" t="str">
         <v/>
       </c>
       <c r="L169" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O169" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7357,15 +8371,21 @@
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K170" t="str">
         <v/>
       </c>
       <c r="L170" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O170" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7398,15 +8418,21 @@
         <v/>
       </c>
       <c r="J171" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K171" t="str">
         <v/>
       </c>
       <c r="L171" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O171" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7439,15 +8465,21 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K172" t="str">
         <v/>
       </c>
       <c r="L172" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O172" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7480,15 +8512,21 @@
         <v/>
       </c>
       <c r="J173" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K173" t="str">
         <v/>
       </c>
       <c r="L173" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O173" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7521,15 +8559,21 @@
         <v/>
       </c>
       <c r="J174" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K174" t="str">
         <v/>
       </c>
       <c r="L174" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O174" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7562,15 +8606,21 @@
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K175" t="str">
         <v/>
       </c>
       <c r="L175" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O175" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7603,15 +8653,21 @@
         <v/>
       </c>
       <c r="J176" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K176" t="str">
         <v/>
       </c>
       <c r="L176" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O176" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7644,15 +8700,21 @@
         <v/>
       </c>
       <c r="J177" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K177" t="str">
         <v/>
       </c>
       <c r="L177" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O177" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7685,15 +8747,21 @@
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K178" t="str">
         <v/>
       </c>
       <c r="L178" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O178" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7726,15 +8794,21 @@
         <v/>
       </c>
       <c r="J179" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K179" t="str">
         <v/>
       </c>
       <c r="L179" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O179" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7767,15 +8841,21 @@
         <v/>
       </c>
       <c r="J180" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K180" t="str">
         <v/>
       </c>
       <c r="L180" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O180" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7808,15 +8888,21 @@
         <v/>
       </c>
       <c r="J181" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K181" t="str">
         <v/>
       </c>
       <c r="L181" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O181" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7849,15 +8935,21 @@
         <v/>
       </c>
       <c r="J182" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K182" t="str">
         <v/>
       </c>
       <c r="L182" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O182" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7890,15 +8982,21 @@
         <v/>
       </c>
       <c r="J183" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K183" t="str">
         <v/>
       </c>
       <c r="L183" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O183" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7931,15 +9029,21 @@
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K184" t="str">
         <v/>
       </c>
       <c r="L184" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O184" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -7972,15 +9076,21 @@
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K185" t="str">
         <v/>
       </c>
       <c r="L185" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O185" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8013,15 +9123,21 @@
         <v/>
       </c>
       <c r="J186" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K186" t="str">
         <v/>
       </c>
       <c r="L186" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O186" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8054,15 +9170,21 @@
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K187" t="str">
         <v/>
       </c>
       <c r="L187" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O187" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -8095,15 +9217,21 @@
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K188" t="str">
         <v/>
       </c>
       <c r="L188" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O188" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8136,15 +9264,21 @@
         <v/>
       </c>
       <c r="J189" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K189" t="str">
         <v/>
       </c>
       <c r="L189" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O189" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8177,15 +9311,21 @@
         <v/>
       </c>
       <c r="J190" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K190" t="str">
         <v/>
       </c>
       <c r="L190" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O190" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8218,15 +9358,21 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K191" t="str">
         <v/>
       </c>
       <c r="L191" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O191" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8259,15 +9405,21 @@
         <v/>
       </c>
       <c r="J192" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K192" t="str">
         <v/>
       </c>
       <c r="L192" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O192" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8300,15 +9452,21 @@
         <v/>
       </c>
       <c r="J193" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K193" t="str">
         <v/>
       </c>
       <c r="L193" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O193" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8341,15 +9499,21 @@
         <v/>
       </c>
       <c r="J194" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K194" t="str">
         <v/>
       </c>
       <c r="L194" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O194" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8382,15 +9546,21 @@
         <v/>
       </c>
       <c r="J195" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K195" t="str">
         <v/>
       </c>
       <c r="L195" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O195" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8423,15 +9593,21 @@
         <v/>
       </c>
       <c r="J196" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K196" t="str">
         <v/>
       </c>
       <c r="L196" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O196" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8464,15 +9640,21 @@
         <v/>
       </c>
       <c r="J197" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K197" t="str">
         <v/>
       </c>
       <c r="L197" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O197" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8505,15 +9687,21 @@
         <v/>
       </c>
       <c r="J198" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K198" t="str">
         <v/>
       </c>
       <c r="L198" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O198" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8546,15 +9734,21 @@
         <v/>
       </c>
       <c r="J199" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K199" t="str">
         <v/>
       </c>
       <c r="L199" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O199" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8587,15 +9781,21 @@
         <v/>
       </c>
       <c r="J200" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K200" t="str">
         <v/>
       </c>
       <c r="L200" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M200" t="str">
+        <v/>
+      </c>
+      <c r="N200" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O200" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -8628,15 +9828,21 @@
         <v/>
       </c>
       <c r="J201" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K201" t="str">
         <v/>
       </c>
       <c r="L201" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M201" t="str">
+        <v/>
+      </c>
+      <c r="N201" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O201" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8669,15 +9875,21 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K202" t="str">
         <v/>
       </c>
       <c r="L202" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O202" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8710,15 +9922,21 @@
         <v/>
       </c>
       <c r="J203" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K203" t="str">
         <v/>
       </c>
       <c r="L203" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O203" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -8751,15 +9969,21 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K204" t="str">
         <v/>
       </c>
       <c r="L204" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M204" t="str">
+        <v/>
+      </c>
+      <c r="N204" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O204" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -8792,15 +10016,21 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K205" t="str">
         <v/>
       </c>
       <c r="L205" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M205" t="str">
+        <v/>
+      </c>
+      <c r="N205" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O205" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8833,15 +10063,21 @@
         <v/>
       </c>
       <c r="J206" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K206" t="str">
         <v/>
       </c>
       <c r="L206" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M206" t="str">
+        <v/>
+      </c>
+      <c r="N206" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O206" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8874,15 +10110,21 @@
         <v/>
       </c>
       <c r="J207" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K207" t="str">
         <v/>
       </c>
       <c r="L207" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M207" t="str">
+        <v/>
+      </c>
+      <c r="N207" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O207" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -8915,15 +10157,21 @@
         <v/>
       </c>
       <c r="J208" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K208" t="str">
         <v/>
       </c>
       <c r="L208" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M208" t="str">
+        <v/>
+      </c>
+      <c r="N208" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O208" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8956,15 +10204,21 @@
         <v/>
       </c>
       <c r="J209" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K209" t="str">
         <v/>
       </c>
       <c r="L209" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M209" t="str">
+        <v/>
+      </c>
+      <c r="N209" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O209" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -8997,15 +10251,21 @@
         <v/>
       </c>
       <c r="J210" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K210" t="str">
         <v/>
       </c>
       <c r="L210" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M210" t="str">
+        <v/>
+      </c>
+      <c r="N210" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O210" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9038,15 +10298,21 @@
         <v/>
       </c>
       <c r="J211" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K211" t="str">
         <v/>
       </c>
       <c r="L211" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M211" t="str">
+        <v/>
+      </c>
+      <c r="N211" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O211" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -9079,15 +10345,21 @@
         <v/>
       </c>
       <c r="J212" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K212" t="str">
         <v/>
       </c>
       <c r="L212" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M212" t="str">
+        <v/>
+      </c>
+      <c r="N212" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O212" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -9120,15 +10392,21 @@
         <v/>
       </c>
       <c r="J213" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K213" t="str">
         <v/>
       </c>
       <c r="L213" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M213" t="str">
+        <v/>
+      </c>
+      <c r="N213" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O213" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9161,15 +10439,21 @@
         <v/>
       </c>
       <c r="J214" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K214" t="str">
         <v/>
       </c>
       <c r="L214" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M214" t="str">
+        <v/>
+      </c>
+      <c r="N214" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O214" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9202,15 +10486,21 @@
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K215" t="str">
         <v/>
       </c>
       <c r="L215" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M215" t="str">
+        <v/>
+      </c>
+      <c r="N215" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O215" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9243,15 +10533,21 @@
         <v/>
       </c>
       <c r="J216" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K216" t="str">
         <v/>
       </c>
       <c r="L216" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M216" t="str">
+        <v/>
+      </c>
+      <c r="N216" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O216" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9284,15 +10580,21 @@
         <v/>
       </c>
       <c r="J217" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K217" t="str">
         <v/>
       </c>
       <c r="L217" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M217" t="str">
+        <v/>
+      </c>
+      <c r="N217" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O217" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9325,15 +10627,21 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K218" t="str">
         <v/>
       </c>
       <c r="L218" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M218" t="str">
+        <v/>
+      </c>
+      <c r="N218" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O218" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9366,15 +10674,21 @@
         <v/>
       </c>
       <c r="J219" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K219" t="str">
         <v/>
       </c>
       <c r="L219" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M219" t="str">
+        <v/>
+      </c>
+      <c r="N219" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O219" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9407,15 +10721,21 @@
         <v/>
       </c>
       <c r="J220" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K220" t="str">
         <v/>
       </c>
       <c r="L220" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M220" t="str">
+        <v/>
+      </c>
+      <c r="N220" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O220" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9448,15 +10768,21 @@
         <v/>
       </c>
       <c r="J221" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K221" t="str">
         <v/>
       </c>
       <c r="L221" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M221" t="str">
+        <v/>
+      </c>
+      <c r="N221" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O221" t="str">
         <v>2026-02-04 16:19:45</v>
       </c>
     </row>
@@ -9489,15 +10815,21 @@
         <v/>
       </c>
       <c r="J222" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K222" t="str">
         <v/>
       </c>
       <c r="L222" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M222" t="str">
+        <v/>
+      </c>
+      <c r="N222" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O222" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9530,15 +10862,21 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K223" t="str">
         <v/>
       </c>
       <c r="L223" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M223" t="str">
+        <v/>
+      </c>
+      <c r="N223" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O223" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
@@ -9571,21 +10909,27 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v>Medium</v>
+        <v/>
       </c>
       <c r="K224" t="str">
         <v/>
       </c>
       <c r="L224" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>Medium</v>
       </c>
       <c r="M224" t="str">
+        <v/>
+      </c>
+      <c r="N224" t="str">
+        <v>2026-02-04 00:22:37</v>
+      </c>
+      <c r="O224" t="str">
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O224"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/internships.xlsx
+++ b/data/internships.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O224"/>
+  <dimension ref="A1:O209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,25 +448,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B2" t="str">
-        <v>TU Eindhoven Security Group</v>
+        <v>Vestas</v>
       </c>
       <c r="C2" t="str">
-        <v>Researching</v>
+        <v>Applied</v>
       </c>
       <c r="D2" t="str">
-        <v>2026 Summer | Security group researching embedded systems security, PUFs, and smart-card side-channel topics. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ; systems/embedded fit. Initiative application.</v>
       </c>
       <c r="E2" t="str">
-        <v>https://research.tue.nl/en/organisations/security</v>
+        <v>https://www.vestas.com</v>
       </c>
       <c r="F2" t="str">
-        <v>Eindhoven, NL</v>
+        <v>Aarhus, DK</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -484,36 +484,36 @@
         <v>High</v>
       </c>
       <c r="M2" t="str">
-        <v>Security,Hardware,Embedded,Systems,Firmware</v>
+        <v>Embedded,Systems,Hardware</v>
       </c>
       <c r="N2" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:59:49</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-03-31</v>
+        <v>2026-03-26 20:11:30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B3" t="str">
-        <v>TUM Embedded Systems and IoT</v>
+        <v>Nordic Semiconductor</v>
       </c>
       <c r="C3" t="str">
         <v>Researching</v>
       </c>
       <c r="D3" t="str">
-        <v>2026 Summer | Embedded systems chair focused on secure and reliable cyber-physical, autonomous, and IoT platforms. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E3" t="str">
-        <v>https://www.ce.cit.tum.de/en/esi/staff/steinhorst/</v>
+        <v>https://www.nordicsemi.com</v>
       </c>
       <c r="F3" t="str">
-        <v>Munich, DE</v>
+        <v>Trondheim, NO</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -531,36 +531,36 @@
         <v>High</v>
       </c>
       <c r="M3" t="str">
-        <v>Embedded,IoT,Systems,Security,Hardware</v>
+        <v>Embedded,Hardware,IoT</v>
       </c>
       <c r="N3" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B4" t="str">
-        <v>Fraunhofer FKIE</v>
+        <v>Kongsberg Gruppen</v>
       </c>
       <c r="C4" t="str">
         <v>Researching</v>
       </c>
       <c r="D4" t="str">
-        <v>2026 Summer | Applied security institute doing firmware reverse engineering, vulnerability analysis, and embedded-device forensics. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E4" t="str">
-        <v>https://www.fkie.fraunhofer.de/en.html</v>
+        <v>https://www.kongsberg.com</v>
       </c>
       <c r="F4" t="str">
-        <v>Bonn, DE</v>
+        <v>Kongsberg, NO</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -578,36 +578,36 @@
         <v>High</v>
       </c>
       <c r="M4" t="str">
-        <v>Firmware,Security,Embedded,Systems,Hardware</v>
+        <v>Embedded,Hardware,Security</v>
       </c>
       <c r="N4" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B5" t="str">
-        <v>AIT Center for Digital Safety &amp; Security</v>
+        <v>Telia Company</v>
       </c>
       <c r="C5" t="str">
         <v>Researching</v>
       </c>
       <c r="D5" t="str">
-        <v>2026 Summer | Applied research center covering secure IoT, industrial control systems, dependable systems, and wireless security. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E5" t="str">
-        <v>https://www.ait.ac.at/en/about-the-ait/center/center-for-digital-safety-security/</v>
+        <v>https://www.teliacompany.com</v>
       </c>
       <c r="F5" t="str">
-        <v>Vienna, AT</v>
+        <v>Solna, SE</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -622,36 +622,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M5" t="str">
-        <v>Security,IoT,Systems,Embedded,Hardware</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N5" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B6" t="str">
-        <v>CARIAD Information and Automotive Security</v>
+        <v>Telenor</v>
       </c>
       <c r="C6" t="str">
         <v>Researching</v>
       </c>
       <c r="D6" t="str">
-        <v>2026 Summer | Automotive security organization covering OTA, digital keys, connected vehicles, and end-to-end platform security. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E6" t="str">
-        <v>https://cariad.technology/de/en/</v>
+        <v>https://www.telenor.com</v>
       </c>
       <c r="F6" t="str">
-        <v>Berlin, DE</v>
+        <v>Fornebu, NO</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -669,36 +669,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M6" t="str">
-        <v>Security,Embedded,Firmware,Systems,IoT</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N6" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B7" t="str">
-        <v>ETH Zurich COMSEC</v>
+        <v>Axis Communications</v>
       </c>
       <c r="C7" t="str">
         <v>Researching</v>
       </c>
       <c r="D7" t="str">
-        <v>2026 Summer | Computer security group doing hardware-bound attack and defense research with open thesis-style student pathways. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E7" t="str">
-        <v>https://comsec.ethz.ch/</v>
+        <v>https://www.axis.com</v>
       </c>
       <c r="F7" t="str">
-        <v>Zurich, CH</v>
+        <v>Lund, SE</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -719,36 +719,36 @@
         <v>High</v>
       </c>
       <c r="M7" t="str">
-        <v>Security,Hardware,Systems,Embedded,Firmware</v>
+        <v>Embedded,Hardware,Security</v>
       </c>
       <c r="N7" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B8" t="str">
-        <v>TU Berlin SecT</v>
+        <v>Saab</v>
       </c>
       <c r="C8" t="str">
         <v>Researching</v>
       </c>
       <c r="D8" t="str">
-        <v>2026 Summer | Security in Telecommunications chair covering hardware security, secure embedded systems, and side-channel attacks. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E8" t="str">
-        <v>https://www.tu.berlin/en/sect</v>
+        <v>https://www.saab.com</v>
       </c>
       <c r="F8" t="str">
-        <v>Berlin, DE</v>
+        <v>Stockholm, SE</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -766,36 +766,36 @@
         <v>High</v>
       </c>
       <c r="M8" t="str">
-        <v>Security,Hardware,Embedded,Firmware,Systems</v>
+        <v>Embedded,Hardware,Security</v>
       </c>
       <c r="N8" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B9" t="str">
-        <v>CASA / Chair for Embedded Security</v>
+        <v>Scania</v>
       </c>
       <c r="C9" t="str">
         <v>Researching</v>
       </c>
       <c r="D9" t="str">
-        <v>2026 Summer | Embedded security chair focused on secure chips, cryptographic implementations, and side-channel or fault analysis. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E9" t="str">
-        <v>https://casa.rub.de/en/</v>
+        <v>https://www.scania.com</v>
       </c>
       <c r="F9" t="str">
-        <v>Bochum, DE</v>
+        <v>Södertälje, SE</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -813,36 +813,36 @@
         <v>High</v>
       </c>
       <c r="M9" t="str">
-        <v>Hardware,Embedded,Security,Firmware,Systems</v>
+        <v>Embedded,Hardware,Systems</v>
       </c>
       <c r="N9" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B10" t="str">
-        <v>TU Darmstadt System Security Lab</v>
+        <v>Volvo Group</v>
       </c>
       <c r="C10" t="str">
         <v>Researching</v>
       </c>
       <c r="D10" t="str">
-        <v>2026 Summer | Hardware-assisted security lab covering secure processors, IoT security, and practical system hardening. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E10" t="str">
-        <v>https://www.informatik.tu-darmstadt.de/systemsecurity/system_security_lab_sys/index.en.jsp</v>
+        <v>https://www.volvogroup.com</v>
       </c>
       <c r="F10" t="str">
-        <v>Darmstadt, DE</v>
+        <v>Gothenburg, SE</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -860,33 +860,33 @@
         <v>High</v>
       </c>
       <c r="M10" t="str">
-        <v>Security,Hardware,Embedded,IoT,Systems</v>
+        <v>Embedded,Hardware,Systems</v>
       </c>
       <c r="N10" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B11" t="str">
-        <v>TU Darmstadt ImpSec</v>
+        <v>Nokia</v>
       </c>
       <c r="C11" t="str">
         <v>Researching</v>
       </c>
       <c r="D11" t="str">
-        <v>2026 Summer | Implementation security chair focused on side-channel and fault attacks, ASICs, FPGAs, and microprocessor security. Initiative application.</v>
+        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
       </c>
       <c r="E11" t="str">
-        <v>https://www.informatik.tu-darmstadt.de/impsec/start_impsec/index.en.jsp</v>
+        <v>https://www.nokia.com</v>
       </c>
       <c r="F11" t="str">
-        <v>Darmstadt, DE</v>
+        <v>Espoo, FI</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -907,33 +907,33 @@
         <v>High</v>
       </c>
       <c r="M11" t="str">
-        <v>Hardware,Security,Embedded,Firmware,Systems</v>
+        <v>Systems,Hardware,Embedded</v>
       </c>
       <c r="N11" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:56:22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B12" t="str">
-        <v>KIT Chair of Dependable Nano Computing (CDNC)</v>
+        <v>STMicroelectronics</v>
       </c>
       <c r="C12" t="str">
         <v>Researching</v>
       </c>
       <c r="D12" t="str">
-        <v>2026 Summer | Hardware security lab known for FPGA side-channel and fault-attack research with active student thesis opportunities. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E12" t="str">
-        <v>https://cdnc.itec.kit.edu/</v>
+        <v>https://www.st.com</v>
       </c>
       <c r="F12" t="str">
-        <v>Karlsruhe, DE</v>
+        <v>Geneva, CH</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -954,36 +954,36 @@
         <v>High</v>
       </c>
       <c r="M12" t="str">
-        <v>Hardware,Security,Embedded,Systems,Firmware</v>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N12" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B13" t="str">
-        <v>TUM Chair of IT Security</v>
+        <v>KUKA</v>
       </c>
       <c r="C13" t="str">
         <v>Researching</v>
       </c>
       <c r="D13" t="str">
-        <v>2026 Summer | University chair with a strong hardware and embedded security track plus thesis and student project intake. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E13" t="str">
-        <v>https://www.sec.in.tum.de/i20/</v>
+        <v>https://www.kuka.com</v>
       </c>
       <c r="F13" t="str">
-        <v>Munich, DE</v>
+        <v>Augsburg, DE</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -1001,33 +1001,33 @@
         <v>High</v>
       </c>
       <c r="M13" t="str">
-        <v>Security,Hardware,Embedded,Firmware,Systems</v>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N13" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B14" t="str">
-        <v>Fraunhofer IMS</v>
+        <v>ZF Friedrichshafen</v>
       </c>
       <c r="C14" t="str">
         <v>Researching</v>
       </c>
       <c r="D14" t="str">
-        <v>2026 Summer | Trusted electronics group researching secure key memory, PUFs, encrypted firmware storage, and secure RISC-V cores. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E14" t="str">
-        <v>https://www.ims.fraunhofer.de/en.html</v>
+        <v>https://www.zf.com</v>
       </c>
       <c r="F14" t="str">
-        <v>Duisburg, DE</v>
+        <v>Friedrichshafen, DE</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1048,36 +1048,36 @@
         <v>High</v>
       </c>
       <c r="M14" t="str">
-        <v>Hardware,Embedded,Firmware,Security,Systems</v>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N14" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B15" t="str">
-        <v>Fraunhofer EMFT</v>
+        <v>Continental</v>
       </c>
       <c r="C15" t="str">
         <v>Researching</v>
       </c>
       <c r="D15" t="str">
-        <v>2026 Summer | Trusted electronics team focused on tamper protection, PUF-based key generation, and secure IoT hardware. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E15" t="str">
-        <v>https://www.emft.fraunhofer.de/en.html</v>
+        <v>https://www.continental.com</v>
       </c>
       <c r="F15" t="str">
-        <v>Munich, DE</v>
+        <v>Hanover, DE</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1095,36 +1095,36 @@
         <v>High</v>
       </c>
       <c r="M15" t="str">
-        <v>Hardware,Embedded,Security,IoT,Firmware</v>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N15" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:49:45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B16" t="str">
-        <v>Fraunhofer SIT</v>
+        <v>Mimecast</v>
       </c>
       <c r="C16" t="str">
         <v>Researching</v>
       </c>
       <c r="D16" t="str">
-        <v>2026 Summer | Embedded and IoT security institute working on protocol security, trusted computing, and secure firmware updates. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E16" t="str">
-        <v>https://www.sit.fraunhofer.de/en/</v>
+        <v>https://www.mimecast.com</v>
       </c>
       <c r="F16" t="str">
-        <v>Darmstadt, DE</v>
+        <v>London, UK</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1139,36 +1139,36 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M16" t="str">
-        <v>Embedded,Firmware,Security,IoT,Systems</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N16" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-03-31</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B17" t="str">
-        <v>Vestas</v>
+        <v>Bitdefender</v>
       </c>
       <c r="C17" t="str">
-        <v>Applied</v>
+        <v>Researching</v>
       </c>
       <c r="D17" t="str">
-        <v>2026 Summer | Nordic HQ; systems/embedded fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E17" t="str">
-        <v>https://www.vestas.com</v>
+        <v>https://www.bitdefender.com</v>
       </c>
       <c r="F17" t="str">
-        <v>Aarhus, DK</v>
+        <v>Bucharest, RO</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1186,36 +1186,36 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M17" t="str">
-        <v>Embedded,Systems,Hardware</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N17" t="str">
-        <v>2026-02-04 22:59:49</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-03-26 20:11:30</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B18" t="str">
-        <v>Nordic Semiconductor</v>
+        <v>Darktrace</v>
       </c>
       <c r="C18" t="str">
         <v>Researching</v>
       </c>
       <c r="D18" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E18" t="str">
-        <v>https://www.nordicsemi.com</v>
+        <v>https://www.darktrace.com</v>
       </c>
       <c r="F18" t="str">
-        <v>Trondheim, NO</v>
+        <v>Cambridge, UK</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1233,36 +1233,36 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M18" t="str">
-        <v>Embedded,Hardware,IoT</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N18" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B19" t="str">
-        <v>Kongsberg Gruppen</v>
+        <v>Sophos</v>
       </c>
       <c r="C19" t="str">
         <v>Researching</v>
       </c>
       <c r="D19" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E19" t="str">
-        <v>https://www.kongsberg.com</v>
+        <v>https://www.sophos.com</v>
       </c>
       <c r="F19" t="str">
-        <v>Kongsberg, NO</v>
+        <v>Abingdon, UK</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1280,36 +1280,36 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M19" t="str">
-        <v>Embedded,Hardware,Security</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N19" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B20" t="str">
-        <v>Telia Company</v>
+        <v>Panda Security</v>
       </c>
       <c r="C20" t="str">
         <v>Researching</v>
       </c>
       <c r="D20" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E20" t="str">
-        <v>https://www.teliacompany.com</v>
+        <v>https://www.pandasecurity.com</v>
       </c>
       <c r="F20" t="str">
-        <v>Solna, SE</v>
+        <v>Bilbao, ES</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1333,30 +1333,30 @@
         <v>Security,Systems</v>
       </c>
       <c r="N20" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B21" t="str">
-        <v>Telenor</v>
+        <v>G DATA</v>
       </c>
       <c r="C21" t="str">
         <v>Researching</v>
       </c>
       <c r="D21" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E21" t="str">
-        <v>https://www.telenor.com</v>
+        <v>https://www.gdatasoftware.com</v>
       </c>
       <c r="F21" t="str">
-        <v>Fornebu, NO</v>
+        <v>Bochum, DE</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1380,30 +1380,30 @@
         <v>Security,Systems</v>
       </c>
       <c r="N21" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B22" t="str">
-        <v>Axis Communications</v>
+        <v>Avira</v>
       </c>
       <c r="C22" t="str">
         <v>Researching</v>
       </c>
       <c r="D22" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E22" t="str">
-        <v>https://www.axis.com</v>
+        <v>https://www.avira.com</v>
       </c>
       <c r="F22" t="str">
-        <v>Lund, SE</v>
+        <v>Tettnang, DE</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1421,36 +1421,36 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M22" t="str">
-        <v>Embedded,Hardware,Security</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N22" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B23" t="str">
-        <v>Saab</v>
+        <v>ESET</v>
       </c>
       <c r="C23" t="str">
         <v>Researching</v>
       </c>
       <c r="D23" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E23" t="str">
-        <v>https://www.saab.com</v>
+        <v>https://www.eset.com</v>
       </c>
       <c r="F23" t="str">
-        <v>Stockholm, SE</v>
+        <v>Bratislava, SK</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1468,36 +1468,36 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M23" t="str">
-        <v>Embedded,Hardware,Security</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N23" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B24" t="str">
-        <v>Scania</v>
+        <v>NCC Group</v>
       </c>
       <c r="C24" t="str">
         <v>Researching</v>
       </c>
       <c r="D24" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E24" t="str">
-        <v>https://www.scania.com</v>
+        <v>https://www.nccgroupplc.com</v>
       </c>
       <c r="F24" t="str">
-        <v>Södertälje, SE</v>
+        <v>Manchester, UK</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M24" t="str">
-        <v>Embedded,Hardware,Systems</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N24" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B25" t="str">
-        <v>Volvo Group</v>
+        <v>WithSecure</v>
       </c>
       <c r="C25" t="str">
         <v>Researching</v>
       </c>
       <c r="D25" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E25" t="str">
-        <v>https://www.volvogroup.com</v>
+        <v>https://www.withsecure.com</v>
       </c>
       <c r="F25" t="str">
-        <v>Gothenburg, SE</v>
+        <v>Helsinki, FI</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1562,36 +1562,36 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M25" t="str">
-        <v>Embedded,Hardware,Systems</v>
+        <v>Security,Systems</v>
       </c>
       <c r="N25" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B26" t="str">
-        <v>Nokia</v>
+        <v>ABB</v>
       </c>
       <c r="C26" t="str">
         <v>Researching</v>
       </c>
       <c r="D26" t="str">
-        <v>2026 Summer | Nordic HQ/major office; embedded/security fit. Initiative application.</v>
+        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E26" t="str">
-        <v>https://www.nokia.com</v>
+        <v>https://www.abb.com</v>
       </c>
       <c r="F26" t="str">
-        <v>Espoo, FI</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1612,21 +1612,21 @@
         <v>High</v>
       </c>
       <c r="M26" t="str">
-        <v>Systems,Hardware,Embedded</v>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N26" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-02-04 22:56:22</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B27" t="str">
-        <v>STMicroelectronics</v>
+        <v>Rohde &amp; Schwarz</v>
       </c>
       <c r="C27" t="str">
         <v>Researching</v>
@@ -1635,10 +1635,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E27" t="str">
-        <v>https://www.st.com</v>
+        <v>https://www.rohde-schwarz.com</v>
       </c>
       <c r="F27" t="str">
-        <v>Geneva, CH</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1662,18 +1662,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N27" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B28" t="str">
-        <v>KUKA</v>
+        <v>Ericsson</v>
       </c>
       <c r="C28" t="str">
         <v>Researching</v>
@@ -1682,10 +1682,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E28" t="str">
-        <v>https://www.kuka.com</v>
+        <v>https://www.ericsson.com</v>
       </c>
       <c r="F28" t="str">
-        <v>Augsburg, DE</v>
+        <v>Stockholm, SE</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1709,18 +1709,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N28" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B29" t="str">
-        <v>ZF Friedrichshafen</v>
+        <v>Siemens</v>
       </c>
       <c r="C29" t="str">
         <v>Researching</v>
@@ -1729,10 +1729,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E29" t="str">
-        <v>https://www.zf.com</v>
+        <v>https://www.siemens.com</v>
       </c>
       <c r="F29" t="str">
-        <v>Friedrichshafen, DE</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1756,18 +1756,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N29" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B30" t="str">
-        <v>Continental</v>
+        <v>Bosch</v>
       </c>
       <c r="C30" t="str">
         <v>Researching</v>
@@ -1776,10 +1776,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E30" t="str">
-        <v>https://www.continental.com</v>
+        <v>https://www.bosch.com</v>
       </c>
       <c r="F30" t="str">
-        <v>Hanover, DE</v>
+        <v>Gerlingen, DE</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1803,18 +1803,18 @@
         <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N30" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-02-04 22:49:45</v>
+        <v>2026-02-04 22:48:04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B31" t="str">
-        <v>Mimecast</v>
+        <v>Infineon Technologies</v>
       </c>
       <c r="C31" t="str">
         <v>Researching</v>
@@ -1823,10 +1823,10 @@
         <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
       </c>
       <c r="E31" t="str">
-        <v>https://www.mimecast.com</v>
+        <v>https://www.infineon.com</v>
       </c>
       <c r="F31" t="str">
-        <v>London, UK</v>
+        <v>Neubiberg, DE</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1844,10 +1844,10 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="M31" t="str">
-        <v>Security,Systems</v>
+        <v>Embedded,Firmware,Systems,Hardware</v>
       </c>
       <c r="N31" t="str">
         <v>2026-02-04 22:48:04</v>
@@ -1858,22 +1858,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B32" t="str">
-        <v>Bitdefender</v>
+        <v>Microsoft</v>
       </c>
       <c r="C32" t="str">
         <v>Researching</v>
       </c>
       <c r="D32" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Microsoft Switzerland office; systems &amp; security-adjacent.</v>
       </c>
       <c r="E32" t="str">
-        <v>https://www.bitdefender.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F32" t="str">
-        <v>Bucharest, RO</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1894,33 +1894,33 @@
         <v>Medium</v>
       </c>
       <c r="M32" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B33" t="str">
-        <v>Darktrace</v>
+        <v>Microsoft</v>
       </c>
       <c r="C33" t="str">
         <v>Researching</v>
       </c>
       <c r="D33" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Microsoft Sweden office; systems &amp; security-adjacent.</v>
       </c>
       <c r="E33" t="str">
-        <v>https://www.darktrace.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F33" t="str">
-        <v>Cambridge, UK</v>
+        <v>Stockholm, SE</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1941,33 +1941,33 @@
         <v>Medium</v>
       </c>
       <c r="M33" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B34" t="str">
-        <v>Sophos</v>
+        <v>Microsoft</v>
       </c>
       <c r="C34" t="str">
         <v>Researching</v>
       </c>
       <c r="D34" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Microsoft Spain office; systems &amp; cloud security-adjacent.</v>
       </c>
       <c r="E34" t="str">
-        <v>https://www.sophos.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F34" t="str">
-        <v>Abingdon, UK</v>
+        <v>Madrid, ES</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1988,33 +1988,33 @@
         <v>Medium</v>
       </c>
       <c r="M34" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="B35" t="str">
-        <v>Panda Security</v>
+        <v>Microsoft</v>
       </c>
       <c r="C35" t="str">
         <v>Researching</v>
       </c>
       <c r="D35" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Microsoft Poland office; systems &amp; security-adjacent.</v>
       </c>
       <c r="E35" t="str">
-        <v>https://www.pandasecurity.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F35" t="str">
-        <v>Bilbao, ES</v>
+        <v>Warsaw, PL</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -2035,33 +2035,33 @@
         <v>Medium</v>
       </c>
       <c r="M35" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B36" t="str">
-        <v>G DATA</v>
+        <v>Microsoft</v>
       </c>
       <c r="C36" t="str">
         <v>Researching</v>
       </c>
       <c r="D36" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Microsoft Campus (Thames Valley Park); systems &amp; security-adjacent.</v>
       </c>
       <c r="E36" t="str">
-        <v>https://www.gdatasoftware.com</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F36" t="str">
-        <v>Bochum, DE</v>
+        <v>Reading, UK</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2082,33 +2082,33 @@
         <v>Medium</v>
       </c>
       <c r="M36" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B37" t="str">
-        <v>Avira</v>
+        <v>SAP</v>
       </c>
       <c r="C37" t="str">
         <v>Researching</v>
       </c>
       <c r="D37" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | SAP Frankfurt office (Eschborn); enterprise systems roles.</v>
       </c>
       <c r="E37" t="str">
-        <v>https://www.avira.com</v>
+        <v>https://www.sap.com</v>
       </c>
       <c r="F37" t="str">
-        <v>Tettnang, DE</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2129,33 +2129,33 @@
         <v>Medium</v>
       </c>
       <c r="M37" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B38" t="str">
-        <v>ESET</v>
+        <v>SAP</v>
       </c>
       <c r="C38" t="str">
         <v>Researching</v>
       </c>
       <c r="D38" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | SAP Berlin office; enterprise systems &amp; security-adjacent roles.</v>
       </c>
       <c r="E38" t="str">
-        <v>https://www.eset.com</v>
+        <v>https://www.sap.com</v>
       </c>
       <c r="F38" t="str">
-        <v>Bratislava, SK</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -2176,33 +2176,33 @@
         <v>Medium</v>
       </c>
       <c r="M38" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="B39" t="str">
-        <v>NCC Group</v>
+        <v>SAP</v>
       </c>
       <c r="C39" t="str">
         <v>Researching</v>
       </c>
       <c r="D39" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Global HQ; large-scale systems &amp; security-adjacent roles.</v>
       </c>
       <c r="E39" t="str">
-        <v>https://www.nccgroupplc.com</v>
+        <v>https://www.sap.com</v>
       </c>
       <c r="F39" t="str">
-        <v>Manchester, UK</v>
+        <v>Walldorf, DE</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2223,33 +2223,33 @@
         <v>Medium</v>
       </c>
       <c r="M39" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N39" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B40" t="str">
-        <v>WithSecure</v>
+        <v>Arm</v>
       </c>
       <c r="C40" t="str">
         <v>Researching</v>
       </c>
       <c r="D40" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E40" t="str">
-        <v>https://www.withsecure.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F40" t="str">
-        <v>Helsinki, FI</v>
+        <v>Oslo, NO</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2270,33 +2270,33 @@
         <v>Medium</v>
       </c>
       <c r="M40" t="str">
-        <v>Security,Systems</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B41" t="str">
-        <v>ABB</v>
+        <v>Arm</v>
       </c>
       <c r="C41" t="str">
         <v>Researching</v>
       </c>
       <c r="D41" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E41" t="str">
-        <v>https://www.abb.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F41" t="str">
-        <v>Zurich, CH</v>
+        <v>Lund, SE</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -2314,36 +2314,36 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M41" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v/>
       </c>
       <c r="N41" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B42" t="str">
-        <v>Rohde &amp; Schwarz</v>
+        <v>Arm</v>
       </c>
       <c r="C42" t="str">
         <v>Researching</v>
       </c>
       <c r="D42" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E42" t="str">
-        <v>https://www.rohde-schwarz.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F42" t="str">
-        <v>Munich, DE</v>
+        <v>Galway, IE</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2361,39 +2361,39 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M42" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v/>
       </c>
       <c r="N42" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="B43" t="str">
-        <v>Ericsson</v>
+        <v>Arm</v>
       </c>
       <c r="C43" t="str">
         <v>Researching</v>
       </c>
       <c r="D43" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; embedded focus.</v>
       </c>
       <c r="E43" t="str">
-        <v>https://www.ericsson.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F43" t="str">
-        <v>Stockholm, SE</v>
+        <v>Aschheim, DE</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2408,36 +2408,36 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M43" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v/>
       </c>
       <c r="N43" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B44" t="str">
-        <v>Siemens</v>
+        <v>Arm</v>
       </c>
       <c r="C44" t="str">
         <v>Researching</v>
       </c>
       <c r="D44" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; systems + security-adjacent roles.</v>
       </c>
       <c r="E44" t="str">
-        <v>https://www.siemens.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F44" t="str">
-        <v>Munich, DE</v>
+        <v>Sophia Antipolis, FR</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2455,36 +2455,36 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M44" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v/>
       </c>
       <c r="N44" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B45" t="str">
-        <v>Bosch</v>
+        <v>Arm</v>
       </c>
       <c r="C45" t="str">
         <v>Researching</v>
       </c>
       <c r="D45" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; firmware/embedded fit.</v>
       </c>
       <c r="E45" t="str">
-        <v>https://www.bosch.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F45" t="str">
-        <v>Gerlingen, DE</v>
+        <v>Bristol, UK</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2502,36 +2502,36 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M45" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v/>
       </c>
       <c r="N45" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B46" t="str">
-        <v>Infineon Technologies</v>
+        <v>Arm</v>
       </c>
       <c r="C46" t="str">
         <v>Researching</v>
       </c>
       <c r="D46" t="str">
-        <v>2026 Summer | Targeted for embedded + security trajectory. Initiative application.</v>
+        <v>2026 Summer | Engineering office; embedded systems fit.</v>
       </c>
       <c r="E46" t="str">
-        <v>https://www.infineon.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F46" t="str">
-        <v>Neubiberg, DE</v>
+        <v>Manchester, UK</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -2549,39 +2549,39 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="M46" t="str">
-        <v>Embedded,Firmware,Systems,Hardware</v>
+        <v/>
       </c>
       <c r="N46" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-02-04 22:48:04</v>
+        <v>2026-02-04 16:44:49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B47" t="str">
-        <v>Microsoft</v>
+        <v>Arm</v>
       </c>
       <c r="C47" t="str">
         <v>Researching</v>
       </c>
       <c r="D47" t="str">
-        <v>2026 Summer | Microsoft Switzerland office; systems &amp; security-adjacent.</v>
+        <v>2026 Summer | Global HQ; embedded systems &amp; security focus.</v>
       </c>
       <c r="E47" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F47" t="str">
-        <v>Zurich, CH</v>
+        <v>Cambridge, UK</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -2610,22 +2610,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B48" t="str">
-        <v>Microsoft</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C48" t="str">
         <v>Researching</v>
       </c>
       <c r="D48" t="str">
-        <v>2026 Summer | Microsoft Sweden office; systems &amp; security-adjacent.</v>
+        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
       </c>
       <c r="E48" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F48" t="str">
-        <v>Stockholm, SE</v>
+        <v>Cambridge, UK</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2657,25 +2657,25 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B49" t="str">
-        <v>Microsoft</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C49" t="str">
         <v>Researching</v>
       </c>
       <c r="D49" t="str">
-        <v>2026 Summer | Microsoft Spain office; systems &amp; cloud security-adjacent.</v>
+        <v>2026 Summer | EU office; engineering &amp; security-adjacent roles.</v>
       </c>
       <c r="E49" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F49" t="str">
-        <v>Madrid, ES</v>
+        <v>London, UK</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -2704,22 +2704,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="B50" t="str">
-        <v>Microsoft</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C50" t="str">
         <v>Researching</v>
       </c>
       <c r="D50" t="str">
-        <v>2026 Summer | Microsoft Poland office; systems &amp; security-adjacent.</v>
+        <v>2026 Summer | EU office; systems &amp; security fit.</v>
       </c>
       <c r="E50" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F50" t="str">
-        <v>Warsaw, PL</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -2751,22 +2751,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B51" t="str">
-        <v>Microsoft</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C51" t="str">
         <v>Researching</v>
       </c>
       <c r="D51" t="str">
-        <v>2026 Summer | Microsoft Campus (Thames Valley Park); systems &amp; security-adjacent.</v>
+        <v>2026 Summer | EU office; systems/embedded adjacent roles.</v>
       </c>
       <c r="E51" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F51" t="str">
-        <v>Reading, UK</v>
+        <v>Helsinki, FI</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2798,22 +2798,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B52" t="str">
-        <v>SAP</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C52" t="str">
         <v>Researching</v>
       </c>
       <c r="D52" t="str">
-        <v>2026 Summer | SAP Frankfurt office (Eschborn); enterprise systems roles.</v>
+        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
       </c>
       <c r="E52" t="str">
-        <v>https://www.sap.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F52" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Warsaw, PL</v>
       </c>
       <c r="G52">
         <v>2</v>
@@ -2845,22 +2845,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="B53" t="str">
-        <v>SAP</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C53" t="str">
         <v>Researching</v>
       </c>
       <c r="D53" t="str">
-        <v>2026 Summer | SAP Berlin office; enterprise systems &amp; security-adjacent roles.</v>
+        <v>2026 Summer | EU office; advanced systems and security-adjacent teams.</v>
       </c>
       <c r="E53" t="str">
-        <v>https://www.sap.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F53" t="str">
-        <v>Berlin, DE</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2892,22 +2892,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B54" t="str">
-        <v>SAP</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C54" t="str">
         <v>Researching</v>
       </c>
       <c r="D54" t="str">
-        <v>2026 Summer | Global HQ; large-scale systems &amp; security-adjacent roles.</v>
+        <v>2026 Summer | EU engineering hub; systems + embedded focus fit.</v>
       </c>
       <c r="E54" t="str">
-        <v>https://www.sap.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F54" t="str">
-        <v>Walldorf, DE</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="B55" t="str">
-        <v>Arm</v>
+        <v>NVIDIA</v>
       </c>
       <c r="C55" t="str">
         <v>Researching</v>
       </c>
       <c r="D55" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | EU engineering presence; compute &amp; security-adjacent systems.</v>
       </c>
       <c r="E55" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.nvidia.com</v>
       </c>
       <c r="F55" t="str">
-        <v>Oslo, NO</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -2986,25 +2986,25 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B56" t="str">
-        <v>Arm</v>
+        <v>Netflix</v>
       </c>
       <c r="C56" t="str">
         <v>Researching</v>
       </c>
       <c r="D56" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | Paris office; global teams and compliance/security-adjacent work.</v>
       </c>
       <c r="E56" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.netflix.com</v>
       </c>
       <c r="F56" t="str">
-        <v>Lund, SE</v>
+        <v>Paris, FR</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -3033,25 +3033,25 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="B57" t="str">
-        <v>Arm</v>
+        <v>Netflix</v>
       </c>
       <c r="C57" t="str">
         <v>Researching</v>
       </c>
       <c r="D57" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | UK office connected to EMEA HQ; cross-functional tech &amp; ops teams.</v>
       </c>
       <c r="E57" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.netflix.com</v>
       </c>
       <c r="F57" t="str">
-        <v>Galway, IE</v>
+        <v>London, UK</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v/>
       </c>
       <c r="N57" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O57" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -3080,22 +3080,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="B58" t="str">
-        <v>Arm</v>
+        <v>Netflix</v>
       </c>
       <c r="C58" t="str">
         <v>Researching</v>
       </c>
       <c r="D58" t="str">
-        <v>2026 Summer | Engineering office; embedded focus.</v>
+        <v>2026 Summer | EMEA HQ; global teams across content, legal, finance, security-adjacent.</v>
       </c>
       <c r="E58" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.netflix.com</v>
       </c>
       <c r="F58" t="str">
-        <v>Aschheim, DE</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3119,7 +3119,7 @@
         <v/>
       </c>
       <c r="N58" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O58" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -3127,25 +3127,25 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="B59" t="str">
-        <v>Arm</v>
+        <v>Apple</v>
       </c>
       <c r="C59" t="str">
         <v>Researching</v>
       </c>
       <c r="D59" t="str">
-        <v>2026 Summer | Engineering office; systems + security-adjacent roles.</v>
+        <v>2026 Summer | Operations &amp; engineering teams in Ireland.</v>
       </c>
       <c r="E59" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.apple.com</v>
       </c>
       <c r="F59" t="str">
-        <v>Sophia Antipolis, FR</v>
+        <v>Cork, IE</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -3166,30 +3166,30 @@
         <v/>
       </c>
       <c r="N59" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="B60" t="str">
-        <v>Arm</v>
+        <v>Google</v>
       </c>
       <c r="C60" t="str">
         <v>Researching</v>
       </c>
       <c r="D60" t="str">
-        <v>2026 Summer | Engineering office; firmware/embedded fit.</v>
+        <v>2026 Summer | Major European engineering hub; systems &amp; security fit.</v>
       </c>
       <c r="E60" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.google.com</v>
       </c>
       <c r="F60" t="str">
-        <v>Bristol, UK</v>
+        <v>Zurich, CH</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -3213,30 +3213,30 @@
         <v/>
       </c>
       <c r="N60" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="B61" t="str">
-        <v>Arm</v>
+        <v>Meta</v>
       </c>
       <c r="C61" t="str">
         <v>Researching</v>
       </c>
       <c r="D61" t="str">
-        <v>2026 Summer | Engineering office; embedded systems fit.</v>
+        <v>2026 Summer | International HQ in Ireland; security &amp; systems-adjacent roles.</v>
       </c>
       <c r="E61" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.meta.com</v>
       </c>
       <c r="F61" t="str">
-        <v>Manchester, UK</v>
+        <v>Dublin, IE</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -3260,7 +3260,7 @@
         <v/>
       </c>
       <c r="N61" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O61" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -3268,25 +3268,25 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="B62" t="str">
-        <v>Arm</v>
+        <v>Amazon</v>
       </c>
       <c r="C62" t="str">
         <v>Researching</v>
       </c>
       <c r="D62" t="str">
-        <v>2026 Summer | Global HQ; embedded systems &amp; security focus.</v>
+        <v>2026 Summer | EU hub (Germany). Initiative application.</v>
       </c>
       <c r="E62" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F62" t="str">
-        <v>Cambridge, UK</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -3307,33 +3307,33 @@
         <v/>
       </c>
       <c r="N62" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B63" t="str">
-        <v>NVIDIA</v>
+        <v>Amazon</v>
       </c>
       <c r="C63" t="str">
         <v>Researching</v>
       </c>
       <c r="D63" t="str">
-        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
+        <v>2026 Summer | EU hub (France). Initiative application.</v>
       </c>
       <c r="E63" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F63" t="str">
-        <v>Cambridge, UK</v>
+        <v>Paris, FR</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -3354,30 +3354,30 @@
         <v/>
       </c>
       <c r="N63" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B64" t="str">
-        <v>NVIDIA</v>
+        <v>Amazon</v>
       </c>
       <c r="C64" t="str">
         <v>Researching</v>
       </c>
       <c r="D64" t="str">
-        <v>2026 Summer | EU office; engineering &amp; security-adjacent roles.</v>
+        <v>2026 Summer | EU tech hub (Germany). Initiative application.</v>
       </c>
       <c r="E64" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F64" t="str">
-        <v>London, UK</v>
+        <v>Munich, DE</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3401,33 +3401,33 @@
         <v/>
       </c>
       <c r="N64" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B65" t="str">
-        <v>NVIDIA</v>
+        <v>Amazon</v>
       </c>
       <c r="C65" t="str">
         <v>Researching</v>
       </c>
       <c r="D65" t="str">
-        <v>2026 Summer | EU office; systems &amp; security fit.</v>
+        <v>2026 Summer | EU tech &amp; business hub. Initiative application.</v>
       </c>
       <c r="E65" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F65" t="str">
-        <v>Amsterdam, NL</v>
+        <v>London, UK</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -3448,30 +3448,30 @@
         <v/>
       </c>
       <c r="N65" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B66" t="str">
-        <v>NVIDIA</v>
+        <v>Amazon</v>
       </c>
       <c r="C66" t="str">
         <v>Researching</v>
       </c>
       <c r="D66" t="str">
-        <v>2026 Summer | EU office; systems/embedded adjacent roles.</v>
+        <v>2026 Summer | EU HQ in Luxembourg; large-scale systems, security-adjacent teams. Initiative application.</v>
       </c>
       <c r="E66" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.amazon.com</v>
       </c>
       <c r="F66" t="str">
-        <v>Helsinki, FI</v>
+        <v>Luxembourg, LU</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -3495,7 +3495,7 @@
         <v/>
       </c>
       <c r="N66" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:37:28</v>
       </c>
       <c r="O66" t="str">
         <v>2026-02-04 16:44:49</v>
@@ -3503,25 +3503,25 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B67" t="str">
-        <v>NVIDIA</v>
+        <v>HSP Technology Global</v>
       </c>
       <c r="C67" t="str">
         <v>Researching</v>
       </c>
       <c r="D67" t="str">
-        <v>2026 Summer | EU office; engineering &amp; systems roles.</v>
+        <v>2026 Summer | Engineering &amp; tech; Antalya Technokent address.</v>
       </c>
       <c r="E67" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.hsptechglobal.com</v>
       </c>
       <c r="F67" t="str">
-        <v>Warsaw, PL</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -3542,33 +3542,33 @@
         <v/>
       </c>
       <c r="N67" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B68" t="str">
-        <v>NVIDIA</v>
+        <v>Savhatek Defence Industries</v>
       </c>
       <c r="C68" t="str">
         <v>Researching</v>
       </c>
       <c r="D68" t="str">
-        <v>2026 Summer | EU office; advanced systems and security-adjacent teams.</v>
+        <v>2026 Summer | Defense &amp; embedded systems; Antalya Technokent HQ.</v>
       </c>
       <c r="E68" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://savhatek.com</v>
       </c>
       <c r="F68" t="str">
-        <v>Zurich, CH</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -3589,33 +3589,33 @@
         <v/>
       </c>
       <c r="N68" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:33:31</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B69" t="str">
-        <v>NVIDIA</v>
+        <v>SANTSG</v>
       </c>
       <c r="C69" t="str">
         <v>Researching</v>
       </c>
       <c r="D69" t="str">
-        <v>2026 Summer | EU engineering hub; systems + embedded focus fit.</v>
+        <v>2026 Summer | Head office in Antalya Technokent; engineering &amp; R&amp;D.</v>
       </c>
       <c r="E69" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.santsg.com</v>
       </c>
       <c r="F69" t="str">
-        <v>Munich, DE</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -3636,33 +3636,33 @@
         <v/>
       </c>
       <c r="N69" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B70" t="str">
-        <v>NVIDIA</v>
+        <v>CRS CAM</v>
       </c>
       <c r="C70" t="str">
         <v>Researching</v>
       </c>
       <c r="D70" t="str">
-        <v>2026 Summer | EU engineering presence; compute &amp; security-adjacent systems.</v>
+        <v>2026 Summer | Camera/vision hardware; R&amp;D office in Antalya Technokent.</v>
       </c>
       <c r="E70" t="str">
-        <v>https://www.nvidia.com</v>
+        <v>https://www.crscam.com</v>
       </c>
       <c r="F70" t="str">
-        <v>Berlin, DE</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -3683,30 +3683,30 @@
         <v/>
       </c>
       <c r="N70" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B71" t="str">
-        <v>Netflix</v>
+        <v>Evant Teknoloji A.S.</v>
       </c>
       <c r="C71" t="str">
         <v>Researching</v>
       </c>
       <c r="D71" t="str">
-        <v>2026 Summer | Paris office; global teams and compliance/security-adjacent work.</v>
+        <v>2026 Summer | System integrator with Antalya branch; security partnerships.</v>
       </c>
       <c r="E71" t="str">
-        <v>https://www.netflix.com</v>
+        <v>https://evant.com.tr/en</v>
       </c>
       <c r="F71" t="str">
-        <v>Paris, FR</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3730,33 +3730,33 @@
         <v/>
       </c>
       <c r="N71" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B72" t="str">
-        <v>Netflix</v>
+        <v>EPAM Systems Türkiye</v>
       </c>
       <c r="C72" t="str">
         <v>Researching</v>
       </c>
       <c r="D72" t="str">
-        <v>2026 Summer | UK office connected to EMEA HQ; cross-functional tech &amp; ops teams.</v>
+        <v>2026 Summer | Global engineering firm; Antalya OSB Technopark R&amp;D presence.</v>
       </c>
       <c r="E72" t="str">
-        <v>https://www.netflix.com</v>
+        <v>https://www.epam.com</v>
       </c>
       <c r="F72" t="str">
-        <v>London, UK</v>
+        <v>Antalya, TR</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -3777,33 +3777,33 @@
         <v/>
       </c>
       <c r="N72" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:32:01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="B73" t="str">
-        <v>Netflix</v>
+        <v>STM Savunma Teknolojileri</v>
       </c>
       <c r="C73" t="str">
         <v>Researching</v>
       </c>
       <c r="D73" t="str">
-        <v>2026 Summer | EMEA HQ; global teams across content, legal, finance, security-adjacent.</v>
+        <v>2026 Summer | Cybersecurity, command-control ve embedded sistemler.</v>
       </c>
       <c r="E73" t="str">
-        <v>https://www.netflix.com</v>
+        <v>https://www.stm.com.tr</v>
       </c>
       <c r="F73" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -3824,33 +3824,33 @@
         <v/>
       </c>
       <c r="N73" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B74" t="str">
-        <v>Apple</v>
+        <v>Turkish Aerospace (TUSAŞ)</v>
       </c>
       <c r="C74" t="str">
         <v>Researching</v>
       </c>
       <c r="D74" t="str">
-        <v>2026 Summer | Operations &amp; engineering teams in Ireland.</v>
+        <v>2026 Summer | Aerospace + embedded systems, secure systems ve avionics odakli ekipler.</v>
       </c>
       <c r="E74" t="str">
-        <v>https://www.apple.com</v>
+        <v>https://www.tusas.com</v>
       </c>
       <c r="F74" t="str">
-        <v>Cork, IE</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -3871,33 +3871,33 @@
         <v/>
       </c>
       <c r="N74" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B75" t="str">
-        <v>Google</v>
+        <v>TOPIC Embedded Systems</v>
       </c>
       <c r="C75" t="str">
         <v>Researching</v>
       </c>
       <c r="D75" t="str">
-        <v>2026 Summer | Major European engineering hub; systems &amp; security fit.</v>
+        <v>2026 Summer | Embedded systems consultancy; firmware ve low-level sistemler.</v>
       </c>
       <c r="E75" t="str">
-        <v>https://www.google.com</v>
+        <v>https://www.topic.nl</v>
       </c>
       <c r="F75" t="str">
-        <v>Zurich, CH</v>
+        <v>Eindhoven, NL</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -3918,33 +3918,33 @@
         <v/>
       </c>
       <c r="N75" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B76" t="str">
-        <v>Meta</v>
+        <v>TomTom</v>
       </c>
       <c r="C76" t="str">
         <v>Researching</v>
       </c>
       <c r="D76" t="str">
-        <v>2026 Summer | International HQ in Ireland; security &amp; systems-adjacent roles.</v>
+        <v>2026 Summer | Automotive navigation &amp; location tech; embedded/vehicle systems odakli ekipler.</v>
       </c>
       <c r="E76" t="str">
-        <v>https://www.meta.com</v>
+        <v>https://www.tomtom.com</v>
       </c>
       <c r="F76" t="str">
-        <v>Dublin, IE</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -3965,30 +3965,30 @@
         <v/>
       </c>
       <c r="N76" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B77" t="str">
-        <v>Amazon</v>
+        <v>Eye Security</v>
       </c>
       <c r="C77" t="str">
         <v>Researching</v>
       </c>
       <c r="D77" t="str">
-        <v>2026 Summer | EU hub (Germany). Initiative application.</v>
+        <v>2026 Summer | Managed detection &amp; response; security operations mindset odakli ekipler.</v>
       </c>
       <c r="E77" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.eye.security</v>
       </c>
       <c r="F77" t="str">
-        <v>Berlin, DE</v>
+        <v>The Hague, NL</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -4012,30 +4012,30 @@
         <v/>
       </c>
       <c r="N77" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B78" t="str">
-        <v>Amazon</v>
+        <v>Fox-IT</v>
       </c>
       <c r="C78" t="str">
         <v>Researching</v>
       </c>
       <c r="D78" t="str">
-        <v>2026 Summer | EU hub (France). Initiative application.</v>
+        <v>2026 Summer | Blue-team &amp; incident-response kültürü; security engineering odakli ekipler.</v>
       </c>
       <c r="E78" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.fox-it.com</v>
       </c>
       <c r="F78" t="str">
-        <v>Paris, FR</v>
+        <v>Delft, NL</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -4059,33 +4059,33 @@
         <v/>
       </c>
       <c r="N78" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B79" t="str">
-        <v>Amazon</v>
+        <v>ASM International</v>
       </c>
       <c r="C79" t="str">
         <v>Researching</v>
       </c>
       <c r="D79" t="str">
-        <v>2026 Summer | EU tech hub (Germany). Initiative application.</v>
+        <v>2026 Summer | Semiconductor manufacturing equipment; systems/embedded odakli ekipler.</v>
       </c>
       <c r="E79" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.asm.com</v>
       </c>
       <c r="F79" t="str">
-        <v>Munich, DE</v>
+        <v>Almere, NL</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -4106,30 +4106,30 @@
         <v/>
       </c>
       <c r="N79" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B80" t="str">
-        <v>Amazon</v>
+        <v>Nexperia</v>
       </c>
       <c r="C80" t="str">
         <v>Researching</v>
       </c>
       <c r="D80" t="str">
-        <v>2026 Summer | EU tech &amp; business hub. Initiative application.</v>
+        <v>2026 Summer | Semiconductor; embedded güvenlik ve donanim-odakli ekipler.</v>
       </c>
       <c r="E80" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.nexperia.com</v>
       </c>
       <c r="F80" t="str">
-        <v>London, UK</v>
+        <v>Nijmegen, NL</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4153,33 +4153,33 @@
         <v/>
       </c>
       <c r="N80" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B81" t="str">
-        <v>Amazon</v>
+        <v>Thales Nederland</v>
       </c>
       <c r="C81" t="str">
         <v>Researching</v>
       </c>
       <c r="D81" t="str">
-        <v>2026 Summer | EU HQ in Luxembourg; large-scale systems, security-adjacent teams. Initiative application.</v>
+        <v>2026 Summer | Defense &amp; cybersecurity; secure systems ve embedded güvenlik odakli ekipler.</v>
       </c>
       <c r="E81" t="str">
-        <v>https://www.amazon.com</v>
+        <v>https://www.thalesgroup.com</v>
       </c>
       <c r="F81" t="str">
-        <v>Luxembourg, LU</v>
+        <v>Hengelo, NL</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -4200,30 +4200,30 @@
         <v/>
       </c>
       <c r="N81" t="str">
-        <v>2026-02-04 16:37:28</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-02-04 16:44:49</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B82" t="str">
-        <v>HSP Technology Global</v>
+        <v>Philips</v>
       </c>
       <c r="C82" t="str">
         <v>Researching</v>
       </c>
       <c r="D82" t="str">
-        <v>2026 Summer | Engineering &amp; tech; Antalya Technokent address.</v>
+        <v>2026 Summer | Medical/health-tech sistemler; embedded + güvenlik odakli ekipler.</v>
       </c>
       <c r="E82" t="str">
-        <v>https://www.hsptechglobal.com</v>
+        <v>https://www.philips.com</v>
       </c>
       <c r="F82" t="str">
-        <v>Antalya, TR</v>
+        <v>Amsterdam, NL</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4247,30 +4247,30 @@
         <v/>
       </c>
       <c r="N82" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B83" t="str">
-        <v>Savhatek Defence Industries</v>
+        <v>ASML</v>
       </c>
       <c r="C83" t="str">
         <v>Researching</v>
       </c>
       <c r="D83" t="str">
-        <v>2026 Summer | Defense &amp; embedded systems; Antalya Technokent HQ.</v>
+        <v>2026 Summer | Semiconductor tooling; embedded + systems security odakli ekipler. Initiative application.</v>
       </c>
       <c r="E83" t="str">
-        <v>https://savhatek.com</v>
+        <v>https://www.asml.com</v>
       </c>
       <c r="F83" t="str">
-        <v>Antalya, TR</v>
+        <v>Veldhoven, NL</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -4294,33 +4294,33 @@
         <v/>
       </c>
       <c r="N83" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-02-04 16:33:31</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B84" t="str">
-        <v>SANTSG</v>
+        <v>Rheinmetall</v>
       </c>
       <c r="C84" t="str">
         <v>Researching</v>
       </c>
       <c r="D84" t="str">
-        <v>2026 Summer | Head office in Antalya Technokent; engineering &amp; R&amp;D.</v>
+        <v>2026 Summer | Guvenlik ve savunma teknolojileri, embedded/secure systems.</v>
       </c>
       <c r="E84" t="str">
-        <v>https://www.santsg.com</v>
+        <v>https://www.rheinmetall.com</v>
       </c>
       <c r="F84" t="str">
-        <v>Antalya, TR</v>
+        <v>Dusseldorf, DE</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -4341,30 +4341,30 @@
         <v/>
       </c>
       <c r="N84" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B85" t="str">
-        <v>CRS CAM</v>
+        <v>Henkel</v>
       </c>
       <c r="C85" t="str">
         <v>Researching</v>
       </c>
       <c r="D85" t="str">
-        <v>2026 Summer | Camera/vision hardware; R&amp;D office in Antalya Technokent.</v>
+        <v>2026 Summer | Endustriyel IT/OT ve guvenlik odakli ekipler.</v>
       </c>
       <c r="E85" t="str">
-        <v>https://www.crscam.com</v>
+        <v>https://www.henkel.com</v>
       </c>
       <c r="F85" t="str">
-        <v>Antalya, TR</v>
+        <v>Dusseldorf, DE</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -4388,30 +4388,30 @@
         <v/>
       </c>
       <c r="N85" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B86" t="str">
-        <v>Evant Teknoloji A.S.</v>
+        <v>DZ BANK</v>
       </c>
       <c r="C86" t="str">
         <v>Researching</v>
       </c>
       <c r="D86" t="str">
-        <v>2026 Summer | System integrator with Antalya branch; security partnerships.</v>
+        <v>2026 Summer | Finansal altyapi ve bilgi guvenligi odakli ekipler.</v>
       </c>
       <c r="E86" t="str">
-        <v>https://evant.com.tr/en</v>
+        <v>https://www.dzbank.com</v>
       </c>
       <c r="F86" t="str">
-        <v>Antalya, TR</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -4435,33 +4435,33 @@
         <v/>
       </c>
       <c r="N86" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B87" t="str">
-        <v>EPAM Systems Türkiye</v>
+        <v>Deutsche Boerse Group</v>
       </c>
       <c r="C87" t="str">
         <v>Researching</v>
       </c>
       <c r="D87" t="str">
-        <v>2026 Summer | Global engineering firm; Antalya OSB Technopark R&amp;D presence.</v>
+        <v>2026 Summer | Piyasa altyapisi, cyber protection ve sistem guvenligi odakli ekipler.</v>
       </c>
       <c r="E87" t="str">
-        <v>https://www.epam.com</v>
+        <v>https://www.deutsche-boerse.com</v>
       </c>
       <c r="F87" t="str">
-        <v>Antalya, TR</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -4482,33 +4482,33 @@
         <v/>
       </c>
       <c r="N87" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-02-04 16:32:01</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B88" t="str">
-        <v>STM Savunma Teknolojileri</v>
+        <v>DekaBank</v>
       </c>
       <c r="C88" t="str">
         <v>Researching</v>
       </c>
       <c r="D88" t="str">
-        <v>2026 Summer | Cybersecurity, command-control ve embedded sistemler.</v>
+        <v>2026 Summer | Finans ve altyapi guvenligi odakli ekipler.</v>
       </c>
       <c r="E88" t="str">
-        <v>https://www.stm.com.tr</v>
+        <v>https://www.deka.de</v>
       </c>
       <c r="F88" t="str">
-        <v>Turkey, TR</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -4529,33 +4529,33 @@
         <v/>
       </c>
       <c r="N88" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B89" t="str">
-        <v>Turkish Aerospace (TUSAŞ)</v>
+        <v>Commerzbank</v>
       </c>
       <c r="C89" t="str">
         <v>Researching</v>
       </c>
       <c r="D89" t="str">
-        <v>2026 Summer | Aerospace + embedded systems, secure systems ve avionics odakli ekipler.</v>
+        <v>2026 Summer | Finansal sistemler ve bilgi guvenligi odakli ekipler.</v>
       </c>
       <c r="E89" t="str">
-        <v>https://www.tusas.com</v>
+        <v>https://www.commerzbank.de</v>
       </c>
       <c r="F89" t="str">
-        <v>Turkey, TR</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -4576,33 +4576,33 @@
         <v/>
       </c>
       <c r="N89" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B90" t="str">
-        <v>TOPIC Embedded Systems</v>
+        <v>Deutsche Bank</v>
       </c>
       <c r="C90" t="str">
         <v>Researching</v>
       </c>
       <c r="D90" t="str">
-        <v>2026 Summer | Embedded systems consultancy; firmware ve low-level sistemler.</v>
+        <v>2026 Summer | Banka altyapisi ve siber guvenlik odakli ekipler.</v>
       </c>
       <c r="E90" t="str">
-        <v>https://www.topic.nl</v>
+        <v>https://www.db.com</v>
       </c>
       <c r="F90" t="str">
-        <v>Eindhoven, NL</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -4623,30 +4623,30 @@
         <v/>
       </c>
       <c r="N90" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B91" t="str">
-        <v>TomTom</v>
+        <v>Giesecke+Devrient</v>
       </c>
       <c r="C91" t="str">
         <v>Researching</v>
       </c>
       <c r="D91" t="str">
-        <v>2026 Summer | Automotive navigation &amp; location tech; embedded/vehicle systems odakli ekipler.</v>
+        <v>2026 Summer | SecurityTech, kimlik ve secure hardware/embedded alanlari.</v>
       </c>
       <c r="E91" t="str">
-        <v>https://www.tomtom.com</v>
+        <v>https://www.gi-de.com</v>
       </c>
       <c r="F91" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G91">
         <v>3</v>
@@ -4670,30 +4670,30 @@
         <v/>
       </c>
       <c r="N91" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B92" t="str">
-        <v>Eye Security</v>
+        <v>BMW Group</v>
       </c>
       <c r="C92" t="str">
         <v>Researching</v>
       </c>
       <c r="D92" t="str">
-        <v>2026 Summer | Managed detection &amp; response; security operations mindset odakli ekipler.</v>
+        <v>2026 Summer | Otomotiv embedded, sistem guvenligi ve yazilim ekipleri.</v>
       </c>
       <c r="E92" t="str">
-        <v>https://www.eye.security</v>
+        <v>https://www.bmwgroup.com</v>
       </c>
       <c r="F92" t="str">
-        <v>The Hague, NL</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -4717,33 +4717,33 @@
         <v/>
       </c>
       <c r="N92" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B93" t="str">
-        <v>Fox-IT</v>
+        <v>Siemens AG</v>
       </c>
       <c r="C93" t="str">
         <v>Researching</v>
       </c>
       <c r="D93" t="str">
-        <v>2026 Summer | Blue-team &amp; incident-response kültürü; security engineering odakli ekipler.</v>
+        <v>2026 Summer | Endustriyel sistemler, OT/ICS guvenligi ve embedded odakli ekipler.</v>
       </c>
       <c r="E93" t="str">
-        <v>https://www.fox-it.com</v>
+        <v>https://www.siemens.com</v>
       </c>
       <c r="F93" t="str">
-        <v>Delft, NL</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -4764,30 +4764,30 @@
         <v/>
       </c>
       <c r="N93" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B94" t="str">
-        <v>ASM International</v>
+        <v>Mercedes-Benz Group AG</v>
       </c>
       <c r="C94" t="str">
         <v>Researching</v>
       </c>
       <c r="D94" t="str">
-        <v>2026 Summer | Semiconductor manufacturing equipment; systems/embedded odakli ekipler.</v>
+        <v>2026 Summer | Otomotiv embedded/vehicle security odakli ekipler. Initiative application.</v>
       </c>
       <c r="E94" t="str">
-        <v>https://www.asm.com</v>
+        <v>https://group.mercedes-benz.com</v>
       </c>
       <c r="F94" t="str">
-        <v>Almere, NL</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G94">
         <v>2</v>
@@ -4811,33 +4811,33 @@
         <v/>
       </c>
       <c r="N94" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B95" t="str">
-        <v>Nexperia</v>
+        <v>ubisys technologies</v>
       </c>
       <c r="C95" t="str">
         <v>Researching</v>
       </c>
       <c r="D95" t="str">
-        <v>2026 Summer | Semiconductor; embedded güvenlik ve donanim-odakli ekipler.</v>
+        <v>2026 Summer | IoT/embedded systems (Zigbee smart home).</v>
       </c>
       <c r="E95" t="str">
-        <v>https://www.nexperia.com</v>
+        <v>https://www.ubisys.de</v>
       </c>
       <c r="F95" t="str">
-        <v>Nijmegen, NL</v>
+        <v>Düsseldorf, DE</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -4858,33 +4858,33 @@
         <v/>
       </c>
       <c r="N95" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B96" t="str">
-        <v>Thales Nederland</v>
+        <v>Vodafone GmbH</v>
       </c>
       <c r="C96" t="str">
         <v>Researching</v>
       </c>
       <c r="D96" t="str">
-        <v>2026 Summer | Defense &amp; cybersecurity; secure systems ve embedded güvenlik odakli ekipler.</v>
+        <v>2026 Summer | Telecom network security ve sistem guvenligi ekipleri.</v>
       </c>
       <c r="E96" t="str">
-        <v>https://www.thalesgroup.com</v>
+        <v>https://www.vodafone.de</v>
       </c>
       <c r="F96" t="str">
-        <v>Hengelo, NL</v>
+        <v>Dusseldorf, DE</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -4905,33 +4905,33 @@
         <v/>
       </c>
       <c r="N96" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B97" t="str">
-        <v>Philips</v>
+        <v>Deutsche Börse Group</v>
       </c>
       <c r="C97" t="str">
         <v>Researching</v>
       </c>
       <c r="D97" t="str">
-        <v>2026 Summer | Medical/health-tech sistemler; embedded + güvenlik odakli ekipler.</v>
+        <v>2026 Summer | Large-scale systems; security &amp; reliability-focused roles.</v>
       </c>
       <c r="E97" t="str">
-        <v>https://www.philips.com</v>
+        <v>https://www.deutsche-boerse.com</v>
       </c>
       <c r="F97" t="str">
-        <v>Amsterdam, NL</v>
+        <v>Frankfurt, DE</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -4952,33 +4952,33 @@
         <v/>
       </c>
       <c r="N97" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B98" t="str">
-        <v>ASML</v>
+        <v>Adva Network Security</v>
       </c>
       <c r="C98" t="str">
         <v>Researching</v>
       </c>
       <c r="D98" t="str">
-        <v>2026 Summer | Semiconductor tooling; embedded + systems security odakli ekipler. Initiative application.</v>
+        <v>2026 Summer | Network security, encryption ve kritik altyapi guvenligi.</v>
       </c>
       <c r="E98" t="str">
-        <v>https://www.asml.com</v>
+        <v>https://www.advasecurity.com</v>
       </c>
       <c r="F98" t="str">
-        <v>Veldhoven, NL</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -4999,33 +4999,33 @@
         <v/>
       </c>
       <c r="N98" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 16:14:09</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B99" t="str">
-        <v>Rheinmetall</v>
+        <v>WebID Solutions</v>
       </c>
       <c r="C99" t="str">
         <v>Researching</v>
       </c>
       <c r="D99" t="str">
-        <v>2026 Summer | Guvenlik ve savunma teknolojileri, embedded/secure systems.</v>
+        <v>2026 Summer | Kimlik dogrulama ve guvenlik odakli sistemler.</v>
       </c>
       <c r="E99" t="str">
-        <v>https://www.rheinmetall.com</v>
+        <v>https://webid-solutions.com</v>
       </c>
       <c r="F99" t="str">
-        <v>Dusseldorf, DE</v>
+        <v>Berlin, DE</v>
       </c>
       <c r="G99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -5046,7 +5046,7 @@
         <v/>
       </c>
       <c r="N99" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O99" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5054,25 +5054,25 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B100" t="str">
-        <v>Henkel</v>
+        <v>Rohde &amp; Schwarz</v>
       </c>
       <c r="C100" t="str">
         <v>Researching</v>
       </c>
       <c r="D100" t="str">
-        <v>2026 Summer | Endustriyel IT/OT ve guvenlik odakli ekipler.</v>
+        <v>2026 Summer | Guvenli haberlesme, test/measurement, cybersecurity ekipleri.</v>
       </c>
       <c r="E100" t="str">
-        <v>https://www.henkel.com</v>
+        <v>https://www.rohde-schwarz.com</v>
       </c>
       <c r="F100" t="str">
-        <v>Dusseldorf, DE</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" t="str">
         <v/>
@@ -5093,7 +5093,7 @@
         <v/>
       </c>
       <c r="N100" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O100" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5101,25 +5101,25 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B101" t="str">
-        <v>DZ BANK</v>
+        <v>NXP Semiconductors</v>
       </c>
       <c r="C101" t="str">
         <v>Researching</v>
       </c>
       <c r="D101" t="str">
-        <v>2026 Summer | Finansal altyapi ve bilgi guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Embedded security, hardware-backed systems, SoC ve firmware odakli ekipler.</v>
       </c>
       <c r="E101" t="str">
-        <v>https://www.dzbank.com</v>
+        <v>https://www.nxp.com</v>
       </c>
       <c r="F101" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Eindhoven, NL</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H101" t="str">
         <v/>
@@ -5140,33 +5140,33 @@
         <v/>
       </c>
       <c r="N101" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:17:32</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B102" t="str">
-        <v>Deutsche Boerse Group</v>
+        <v>Infineon Technologies</v>
       </c>
       <c r="C102" t="str">
         <v>Researching</v>
       </c>
       <c r="D102" t="str">
-        <v>2026 Summer | Piyasa altyapisi, cyber protection ve sistem guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Semiconductor, embedded security ve hardware-backed systems.</v>
       </c>
       <c r="E102" t="str">
-        <v>https://www.deutsche-boerse.com</v>
+        <v>https://www.infineon.com</v>
       </c>
       <c r="F102" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H102" t="str">
         <v/>
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="N102" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O102" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5195,25 +5195,25 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B103" t="str">
-        <v>DekaBank</v>
+        <v>Porsche AG</v>
       </c>
       <c r="C103" t="str">
         <v>Researching</v>
       </c>
       <c r="D103" t="str">
-        <v>2026 Summer | Finans ve altyapi guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Embedded systems, firmware ve otomotiv guvenligi odakli roller. Initiative application.</v>
       </c>
       <c r="E103" t="str">
-        <v>https://www.deka.de</v>
+        <v>https://www.porsche.com</v>
       </c>
       <c r="F103" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H103" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="N103" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O103" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5242,22 +5242,22 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B104" t="str">
-        <v>Commerzbank</v>
+        <v>Bosch Rexroth</v>
       </c>
       <c r="C104" t="str">
         <v>Researching</v>
       </c>
       <c r="D104" t="str">
-        <v>2026 Summer | Finansal sistemler ve bilgi guvenligi odakli ekipler.</v>
+        <v>2026 Summer | Endustriyel otomasyon, kontrol sistemleri ve embedded guvenlik.</v>
       </c>
       <c r="E104" t="str">
-        <v>https://www.commerzbank.de</v>
+        <v>https://www.boschrexroth.com</v>
       </c>
       <c r="F104" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Bayern, DE</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -5281,7 +5281,7 @@
         <v/>
       </c>
       <c r="N104" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O104" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5289,22 +5289,22 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B105" t="str">
-        <v>Deutsche Bank</v>
+        <v>Vector Informatik</v>
       </c>
       <c r="C105" t="str">
         <v>Researching</v>
       </c>
       <c r="D105" t="str">
-        <v>2026 Summer | Banka altyapisi ve siber guvenlik odakli ekipler.</v>
+        <v>2026 Summer | Embedded software tooling, ECU ve sistem guvenligi odakli ekipler.</v>
       </c>
       <c r="E105" t="str">
-        <v>https://www.db.com</v>
+        <v>https://www.vector.com</v>
       </c>
       <c r="F105" t="str">
-        <v>Frankfurt, DE</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -5328,7 +5328,7 @@
         <v/>
       </c>
       <c r="N105" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O105" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5336,22 +5336,22 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B106" t="str">
-        <v>Giesecke+Devrient</v>
+        <v>ETAS GmbH</v>
       </c>
       <c r="C106" t="str">
         <v>Researching</v>
       </c>
       <c r="D106" t="str">
-        <v>2026 Summer | SecurityTech, kimlik ve secure hardware/embedded alanlari.</v>
+        <v>2026 Summer | Embedded tooling, ECU ve embedded security odakli ekipler.</v>
       </c>
       <c r="E106" t="str">
-        <v>https://www.gi-de.com</v>
+        <v>https://www.etas.com</v>
       </c>
       <c r="F106" t="str">
-        <v>Bayern, DE</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -5375,7 +5375,7 @@
         <v/>
       </c>
       <c r="N106" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O106" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B107" t="str">
-        <v>BMW Group</v>
+        <v>Robert Bosch GmbH</v>
       </c>
       <c r="C107" t="str">
         <v>Researching</v>
       </c>
       <c r="D107" t="str">
-        <v>2026 Summer | Otomotiv embedded, sistem guvenligi ve yazilim ekipleri.</v>
+        <v>2026 Summer | Embedded systems + security odakli ekipler. Initiative application.</v>
       </c>
       <c r="E107" t="str">
-        <v>https://www.bmwgroup.com</v>
+        <v>https://www.bosch.com</v>
       </c>
       <c r="F107" t="str">
-        <v>Bayern, DE</v>
+        <v>Stuttgart, DE</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H107" t="str">
         <v/>
@@ -5422,7 +5422,7 @@
         <v/>
       </c>
       <c r="N107" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 16:05:17</v>
       </c>
       <c r="O107" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5430,25 +5430,25 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B108" t="str">
-        <v>Siemens AG</v>
+        <v>VTT Teknik Arastirma Merkezi</v>
       </c>
       <c r="C108" t="str">
         <v>Researching</v>
       </c>
       <c r="D108" t="str">
-        <v>2026 Summer | Endustriyel sistemler, OT/ICS guvenligi ve embedded odakli ekipler.</v>
+        <v/>
       </c>
       <c r="E108" t="str">
-        <v>https://www.siemens.com</v>
+        <v/>
       </c>
       <c r="F108" t="str">
-        <v>Bayern, DE</v>
+        <v/>
       </c>
       <c r="G108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" t="str">
         <v/>
@@ -5469,33 +5469,33 @@
         <v/>
       </c>
       <c r="N108" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B109" t="str">
-        <v>Mercedes-Benz Group AG</v>
+        <v>Nordic Semiconductor</v>
       </c>
       <c r="C109" t="str">
         <v>Researching</v>
       </c>
       <c r="D109" t="str">
-        <v>2026 Summer | Otomotiv embedded/vehicle security odakli ekipler. Initiative application.</v>
+        <v/>
       </c>
       <c r="E109" t="str">
-        <v>https://group.mercedes-benz.com</v>
+        <v/>
       </c>
       <c r="F109" t="str">
-        <v>Stuttgart, DE</v>
+        <v/>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" t="str">
         <v/>
@@ -5516,33 +5516,33 @@
         <v/>
       </c>
       <c r="N109" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B110" t="str">
-        <v>ubisys technologies</v>
+        <v>SINTEF</v>
       </c>
       <c r="C110" t="str">
         <v>Researching</v>
       </c>
       <c r="D110" t="str">
-        <v>2026 Summer | IoT/embedded systems (Zigbee smart home).</v>
+        <v/>
       </c>
       <c r="E110" t="str">
-        <v>https://www.ubisys.de</v>
+        <v/>
       </c>
       <c r="F110" t="str">
-        <v>Düsseldorf, DE</v>
+        <v/>
       </c>
       <c r="G110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H110" t="str">
         <v/>
@@ -5563,33 +5563,33 @@
         <v/>
       </c>
       <c r="N110" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B111" t="str">
-        <v>Vodafone GmbH</v>
+        <v>RISE Araştirma Enstitileri</v>
       </c>
       <c r="C111" t="str">
         <v>Researching</v>
       </c>
       <c r="D111" t="str">
-        <v>2026 Summer | Telecom network security ve sistem guvenligi ekipleri.</v>
+        <v/>
       </c>
       <c r="E111" t="str">
-        <v>https://www.vodafone.de</v>
+        <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dusseldorf, DE</v>
+        <v/>
       </c>
       <c r="G111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" t="str">
         <v/>
@@ -5610,33 +5610,33 @@
         <v/>
       </c>
       <c r="N111" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B112" t="str">
-        <v>Deutsche Börse Group</v>
+        <v>Prodrive Technologies</v>
       </c>
       <c r="C112" t="str">
         <v>Researching</v>
       </c>
       <c r="D112" t="str">
-        <v>2026 Summer | Large-scale systems; security &amp; reliability-focused roles.</v>
+        <v/>
       </c>
       <c r="E112" t="str">
-        <v>https://www.deutsche-boerse.com</v>
+        <v/>
       </c>
       <c r="F112" t="str">
-        <v>Frankfurt, DE</v>
+        <v/>
       </c>
       <c r="G112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H112" t="str">
         <v/>
@@ -5657,30 +5657,30 @@
         <v/>
       </c>
       <c r="N112" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B113" t="str">
-        <v>Adva Network Security</v>
+        <v>Holst Centre</v>
       </c>
       <c r="C113" t="str">
         <v>Researching</v>
       </c>
       <c r="D113" t="str">
-        <v>2026 Summer | Network security, encryption ve kritik altyapi guvenligi.</v>
+        <v/>
       </c>
       <c r="E113" t="str">
-        <v>https://www.advasecurity.com</v>
+        <v/>
       </c>
       <c r="F113" t="str">
-        <v>Berlin, DE</v>
+        <v/>
       </c>
       <c r="G113">
         <v>1</v>
@@ -5704,33 +5704,33 @@
         <v/>
       </c>
       <c r="N113" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B114" t="str">
-        <v>WebID Solutions</v>
+        <v>TNO Embedded Systems Innovation (ESI)</v>
       </c>
       <c r="C114" t="str">
         <v>Researching</v>
       </c>
       <c r="D114" t="str">
-        <v>2026 Summer | Kimlik dogrulama ve guvenlik odakli sistemler.</v>
+        <v/>
       </c>
       <c r="E114" t="str">
-        <v>https://webid-solutions.com</v>
+        <v/>
       </c>
       <c r="F114" t="str">
-        <v>Berlin, DE</v>
+        <v/>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" t="str">
         <v/>
@@ -5751,33 +5751,33 @@
         <v/>
       </c>
       <c r="N114" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B115" t="str">
-        <v>Rohde &amp; Schwarz</v>
+        <v>Roke Manor Research</v>
       </c>
       <c r="C115" t="str">
         <v>Researching</v>
       </c>
       <c r="D115" t="str">
-        <v>2026 Summer | Guvenli haberlesme, test/measurement, cybersecurity ekipleri.</v>
+        <v>Videantis Hannover merkezli derin öğrenme, bilgisayarla görme ve video işleme çözümleri sağlayan bir şirkettir.</v>
       </c>
       <c r="E115" t="str">
-        <v>https://www.rohde-schwarz.com</v>
+        <v>https://www.videantis.com</v>
       </c>
       <c r="F115" t="str">
-        <v>Bayern, DE</v>
+        <v>Hannover, DE</v>
       </c>
       <c r="G115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" t="str">
         <v/>
@@ -5798,7 +5798,7 @@
         <v/>
       </c>
       <c r="N115" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O115" t="str">
         <v>2026-02-04 16:14:09</v>
@@ -5806,25 +5806,25 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B116" t="str">
-        <v>NXP Semiconductors</v>
+        <v>Cambridge Consultants</v>
       </c>
       <c r="C116" t="str">
         <v>Researching</v>
       </c>
       <c r="D116" t="str">
-        <v>2026 Summer | Embedded security, hardware-backed systems, SoC ve firmware odakli ekipler.</v>
+        <v/>
       </c>
       <c r="E116" t="str">
-        <v>https://www.nxp.com</v>
+        <v/>
       </c>
       <c r="F116" t="str">
-        <v>Eindhoven, NL</v>
+        <v/>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H116" t="str">
         <v/>
@@ -5845,33 +5845,33 @@
         <v/>
       </c>
       <c r="N116" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-02-04 16:17:32</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B117" t="str">
-        <v>Infineon Technologies</v>
+        <v>Videantis</v>
       </c>
       <c r="C117" t="str">
         <v>Researching</v>
       </c>
       <c r="D117" t="str">
-        <v>2026 Summer | Semiconductor, embedded security ve hardware-backed systems.</v>
+        <v/>
       </c>
       <c r="E117" t="str">
-        <v>https://www.infineon.com</v>
+        <v/>
       </c>
       <c r="F117" t="str">
-        <v>Bayern, DE</v>
+        <v/>
       </c>
       <c r="G117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H117" t="str">
         <v/>
@@ -5892,33 +5892,33 @@
         <v/>
       </c>
       <c r="N117" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B118" t="str">
-        <v>Porsche AG</v>
+        <v>FZI</v>
       </c>
       <c r="C118" t="str">
         <v>Researching</v>
       </c>
       <c r="D118" t="str">
-        <v>2026 Summer | Embedded systems, firmware ve otomotiv guvenligi odakli roller. Initiative application.</v>
+        <v/>
       </c>
       <c r="E118" t="str">
-        <v>https://www.porsche.com</v>
+        <v/>
       </c>
       <c r="F118" t="str">
-        <v>Stuttgart, DE</v>
+        <v/>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H118" t="str">
         <v/>
@@ -5939,30 +5939,30 @@
         <v/>
       </c>
       <c r="N118" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B119" t="str">
-        <v>Bosch Rexroth</v>
+        <v>DLR Robotik &amp; Mekatronik Enstitüsü</v>
       </c>
       <c r="C119" t="str">
         <v>Researching</v>
       </c>
       <c r="D119" t="str">
-        <v>2026 Summer | Endustriyel otomasyon, kontrol sistemleri ve embedded guvenlik.</v>
+        <v/>
       </c>
       <c r="E119" t="str">
-        <v>https://www.boschrexroth.com</v>
+        <v/>
       </c>
       <c r="F119" t="str">
-        <v>Bayern, DE</v>
+        <v/>
       </c>
       <c r="G119">
         <v>1</v>
@@ -5986,30 +5986,30 @@
         <v/>
       </c>
       <c r="N119" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B120" t="str">
-        <v>Vector Informatik</v>
+        <v>Sematicon AG</v>
       </c>
       <c r="C120" t="str">
-        <v>Researching</v>
+        <v>Applied</v>
       </c>
       <c r="D120" t="str">
-        <v>2026 Summer | Embedded software tooling, ECU ve sistem guvenligi odakli ekipler.</v>
+        <v>Akıllı sensörler; elektronik ve mekanik sistem entegrasyonu; endüstriyel gömülü çözümler</v>
       </c>
       <c r="E120" t="str">
-        <v>https://www.vector.com</v>
+        <v>https://www.lbf.fraunhofer.de</v>
       </c>
       <c r="F120" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Darmstadt</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -6033,33 +6033,33 @@
         <v/>
       </c>
       <c r="N120" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 15:44:52</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B121" t="str">
-        <v>ETAS GmbH</v>
+        <v>VDE Prüf- und Zertifizierungsinstitut</v>
       </c>
       <c r="C121" t="str">
         <v>Researching</v>
       </c>
       <c r="D121" t="str">
-        <v>2026 Summer | Embedded tooling, ECU ve embedded security odakli ekipler.</v>
+        <v>Elektronik ve gömülü sistem testleri; güvenlik, EMC ve donanım doğrulaması; sertifikasyon öncesi teknik analiz</v>
       </c>
       <c r="E121" t="str">
-        <v>https://www.etas.com</v>
+        <v>https://www.vde.com</v>
       </c>
       <c r="F121" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Offenbach</v>
       </c>
       <c r="G121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H121" t="str">
         <v/>
@@ -6080,33 +6080,33 @@
         <v/>
       </c>
       <c r="N121" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B122" t="str">
-        <v>Robert Bosch GmbH</v>
+        <v>ESCRYPT</v>
       </c>
       <c r="C122" t="str">
         <v>Researching</v>
       </c>
       <c r="D122" t="str">
-        <v>2026 Summer | Embedded systems + security odakli ekipler. Initiative application.</v>
+        <v>Otomotiv siber güvenliği; ECU, firmware ve gömülü güvenlik; güvenli yaşam döngüsü ve tehdit modelleme</v>
       </c>
       <c r="E122" t="str">
-        <v>https://www.bosch.com</v>
+        <v>https://www.escrypt.com</v>
       </c>
       <c r="F122" t="str">
-        <v>Stuttgart, DE</v>
+        <v>Frankfurt</v>
       </c>
       <c r="G122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H122" t="str">
         <v/>
@@ -6127,30 +6127,30 @@
         <v/>
       </c>
       <c r="N122" t="str">
-        <v>2026-02-04 16:05:17</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B123" t="str">
-        <v>VTT Teknik Arastirma Merkezi</v>
+        <v>ATHENE</v>
       </c>
       <c r="C123" t="str">
         <v>Researching</v>
       </c>
       <c r="D123" t="str">
-        <v/>
+        <v>Donanım destekli güvenlik; gömülü ve siber-fiziksel sistem güvenliği; endüstriyel ve kritik altyapı güvenliği</v>
       </c>
       <c r="E123" t="str">
-        <v/>
+        <v>https://www.athene-center.de</v>
       </c>
       <c r="F123" t="str">
-        <v/>
+        <v>Darmstadt</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -6182,22 +6182,22 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B124" t="str">
-        <v>Nordic Semiconductor</v>
+        <v>Fraunhofer IGD</v>
       </c>
       <c r="C124" t="str">
         <v>Researching</v>
       </c>
       <c r="D124" t="str">
-        <v/>
+        <v>Güvenli görselleştirme; endüstriyel yazılım-donanım entegrasyonu; sistem güvenliği + insan–makine etkileşimi</v>
       </c>
       <c r="E124" t="str">
-        <v/>
+        <v>https://www.igd.fraunhofer.de</v>
       </c>
       <c r="F124" t="str">
-        <v/>
+        <v>Darmstadt</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -6229,22 +6229,22 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B125" t="str">
-        <v>SINTEF</v>
+        <v>Rovenma</v>
       </c>
       <c r="C125" t="str">
         <v>Researching</v>
       </c>
       <c r="D125" t="str">
-        <v/>
+        <v>FPGA kripto</v>
       </c>
       <c r="E125" t="str">
-        <v/>
+        <v>https://www.rovenma.com</v>
       </c>
       <c r="F125" t="str">
-        <v/>
+        <v>Ankara</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -6276,22 +6276,22 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B126" t="str">
-        <v>RISE Araştirma Enstitileri</v>
+        <v>TÜBİTAK BİLGEM</v>
       </c>
       <c r="C126" t="str">
         <v>Researching</v>
       </c>
       <c r="D126" t="str">
-        <v/>
+        <v>Kriptoloji/Elektronik</v>
       </c>
       <c r="E126" t="str">
-        <v/>
+        <v>https://bilgem.tubitak.gov.tr</v>
       </c>
       <c r="F126" t="str">
-        <v/>
+        <v>Gebze</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B127" t="str">
-        <v>Prodrive Technologies</v>
+        <v>ProvenRun</v>
       </c>
       <c r="C127" t="str">
         <v>Researching</v>
       </c>
       <c r="D127" t="str">
-        <v/>
+        <v>Güvenli OS/TEE</v>
       </c>
       <c r="E127" t="str">
-        <v/>
+        <v>https://provenrun.com</v>
       </c>
       <c r="F127" t="str">
-        <v/>
+        <v>Paris</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -6370,25 +6370,25 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B128" t="str">
-        <v>Holst Centre</v>
+        <v>Secure-IC</v>
       </c>
       <c r="C128" t="str">
         <v>Researching</v>
       </c>
       <c r="D128" t="str">
-        <v/>
+        <v>SoC/FPGA IP</v>
       </c>
       <c r="E128" t="str">
-        <v/>
+        <v>https://www.secure-ic.com</v>
       </c>
       <c r="F128" t="str">
-        <v/>
+        <v>Rennes</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H128" t="str">
         <v/>
@@ -6417,25 +6417,25 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B129" t="str">
-        <v>TNO Embedded Systems Innovation (ESI)</v>
+        <v>Emproof</v>
       </c>
       <c r="C129" t="str">
         <v>Researching</v>
       </c>
       <c r="D129" t="str">
-        <v/>
+        <v>Anti-RE araçları</v>
       </c>
       <c r="E129" t="str">
-        <v/>
+        <v>https://www.emproof.com</v>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>Bochum</v>
       </c>
       <c r="G129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H129" t="str">
         <v/>
@@ -6464,22 +6464,22 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B130" t="str">
-        <v>Roke Manor Research</v>
+        <v>Riscure</v>
       </c>
       <c r="C130" t="str">
         <v>Researching</v>
       </c>
       <c r="D130" t="str">
-        <v>Videantis Hannover merkezli derin öğrenme, bilgisayarla görme ve video işleme çözümleri sağlayan bir şirkettir.</v>
+        <v>Güvenlik testleri</v>
       </c>
       <c r="E130" t="str">
-        <v>https://www.videantis.com</v>
+        <v>https://www.riscure.com</v>
       </c>
       <c r="F130" t="str">
-        <v>Hannover, DE</v>
+        <v>Delft</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -6506,27 +6506,27 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-02-04 16:14:09</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B131" t="str">
-        <v>Cambridge Consultants</v>
+        <v>IMEC</v>
       </c>
       <c r="C131" t="str">
         <v>Researching</v>
       </c>
       <c r="D131" t="str">
-        <v/>
+        <v>Yarıiletken Ar-Ge</v>
       </c>
       <c r="E131" t="str">
-        <v/>
+        <v>https://www.imec-int.com</v>
       </c>
       <c r="F131" t="str">
-        <v/>
+        <v>Leuven</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -6558,22 +6558,22 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B132" t="str">
-        <v>Videantis</v>
+        <v>KU Leuven</v>
       </c>
       <c r="C132" t="str">
         <v>Researching</v>
       </c>
       <c r="D132" t="str">
-        <v/>
+        <v>Physical attacks</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>https://www.esat.kuleuven.be</v>
       </c>
       <c r="F132" t="str">
-        <v/>
+        <v>Leuven</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B133" t="str">
-        <v>FZI</v>
+        <v>TU Graz - IAIK</v>
       </c>
       <c r="C133" t="str">
         <v>Researching</v>
       </c>
       <c r="D133" t="str">
-        <v/>
+        <v>RISC-V güvenliği</v>
       </c>
       <c r="E133" t="str">
-        <v/>
+        <v>https://www.iaik.tugraz.at</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>Graz</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -6652,22 +6652,22 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B134" t="str">
-        <v>DLR Robotik &amp; Mekatronik Enstitüsü</v>
+        <v>UniBW Münih</v>
       </c>
       <c r="C134" t="str">
         <v>Researching</v>
       </c>
       <c r="D134" t="str">
-        <v/>
+        <v>Gömülü kriptografi</v>
       </c>
       <c r="E134" t="str">
-        <v/>
+        <v>https://www.unibw.de</v>
       </c>
       <c r="F134" t="str">
-        <v/>
+        <v>Münih</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -6699,22 +6699,22 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="B135" t="str">
-        <v>Sematicon AG</v>
+        <v>HGI / MPI-SP</v>
       </c>
       <c r="C135" t="str">
-        <v>Applied</v>
+        <v>Researching</v>
       </c>
       <c r="D135" t="str">
-        <v>Akıllı sensörler; elektronik ve mekanik sistem entegrasyonu; endüstriyel gömülü çözümler</v>
+        <v>Donanım Trojan</v>
       </c>
       <c r="E135" t="str">
-        <v>https://www.lbf.fraunhofer.de</v>
+        <v>https://hgi.rub.de</v>
       </c>
       <c r="F135" t="str">
-        <v>Darmstadt</v>
+        <v>Bochum</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -6741,27 +6741,27 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-02-04 15:44:52</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B136" t="str">
-        <v>VDE Prüf- und Zertifizierungsinstitut</v>
+        <v>CISPA</v>
       </c>
       <c r="C136" t="str">
         <v>Researching</v>
       </c>
       <c r="D136" t="str">
-        <v>Elektronik ve gömülü sistem testleri; güvenlik, EMC ve donanım doğrulaması; sertifikasyon öncesi teknik analiz</v>
+        <v>Firmware güvenliği</v>
       </c>
       <c r="E136" t="str">
-        <v>https://www.vde.com</v>
+        <v>https://cispa.de</v>
       </c>
       <c r="F136" t="str">
-        <v>Offenbach</v>
+        <v>Saarbrücken</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -6793,22 +6793,22 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B137" t="str">
-        <v>ESCRYPT</v>
+        <v>Fraunhofer AISEC</v>
       </c>
       <c r="C137" t="str">
         <v>Researching</v>
       </c>
       <c r="D137" t="str">
-        <v>Otomotiv siber güvenliği; ECU, firmware ve gömülü güvenlik; güvenli yaşam döngüsü ve tehdit modelleme</v>
+        <v>Donanım güvenliği</v>
       </c>
       <c r="E137" t="str">
-        <v>https://www.escrypt.com</v>
+        <v>https://www.aisec.fraunhofer.de</v>
       </c>
       <c r="F137" t="str">
-        <v>Frankfurt</v>
+        <v>Münih</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -6840,22 +6840,22 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B138" t="str">
-        <v>ATHENE</v>
+        <v>Digital Worx</v>
       </c>
       <c r="C138" t="str">
         <v>Researching</v>
       </c>
       <c r="D138" t="str">
-        <v>Donanım destekli güvenlik; gömülü ve siber-fiziksel sistem güvenliği; endüstriyel ve kritik altyapı güvenliği</v>
+        <v>Mobil/IoT</v>
       </c>
       <c r="E138" t="str">
-        <v>https://www.athene-center.de</v>
+        <v>https://digital-worx.de</v>
       </c>
       <c r="F138" t="str">
-        <v>Darmstadt</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -6887,22 +6887,22 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B139" t="str">
-        <v>Fraunhofer IGD</v>
+        <v>diconium</v>
       </c>
       <c r="C139" t="str">
         <v>Researching</v>
       </c>
       <c r="D139" t="str">
-        <v>Güvenli görselleştirme; endüstriyel yazılım-donanım entegrasyonu; sistem güvenliği + insan–makine etkileşimi</v>
+        <v>Dijital dönüşüm</v>
       </c>
       <c r="E139" t="str">
-        <v>https://www.igd.fraunhofer.de</v>
+        <v>https://diconium.com</v>
       </c>
       <c r="F139" t="str">
-        <v>Darmstadt</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -6934,22 +6934,22 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B140" t="str">
-        <v>Rovenma</v>
+        <v>Zoi</v>
       </c>
       <c r="C140" t="str">
         <v>Researching</v>
       </c>
       <c r="D140" t="str">
-        <v>FPGA kripto</v>
+        <v>Bulut/IoT</v>
       </c>
       <c r="E140" t="str">
-        <v>https://www.rovenma.com</v>
+        <v>https://zoi.de</v>
       </c>
       <c r="F140" t="str">
-        <v>Ankara</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -6981,22 +6981,22 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B141" t="str">
-        <v>TÜBİTAK BİLGEM</v>
+        <v>tsenso</v>
       </c>
       <c r="C141" t="str">
         <v>Researching</v>
       </c>
       <c r="D141" t="str">
-        <v>Kriptoloji/Elektronik</v>
+        <v>Gıda takip</v>
       </c>
       <c r="E141" t="str">
-        <v>https://bilgem.tubitak.gov.tr</v>
+        <v>https://tsenso.com</v>
       </c>
       <c r="F141" t="str">
-        <v>Gebze</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B142" t="str">
-        <v>ProvenRun</v>
+        <v>vialytics</v>
       </c>
       <c r="C142" t="str">
         <v>Researching</v>
       </c>
       <c r="D142" t="str">
-        <v>Güvenli OS/TEE</v>
+        <v>Yol denetimi</v>
       </c>
       <c r="E142" t="str">
-        <v>https://provenrun.com</v>
+        <v>https://vialytics.com</v>
       </c>
       <c r="F142" t="str">
-        <v>Paris</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -7075,25 +7075,25 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B143" t="str">
-        <v>Secure-IC</v>
+        <v>BABLE</v>
       </c>
       <c r="C143" t="str">
         <v>Researching</v>
       </c>
       <c r="D143" t="str">
-        <v>SoC/FPGA IP</v>
+        <v>Akıllı şehirler</v>
       </c>
       <c r="E143" t="str">
-        <v>https://www.secure-ic.com</v>
+        <v>https://bable-smartcities.eu</v>
       </c>
       <c r="F143" t="str">
-        <v>Rennes</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143" t="str">
         <v/>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B144" t="str">
-        <v>Emproof</v>
+        <v>asvin</v>
       </c>
       <c r="C144" t="str">
         <v>Researching</v>
       </c>
       <c r="D144" t="str">
-        <v>Anti-RE araçları</v>
+        <v>IoT tedarik zinciri</v>
       </c>
       <c r="E144" t="str">
-        <v>https://www.emproof.com</v>
+        <v>https://asvin.io</v>
       </c>
       <c r="F144" t="str">
-        <v>Bochum</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -7169,22 +7169,22 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B145" t="str">
-        <v>Riscure</v>
+        <v>DevsUnity</v>
       </c>
       <c r="C145" t="str">
         <v>Researching</v>
       </c>
       <c r="D145" t="str">
-        <v>Güvenlik testleri</v>
+        <v>Yazılım danışmanlık</v>
       </c>
       <c r="E145" t="str">
-        <v>https://www.riscure.com</v>
+        <v>https://devsunity.com</v>
       </c>
       <c r="F145" t="str">
-        <v>Delft</v>
+        <v>Berlin</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -7216,22 +7216,22 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B146" t="str">
-        <v>IMEC</v>
+        <v>ProSec</v>
       </c>
       <c r="C146" t="str">
         <v>Researching</v>
       </c>
       <c r="D146" t="str">
-        <v>Yarıiletken Ar-Ge</v>
+        <v>OT ağ koruması</v>
       </c>
       <c r="E146" t="str">
-        <v>https://www.imec-int.com</v>
+        <v>https://www.prosec-networks.com</v>
       </c>
       <c r="F146" t="str">
-        <v>Leuven</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -7263,22 +7263,22 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B147" t="str">
-        <v>KU Leuven</v>
+        <v>Wire</v>
       </c>
       <c r="C147" t="str">
         <v>Researching</v>
       </c>
       <c r="D147" t="str">
-        <v>Physical attacks</v>
+        <v>Güvenli mesajlaşma</v>
       </c>
       <c r="E147" t="str">
-        <v>https://www.esat.kuleuven.be</v>
+        <v>https://wire.com</v>
       </c>
       <c r="F147" t="str">
-        <v>Leuven</v>
+        <v>Berlin</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B148" t="str">
-        <v>TU Graz - IAIK</v>
+        <v>Spyrosoft</v>
       </c>
       <c r="C148" t="str">
         <v>Researching</v>
       </c>
       <c r="D148" t="str">
-        <v>RISC-V güvenliği</v>
+        <v>Gömülü/Otomotiv</v>
       </c>
       <c r="E148" t="str">
-        <v>https://www.iaik.tugraz.at</v>
+        <v>https://spyro-soft.com</v>
       </c>
       <c r="F148" t="str">
-        <v>Graz</v>
+        <v>Stuttgart</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -7357,22 +7357,22 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B149" t="str">
-        <v>UniBW Münih</v>
+        <v>IT Designers</v>
       </c>
       <c r="C149" t="str">
         <v>Researching</v>
       </c>
       <c r="D149" t="str">
-        <v>Gömülü kriptografi</v>
+        <v>IoT yazılım</v>
       </c>
       <c r="E149" t="str">
-        <v>https://www.unibw.de</v>
+        <v>https://www.itdesigners.de</v>
       </c>
       <c r="F149" t="str">
-        <v>Münih</v>
+        <v>Frankfurt</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -7404,22 +7404,22 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B150" t="str">
-        <v>HGI / MPI-SP</v>
+        <v>Phoenix Contact</v>
       </c>
       <c r="C150" t="str">
         <v>Researching</v>
       </c>
       <c r="D150" t="str">
-        <v>Donanım Trojan</v>
+        <v>Siber güvenlik</v>
       </c>
       <c r="E150" t="str">
-        <v>https://hgi.rub.de</v>
+        <v>https://www.phoenixcontact.com</v>
       </c>
       <c r="F150" t="str">
-        <v>Bochum</v>
+        <v>Frankfurt</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -7451,22 +7451,22 @@
     </row>
     <row r="151">
       <c r="A151">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B151" t="str">
-        <v>CISPA</v>
+        <v>Fraunhofer IZM</v>
       </c>
       <c r="C151" t="str">
         <v>Researching</v>
       </c>
       <c r="D151" t="str">
-        <v>Firmware güvenliği</v>
+        <v>Mikroelektronik</v>
       </c>
       <c r="E151" t="str">
-        <v>https://cispa.de</v>
+        <v>https://www.izm.fraunhofer.de</v>
       </c>
       <c r="F151" t="str">
-        <v>Saarbrücken</v>
+        <v>Berlin</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -7498,22 +7498,22 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B152" t="str">
-        <v>Fraunhofer AISEC</v>
+        <v>Continental</v>
       </c>
       <c r="C152" t="str">
         <v>Researching</v>
       </c>
       <c r="D152" t="str">
-        <v>Donanım güvenliği</v>
+        <v>Otomotiv</v>
       </c>
       <c r="E152" t="str">
-        <v>https://www.aisec.fraunhofer.de</v>
+        <v>https://www.continental.com</v>
       </c>
       <c r="F152" t="str">
-        <v>Münih</v>
+        <v>Türkiye</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -7545,22 +7545,22 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B153" t="str">
-        <v>Digital Worx</v>
+        <v>Bosch</v>
       </c>
       <c r="C153" t="str">
         <v>Researching</v>
       </c>
       <c r="D153" t="str">
-        <v>Mobil/IoT</v>
+        <v>Otomotiv</v>
       </c>
       <c r="E153" t="str">
-        <v>https://digital-worx.de</v>
+        <v>https://www.bosch.com</v>
       </c>
       <c r="F153" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -7592,22 +7592,22 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B154" t="str">
-        <v>diconium</v>
+        <v>Infineon</v>
       </c>
       <c r="C154" t="str">
         <v>Researching</v>
       </c>
       <c r="D154" t="str">
-        <v>Dijital dönüşüm</v>
+        <v>Çip</v>
       </c>
       <c r="E154" t="str">
-        <v>https://diconium.com</v>
+        <v>https://www.infineon.com</v>
       </c>
       <c r="F154" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -7639,22 +7639,22 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B155" t="str">
-        <v>Zoi</v>
+        <v>STMicro</v>
       </c>
       <c r="C155" t="str">
         <v>Researching</v>
       </c>
       <c r="D155" t="str">
-        <v>Bulut/IoT</v>
+        <v>Çip</v>
       </c>
       <c r="E155" t="str">
-        <v>https://zoi.de</v>
+        <v>https://www.st.com</v>
       </c>
       <c r="F155" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -7686,22 +7686,22 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B156" t="str">
-        <v>tsenso</v>
+        <v>NXP</v>
       </c>
       <c r="C156" t="str">
         <v>Researching</v>
       </c>
       <c r="D156" t="str">
-        <v>Gıda takip</v>
+        <v>Çip</v>
       </c>
       <c r="E156" t="str">
-        <v>https://tsenso.com</v>
+        <v>https://www.nxp.com</v>
       </c>
       <c r="F156" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -7733,25 +7733,25 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B157" t="str">
-        <v>vialytics</v>
+        <v>Qualcomm</v>
       </c>
       <c r="C157" t="str">
         <v>Researching</v>
       </c>
       <c r="D157" t="str">
-        <v>Yol denetimi</v>
+        <v>SoC/çip</v>
       </c>
       <c r="E157" t="str">
-        <v>https://vialytics.com</v>
+        <v>https://www.qualcomm.com</v>
       </c>
       <c r="F157" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H157" t="str">
         <v/>
@@ -7780,22 +7780,22 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B158" t="str">
-        <v>BABLE</v>
+        <v>ARM</v>
       </c>
       <c r="C158" t="str">
         <v>Researching</v>
       </c>
       <c r="D158" t="str">
-        <v>Akıllı şehirler</v>
+        <v>Çekirdek IP</v>
       </c>
       <c r="E158" t="str">
-        <v>https://bable-smartcities.eu</v>
+        <v>https://www.arm.com</v>
       </c>
       <c r="F158" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -7827,22 +7827,22 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B159" t="str">
-        <v>asvin</v>
+        <v>Intel</v>
       </c>
       <c r="C159" t="str">
         <v>Researching</v>
       </c>
       <c r="D159" t="str">
-        <v>IoT tedarik zinciri</v>
+        <v>Yarıiletken</v>
       </c>
       <c r="E159" t="str">
-        <v>https://asvin.io</v>
+        <v>https://www.intel.com</v>
       </c>
       <c r="F159" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -7874,22 +7874,22 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B160" t="str">
-        <v>DevsUnity</v>
+        <v>Xiaomi</v>
       </c>
       <c r="C160" t="str">
         <v>Researching</v>
       </c>
       <c r="D160" t="str">
-        <v>Yazılım danışmanlık</v>
+        <v>Elektronik</v>
       </c>
       <c r="E160" t="str">
-        <v>https://devsunity.com</v>
+        <v>https://www.mi.com/tr</v>
       </c>
       <c r="F160" t="str">
-        <v>Berlin</v>
+        <v>Türkiye</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -7921,22 +7921,22 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B161" t="str">
-        <v>ProSec</v>
+        <v>LG</v>
       </c>
       <c r="C161" t="str">
         <v>Researching</v>
       </c>
       <c r="D161" t="str">
-        <v>OT ağ koruması</v>
+        <v>Elektronik</v>
       </c>
       <c r="E161" t="str">
-        <v>https://www.prosec-networks.com</v>
+        <v>https://www.lg.com/tr</v>
       </c>
       <c r="F161" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -7968,22 +7968,22 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B162" t="str">
-        <v>Wire</v>
+        <v>Samsung</v>
       </c>
       <c r="C162" t="str">
         <v>Researching</v>
       </c>
       <c r="D162" t="str">
-        <v>Güvenli mesajlaşma</v>
+        <v>Elektronik</v>
       </c>
       <c r="E162" t="str">
-        <v>https://wire.com</v>
+        <v>https://www.samsung.com/tr</v>
       </c>
       <c r="F162" t="str">
-        <v>Berlin</v>
+        <v>Türkiye</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B163" t="str">
-        <v>Spyrosoft</v>
+        <v>Apple</v>
       </c>
       <c r="C163" t="str">
         <v>Researching</v>
       </c>
       <c r="D163" t="str">
-        <v>Gömülü/Otomotiv</v>
+        <v>Tüketici teknoloji</v>
       </c>
       <c r="E163" t="str">
-        <v>https://spyro-soft.com</v>
+        <v>https://www.apple.com/tr</v>
       </c>
       <c r="F163" t="str">
-        <v>Stuttgart</v>
+        <v>Türkiye</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -8062,22 +8062,22 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B164" t="str">
-        <v>IT Designers</v>
+        <v>Amazon</v>
       </c>
       <c r="C164" t="str">
         <v>Researching</v>
       </c>
       <c r="D164" t="str">
-        <v>IoT yazılım</v>
+        <v>E-ticaret</v>
       </c>
       <c r="E164" t="str">
-        <v>https://www.itdesigners.de</v>
+        <v>https://www.amazon.com.tr</v>
       </c>
       <c r="F164" t="str">
-        <v>Frankfurt</v>
+        <v>Türkiye</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B165" t="str">
-        <v>Phoenix Contact</v>
+        <v>Google</v>
       </c>
       <c r="C165" t="str">
         <v>Researching</v>
       </c>
       <c r="D165" t="str">
-        <v>Siber güvenlik</v>
+        <v>Teknoloji</v>
       </c>
       <c r="E165" t="str">
-        <v>https://www.phoenixcontact.com</v>
+        <v>https://www.google.com</v>
       </c>
       <c r="F165" t="str">
-        <v>Frankfurt</v>
+        <v>Türkiye</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -8156,22 +8156,22 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B166" t="str">
-        <v>Fraunhofer IZM</v>
+        <v>Microsoft</v>
       </c>
       <c r="C166" t="str">
         <v>Researching</v>
       </c>
       <c r="D166" t="str">
-        <v>Mikroelektronik</v>
+        <v>Teknoloji</v>
       </c>
       <c r="E166" t="str">
-        <v>https://www.izm.fraunhofer.de</v>
+        <v>https://www.microsoft.com</v>
       </c>
       <c r="F166" t="str">
-        <v>Berlin</v>
+        <v>Türkiye</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -8203,19 +8203,19 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B167" t="str">
-        <v>Continental</v>
+        <v>SAP</v>
       </c>
       <c r="C167" t="str">
         <v>Researching</v>
       </c>
       <c r="D167" t="str">
-        <v>Otomotiv</v>
+        <v>Kurumsal yazılım</v>
       </c>
       <c r="E167" t="str">
-        <v>https://www.continental.com</v>
+        <v>https://www.sap.com/turkey</v>
       </c>
       <c r="F167" t="str">
         <v>Türkiye</v>
@@ -8250,19 +8250,19 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B168" t="str">
-        <v>Bosch</v>
+        <v>Huawei</v>
       </c>
       <c r="C168" t="str">
         <v>Researching</v>
       </c>
       <c r="D168" t="str">
-        <v>Otomotiv</v>
+        <v>Telekom altyapı</v>
       </c>
       <c r="E168" t="str">
-        <v>https://www.bosch.com</v>
+        <v>https://www.huawei.com/tr</v>
       </c>
       <c r="F168" t="str">
         <v>Türkiye</v>
@@ -8297,19 +8297,19 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B169" t="str">
-        <v>Infineon</v>
+        <v>Nokia</v>
       </c>
       <c r="C169" t="str">
         <v>Researching</v>
       </c>
       <c r="D169" t="str">
-        <v>Çip</v>
+        <v>Telekom altyapı</v>
       </c>
       <c r="E169" t="str">
-        <v>https://www.infineon.com</v>
+        <v>https://www.nokia.com</v>
       </c>
       <c r="F169" t="str">
         <v>Türkiye</v>
@@ -8344,19 +8344,19 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B170" t="str">
-        <v>STMicro</v>
+        <v>Ericsson</v>
       </c>
       <c r="C170" t="str">
         <v>Researching</v>
       </c>
       <c r="D170" t="str">
-        <v>Çip</v>
+        <v>Telekom altyapı</v>
       </c>
       <c r="E170" t="str">
-        <v>https://www.st.com</v>
+        <v>https://www.ericsson.com/tr</v>
       </c>
       <c r="F170" t="str">
         <v>Türkiye</v>
@@ -8391,19 +8391,19 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B171" t="str">
-        <v>NXP</v>
+        <v>Vodafone</v>
       </c>
       <c r="C171" t="str">
         <v>Researching</v>
       </c>
       <c r="D171" t="str">
-        <v>Çip</v>
+        <v>Telekom</v>
       </c>
       <c r="E171" t="str">
-        <v>https://www.nxp.com</v>
+        <v>https://www.vodafone.com.tr</v>
       </c>
       <c r="F171" t="str">
         <v>Türkiye</v>
@@ -8438,22 +8438,22 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B172" t="str">
-        <v>Qualcomm</v>
+        <v>Turkcell</v>
       </c>
       <c r="C172" t="str">
         <v>Researching</v>
       </c>
       <c r="D172" t="str">
-        <v>SoC/çip</v>
+        <v>2026 Summer | Telecom-scale systems, security engineering ve detection odakli ekipler.</v>
       </c>
       <c r="E172" t="str">
-        <v>https://www.qualcomm.com</v>
+        <v>https://www.turkcell.com.tr</v>
       </c>
       <c r="F172" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G172">
         <v>2</v>
@@ -8480,24 +8480,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B173" t="str">
-        <v>ARM</v>
+        <v>Mavi Jeans</v>
       </c>
       <c r="C173" t="str">
         <v>Researching</v>
       </c>
       <c r="D173" t="str">
-        <v>Çekirdek IP</v>
+        <v>Perakende</v>
       </c>
       <c r="E173" t="str">
-        <v>https://www.arm.com</v>
+        <v>https://www.mavi.com</v>
       </c>
       <c r="F173" t="str">
         <v>Türkiye</v>
@@ -8532,19 +8532,19 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B174" t="str">
-        <v>Intel</v>
+        <v>Obsidian</v>
       </c>
       <c r="C174" t="str">
         <v>Researching</v>
       </c>
       <c r="D174" t="str">
-        <v>Yarıiletken</v>
+        <v>Genel yazılım</v>
       </c>
       <c r="E174" t="str">
-        <v>https://www.intel.com</v>
+        <v>https://obsidian.md</v>
       </c>
       <c r="F174" t="str">
         <v>Türkiye</v>
@@ -8579,19 +8579,19 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B175" t="str">
-        <v>Xiaomi</v>
+        <v>KoçSistem</v>
       </c>
       <c r="C175" t="str">
         <v>Researching</v>
       </c>
       <c r="D175" t="str">
-        <v>Elektronik</v>
+        <v>BT hizmetleri</v>
       </c>
       <c r="E175" t="str">
-        <v>https://www.mi.com/tr</v>
+        <v>https://www.kocsistem.com.tr</v>
       </c>
       <c r="F175" t="str">
         <v>Türkiye</v>
@@ -8626,19 +8626,19 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B176" t="str">
-        <v>LG</v>
+        <v>Martı</v>
       </c>
       <c r="C176" t="str">
         <v>Researching</v>
       </c>
       <c r="D176" t="str">
-        <v>Elektronik</v>
+        <v>Mikromobilite</v>
       </c>
       <c r="E176" t="str">
-        <v>https://www.lg.com/tr</v>
+        <v>https://www.marti.tech</v>
       </c>
       <c r="F176" t="str">
         <v>Türkiye</v>
@@ -8673,19 +8673,19 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B177" t="str">
-        <v>Samsung</v>
+        <v>BiTaksi</v>
       </c>
       <c r="C177" t="str">
         <v>Researching</v>
       </c>
       <c r="D177" t="str">
-        <v>Elektronik</v>
+        <v>Ulaşım</v>
       </c>
       <c r="E177" t="str">
-        <v>https://www.samsung.com/tr</v>
+        <v>https://bitaksi.com</v>
       </c>
       <c r="F177" t="str">
         <v>Türkiye</v>
@@ -8720,19 +8720,19 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B178" t="str">
-        <v>Apple</v>
+        <v>Peak Games</v>
       </c>
       <c r="C178" t="str">
         <v>Researching</v>
       </c>
       <c r="D178" t="str">
-        <v>Tüketici teknoloji</v>
+        <v>Oyun</v>
       </c>
       <c r="E178" t="str">
-        <v>https://www.apple.com/tr</v>
+        <v>https://peak.com</v>
       </c>
       <c r="F178" t="str">
         <v>Türkiye</v>
@@ -8767,19 +8767,19 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B179" t="str">
-        <v>Amazon</v>
+        <v>Getir</v>
       </c>
       <c r="C179" t="str">
         <v>Researching</v>
       </c>
       <c r="D179" t="str">
-        <v>E-ticaret</v>
+        <v>Tüketici uygulaması</v>
       </c>
       <c r="E179" t="str">
-        <v>https://www.amazon.com.tr</v>
+        <v>https://getir.com</v>
       </c>
       <c r="F179" t="str">
         <v>Türkiye</v>
@@ -8814,19 +8814,19 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B180" t="str">
-        <v>Google</v>
+        <v>Hepsiburada</v>
       </c>
       <c r="C180" t="str">
         <v>Researching</v>
       </c>
       <c r="D180" t="str">
-        <v>Teknoloji</v>
+        <v>E-ticaret</v>
       </c>
       <c r="E180" t="str">
-        <v>https://www.google.com</v>
+        <v>https://www.hepsiburada.com</v>
       </c>
       <c r="F180" t="str">
         <v>Türkiye</v>
@@ -8861,19 +8861,19 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B181" t="str">
-        <v>Microsoft</v>
+        <v>Trendyol</v>
       </c>
       <c r="C181" t="str">
         <v>Researching</v>
       </c>
       <c r="D181" t="str">
-        <v>Teknoloji</v>
+        <v>E-ticaret</v>
       </c>
       <c r="E181" t="str">
-        <v>https://www.microsoft.com</v>
+        <v>https://www.trendyol.com</v>
       </c>
       <c r="F181" t="str">
         <v>Türkiye</v>
@@ -8908,19 +8908,19 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B182" t="str">
-        <v>SAP</v>
+        <v>Sahibinden.com</v>
       </c>
       <c r="C182" t="str">
         <v>Researching</v>
       </c>
       <c r="D182" t="str">
-        <v>Kurumsal yazılım</v>
+        <v>İnternet platformu</v>
       </c>
       <c r="E182" t="str">
-        <v>https://www.sap.com/turkey</v>
+        <v>https://www.sahibinden.com</v>
       </c>
       <c r="F182" t="str">
         <v>Türkiye</v>
@@ -8955,19 +8955,19 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B183" t="str">
-        <v>Huawei</v>
+        <v>Logo Yazılım</v>
       </c>
       <c r="C183" t="str">
         <v>Researching</v>
       </c>
       <c r="D183" t="str">
-        <v>Telekom altyapı</v>
+        <v>Kurumsal yazılım</v>
       </c>
       <c r="E183" t="str">
-        <v>https://www.huawei.com/tr</v>
+        <v>https://www.logo.com.tr</v>
       </c>
       <c r="F183" t="str">
         <v>Türkiye</v>
@@ -9002,19 +9002,19 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B184" t="str">
-        <v>Nokia</v>
+        <v>ASELSANNET</v>
       </c>
       <c r="C184" t="str">
         <v>Researching</v>
       </c>
       <c r="D184" t="str">
-        <v>Telekom altyapı</v>
+        <v>Ağ çözümleri</v>
       </c>
       <c r="E184" t="str">
-        <v>https://www.nokia.com</v>
+        <v>https://www.aselsannet.com.tr</v>
       </c>
       <c r="F184" t="str">
         <v>Türkiye</v>
@@ -9049,25 +9049,25 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B185" t="str">
-        <v>Ericsson</v>
+        <v>Roketsan</v>
       </c>
       <c r="C185" t="str">
         <v>Researching</v>
       </c>
       <c r="D185" t="str">
-        <v>Telekom altyapı</v>
+        <v>2026 Summer | Embedded systems, guidance/control ve güvenlik odakli ekipler.</v>
       </c>
       <c r="E185" t="str">
-        <v>https://www.ericsson.com/tr</v>
+        <v>https://www.roketsan.com.tr</v>
       </c>
       <c r="F185" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H185" t="str">
         <v/>
@@ -9091,24 +9091,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B186" t="str">
-        <v>Vodafone</v>
+        <v>Baykar</v>
       </c>
       <c r="C186" t="str">
         <v>Researching</v>
       </c>
       <c r="D186" t="str">
-        <v>Telekom</v>
+        <v>İHA sistemleri</v>
       </c>
       <c r="E186" t="str">
-        <v>https://www.vodafone.com.tr</v>
+        <v>https://www.baykartech.com</v>
       </c>
       <c r="F186" t="str">
         <v>Türkiye</v>
@@ -9143,25 +9143,25 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B187" t="str">
-        <v>Turkcell</v>
+        <v>TOGG</v>
       </c>
       <c r="C187" t="str">
         <v>Researching</v>
       </c>
       <c r="D187" t="str">
-        <v>2026 Summer | Telecom-scale systems, security engineering ve detection odakli ekipler.</v>
+        <v>Elektrikli araç</v>
       </c>
       <c r="E187" t="str">
-        <v>https://www.turkcell.com.tr</v>
+        <v>https://www.togg.com.tr</v>
       </c>
       <c r="F187" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" t="str">
         <v/>
@@ -9185,30 +9185,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B188" t="str">
-        <v>Mavi Jeans</v>
+        <v>Ford Otosan</v>
       </c>
       <c r="C188" t="str">
         <v>Researching</v>
       </c>
       <c r="D188" t="str">
-        <v>Perakende</v>
+        <v>2026 Summer | Otomotiv embedded, vehicle security ve sistem engineering odakli ekipler.</v>
       </c>
       <c r="E188" t="str">
-        <v>https://www.mavi.com</v>
+        <v>https://www.fordotosan.com.tr</v>
       </c>
       <c r="F188" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188" t="str">
         <v/>
@@ -9232,30 +9232,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B189" t="str">
-        <v>Obsidian</v>
+        <v>Vestel</v>
       </c>
       <c r="C189" t="str">
         <v>Researching</v>
       </c>
       <c r="D189" t="str">
-        <v>Genel yazılım</v>
+        <v>2026 Summer | IoT/embedded cihazlar ve güvenli ürün geliştirme odakli ekipler.</v>
       </c>
       <c r="E189" t="str">
-        <v>https://obsidian.md</v>
+        <v>https://www.vestel.com</v>
       </c>
       <c r="F189" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H189" t="str">
         <v/>
@@ -9279,24 +9279,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B190" t="str">
-        <v>KoçSistem</v>
+        <v>Yıldız Holding</v>
       </c>
       <c r="C190" t="str">
         <v>Researching</v>
       </c>
       <c r="D190" t="str">
-        <v>BT hizmetleri</v>
+        <v>Genel holding</v>
       </c>
       <c r="E190" t="str">
-        <v>https://www.kocsistem.com.tr</v>
+        <v>https://www.yildizholding.com.tr</v>
       </c>
       <c r="F190" t="str">
         <v>Türkiye</v>
@@ -9331,19 +9331,19 @@
     </row>
     <row r="191">
       <c r="A191">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B191" t="str">
-        <v>Martı</v>
+        <v>TÜBİTAK SAGE</v>
       </c>
       <c r="C191" t="str">
         <v>Researching</v>
       </c>
       <c r="D191" t="str">
-        <v>Mikromobilite</v>
+        <v>Savunma Ar-Ge</v>
       </c>
       <c r="E191" t="str">
-        <v>https://www.marti.tech</v>
+        <v>https://www.sage.tubitak.gov.tr</v>
       </c>
       <c r="F191" t="str">
         <v>Türkiye</v>
@@ -9378,25 +9378,25 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B192" t="str">
-        <v>BiTaksi</v>
+        <v>Havelsan</v>
       </c>
       <c r="C192" t="str">
         <v>Researching</v>
       </c>
       <c r="D192" t="str">
-        <v>Ulaşım</v>
+        <v>2026 Summer | Cybersecurity, command-control, simulation ve secure software odakli ekipler.</v>
       </c>
       <c r="E192" t="str">
-        <v>https://bitaksi.com</v>
+        <v>https://www.havelsan.com</v>
       </c>
       <c r="F192" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192" t="str">
         <v/>
@@ -9420,24 +9420,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B193" t="str">
-        <v>Peak Games</v>
+        <v>Beko</v>
       </c>
       <c r="C193" t="str">
         <v>Researching</v>
       </c>
       <c r="D193" t="str">
-        <v>Oyun</v>
+        <v>Tüketici elektroniği</v>
       </c>
       <c r="E193" t="str">
-        <v>https://peak.com</v>
+        <v>https://www.beko.com/tr-tr</v>
       </c>
       <c r="F193" t="str">
         <v>Türkiye</v>
@@ -9472,19 +9472,19 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B194" t="str">
-        <v>Getir</v>
+        <v>STM</v>
       </c>
       <c r="C194" t="str">
         <v>Researching</v>
       </c>
       <c r="D194" t="str">
-        <v>Tüketici uygulaması</v>
+        <v>Savunma ve siber güvenlik</v>
       </c>
       <c r="E194" t="str">
-        <v>https://getir.com</v>
+        <v>https://www.stm.com.tr</v>
       </c>
       <c r="F194" t="str">
         <v>Türkiye</v>
@@ -9519,19 +9519,19 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B195" t="str">
-        <v>Hepsiburada</v>
+        <v>Ansys</v>
       </c>
       <c r="C195" t="str">
         <v>Researching</v>
       </c>
       <c r="D195" t="str">
-        <v>E-ticaret</v>
+        <v>Emniyet-kritik gömülü sistem</v>
       </c>
       <c r="E195" t="str">
-        <v>https://www.hepsiburada.com</v>
+        <v>https://www.numesys.com.tr</v>
       </c>
       <c r="F195" t="str">
         <v>Türkiye</v>
@@ -9566,25 +9566,25 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B196" t="str">
-        <v>Trendyol</v>
+        <v>Türk Telekom</v>
       </c>
       <c r="C196" t="str">
         <v>Researching</v>
       </c>
       <c r="D196" t="str">
-        <v>E-ticaret</v>
+        <v>2026 Summer | Network/security ve large-scale systems odakli ekipler.</v>
       </c>
       <c r="E196" t="str">
-        <v>https://www.trendyol.com</v>
+        <v>https://www.turktelekom.com.tr/en</v>
       </c>
       <c r="F196" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H196" t="str">
         <v/>
@@ -9608,30 +9608,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B197" t="str">
-        <v>Sahibinden.com</v>
+        <v>Arçelik</v>
       </c>
       <c r="C197" t="str">
         <v>Researching</v>
       </c>
       <c r="D197" t="str">
-        <v>İnternet platformu</v>
+        <v>2026 Summer | Embedded/IoT cihazlar, secure firmware ve product security odakli ekipler.</v>
       </c>
       <c r="E197" t="str">
-        <v>https://www.sahibinden.com</v>
+        <v>https://www.arcelikglobal.com/en</v>
       </c>
       <c r="F197" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G197">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H197" t="str">
         <v/>
@@ -9655,24 +9655,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B198" t="str">
-        <v>Logo Yazılım</v>
+        <v>AET Elektronik</v>
       </c>
       <c r="C198" t="str">
         <v>Researching</v>
       </c>
       <c r="D198" t="str">
-        <v>Kurumsal yazılım</v>
+        <v>Elektronik ve telekom</v>
       </c>
       <c r="E198" t="str">
-        <v>https://www.logo.com.tr</v>
+        <v>https://www.aetelectronics.com</v>
       </c>
       <c r="F198" t="str">
         <v>Türkiye</v>
@@ -9707,19 +9707,19 @@
     </row>
     <row r="199">
       <c r="A199">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B199" t="str">
-        <v>ASELSANNET</v>
+        <v>Infrasis</v>
       </c>
       <c r="C199" t="str">
         <v>Researching</v>
       </c>
       <c r="D199" t="str">
-        <v>Ağ çözümleri</v>
+        <v>Siber mühendislik</v>
       </c>
       <c r="E199" t="str">
-        <v>https://www.aselsannet.com.tr</v>
+        <v>https://infrasis.com.tr</v>
       </c>
       <c r="F199" t="str">
         <v>Türkiye</v>
@@ -9754,25 +9754,25 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B200" t="str">
-        <v>Roketsan</v>
+        <v>Seccops</v>
       </c>
       <c r="C200" t="str">
         <v>Researching</v>
       </c>
       <c r="D200" t="str">
-        <v>2026 Summer | Embedded systems, guidance/control ve güvenlik odakli ekipler.</v>
+        <v>Kurumsal siber güvenlik</v>
       </c>
       <c r="E200" t="str">
-        <v>https://www.roketsan.com.tr</v>
+        <v>https://seccops.com</v>
       </c>
       <c r="F200" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H200" t="str">
         <v/>
@@ -9796,24 +9796,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B201" t="str">
-        <v>Baykar</v>
+        <v>Onex Yazılım</v>
       </c>
       <c r="C201" t="str">
         <v>Researching</v>
       </c>
       <c r="D201" t="str">
-        <v>İHA sistemleri</v>
+        <v>M2M ve gömülü yazılım</v>
       </c>
       <c r="E201" t="str">
-        <v>https://www.baykartech.com</v>
+        <v>https://onexyazilim.com</v>
       </c>
       <c r="F201" t="str">
         <v>Türkiye</v>
@@ -9848,19 +9848,19 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B202" t="str">
-        <v>TOGG</v>
+        <v>Inventra</v>
       </c>
       <c r="C202" t="str">
         <v>Researching</v>
       </c>
       <c r="D202" t="str">
-        <v>Elektrikli araç</v>
+        <v>Gömülü sistemler</v>
       </c>
       <c r="E202" t="str">
-        <v>https://www.togg.com.tr</v>
+        <v>https://www.inventra.com.tr</v>
       </c>
       <c r="F202" t="str">
         <v>Türkiye</v>
@@ -9895,25 +9895,25 @@
     </row>
     <row r="203">
       <c r="A203">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B203" t="str">
-        <v>Ford Otosan</v>
+        <v>Cyberwise</v>
       </c>
       <c r="C203" t="str">
         <v>Researching</v>
       </c>
       <c r="D203" t="str">
-        <v>2026 Summer | Otomotiv embedded, vehicle security ve sistem engineering odakli ekipler.</v>
+        <v>Entegre siber güvenlik</v>
       </c>
       <c r="E203" t="str">
-        <v>https://www.fordotosan.com.tr</v>
+        <v>https://cyberwise.com</v>
       </c>
       <c r="F203" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H203" t="str">
         <v/>
@@ -9937,30 +9937,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B204" t="str">
-        <v>Vestel</v>
+        <v>Desird Tasarım</v>
       </c>
       <c r="C204" t="str">
         <v>Researching</v>
       </c>
       <c r="D204" t="str">
-        <v>2026 Summer | IoT/embedded cihazlar ve güvenli ürün geliştirme odakli ekipler.</v>
+        <v>Mikrokontrol ve gömülü yazılım</v>
       </c>
       <c r="E204" t="str">
-        <v>https://www.vestel.com</v>
+        <v>https://desird.com</v>
       </c>
       <c r="F204" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H204" t="str">
         <v/>
@@ -9984,24 +9984,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B205" t="str">
-        <v>Yıldız Holding</v>
+        <v>Siemens</v>
       </c>
       <c r="C205" t="str">
         <v>Researching</v>
       </c>
       <c r="D205" t="str">
-        <v>Genel holding</v>
+        <v>Enerji ve otomasyon stajı</v>
       </c>
       <c r="E205" t="str">
-        <v>https://www.yildizholding.com.tr</v>
+        <v>https://www.siemens.com/tr</v>
       </c>
       <c r="F205" t="str">
         <v>Türkiye</v>
@@ -10036,25 +10036,25 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B206" t="str">
-        <v>TÜBİTAK SAGE</v>
+        <v>Aselsan</v>
       </c>
       <c r="C206" t="str">
         <v>Researching</v>
       </c>
       <c r="D206" t="str">
-        <v>Savunma Ar-Ge</v>
+        <v>2026 Summer | Embedded systems, defense tech and secure systems odakli ekipler.</v>
       </c>
       <c r="E206" t="str">
-        <v>https://www.sage.tubitak.gov.tr</v>
+        <v>https://www.aselsan.com/en</v>
       </c>
       <c r="F206" t="str">
-        <v>Türkiye</v>
+        <v>Turkey, TR</v>
       </c>
       <c r="G206">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H206" t="str">
         <v/>
@@ -10078,30 +10078,30 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-02-04 00:22:37</v>
+        <v>2026-02-04 16:19:45</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B207" t="str">
-        <v>Havelsan</v>
+        <v>ePati</v>
       </c>
       <c r="C207" t="str">
         <v>Researching</v>
       </c>
       <c r="D207" t="str">
-        <v>2026 Summer | Cybersecurity, command-control, simulation ve secure software odakli ekipler.</v>
+        <v>Yerli siber güvenlik ürünleri geliştiriyor</v>
       </c>
       <c r="E207" t="str">
-        <v>https://www.havelsan.com</v>
+        <v>https://www.technoscope.com.tr</v>
       </c>
       <c r="F207" t="str">
-        <v>Turkey, TR</v>
+        <v>Türkiye</v>
       </c>
       <c r="G207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H207" t="str">
         <v/>
@@ -10125,24 +10125,24 @@
         <v>2026-02-04 00:22:37</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-02-04 16:19:45</v>
+        <v>2026-02-04 00:22:37</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B208" t="str">
-        <v>Beko</v>
+        <v>Barikat</v>
       </c>
       <c r="C208" t="str">
         <v>Researching</v>
       </c>
       <c r="D208" t="str">
-        <v>Tüketici elektroniği</v>
+        <v>Siber güvenlik çözümleri sağlayıcısı</v>
       </c>
       <c r="E208" t="str">
-        <v>https://www.beko.com/tr-tr</v>
+        <v>Barikat</v>
       </c>
       <c r="F208" t="str">
         <v>Türkiye</v>
@@ -10177,19 +10177,19 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B209" t="str">
-        <v>STM</v>
+        <v>MELSiS</v>
       </c>
       <c r="C209" t="str">
         <v>Researching</v>
       </c>
       <c r="D209" t="str">
-        <v>Savunma ve siber güvenlik</v>
+        <v>Elektronik tasarım ve gömülü sistem çözümleri</v>
       </c>
       <c r="E209" t="str">
-        <v>https://www.stm.com.tr</v>
+        <v>MELSİS</v>
       </c>
       <c r="F209" t="str">
         <v>Türkiye</v>
@@ -10222,714 +10222,9 @@
         <v>2026-02-04 00:22:37</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210">
-        <v>15</v>
-      </c>
-      <c r="B210" t="str">
-        <v>Ansys</v>
-      </c>
-      <c r="C210" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D210" t="str">
-        <v>Emniyet-kritik gömülü sistem</v>
-      </c>
-      <c r="E210" t="str">
-        <v>https://www.numesys.com.tr</v>
-      </c>
-      <c r="F210" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G210">
-        <v>1</v>
-      </c>
-      <c r="H210" t="str">
-        <v/>
-      </c>
-      <c r="I210" t="str">
-        <v/>
-      </c>
-      <c r="J210" t="str">
-        <v/>
-      </c>
-      <c r="K210" t="str">
-        <v/>
-      </c>
-      <c r="L210" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M210" t="str">
-        <v/>
-      </c>
-      <c r="N210" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O210" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211">
-        <v>14</v>
-      </c>
-      <c r="B211" t="str">
-        <v>Türk Telekom</v>
-      </c>
-      <c r="C211" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026 Summer | Network/security ve large-scale systems odakli ekipler.</v>
-      </c>
-      <c r="E211" t="str">
-        <v>https://www.turktelekom.com.tr/en</v>
-      </c>
-      <c r="F211" t="str">
-        <v>Turkey, TR</v>
-      </c>
-      <c r="G211">
-        <v>2</v>
-      </c>
-      <c r="H211" t="str">
-        <v/>
-      </c>
-      <c r="I211" t="str">
-        <v/>
-      </c>
-      <c r="J211" t="str">
-        <v/>
-      </c>
-      <c r="K211" t="str">
-        <v/>
-      </c>
-      <c r="L211" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M211" t="str">
-        <v/>
-      </c>
-      <c r="N211" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O211" t="str">
-        <v>2026-02-04 16:19:45</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212">
-        <v>13</v>
-      </c>
-      <c r="B212" t="str">
-        <v>Arçelik</v>
-      </c>
-      <c r="C212" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026 Summer | Embedded/IoT cihazlar, secure firmware ve product security odakli ekipler.</v>
-      </c>
-      <c r="E212" t="str">
-        <v>https://www.arcelikglobal.com/en</v>
-      </c>
-      <c r="F212" t="str">
-        <v>Turkey, TR</v>
-      </c>
-      <c r="G212">
-        <v>3</v>
-      </c>
-      <c r="H212" t="str">
-        <v/>
-      </c>
-      <c r="I212" t="str">
-        <v/>
-      </c>
-      <c r="J212" t="str">
-        <v/>
-      </c>
-      <c r="K212" t="str">
-        <v/>
-      </c>
-      <c r="L212" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M212" t="str">
-        <v/>
-      </c>
-      <c r="N212" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O212" t="str">
-        <v>2026-02-04 16:19:45</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213">
-        <v>12</v>
-      </c>
-      <c r="B213" t="str">
-        <v>AET Elektronik</v>
-      </c>
-      <c r="C213" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D213" t="str">
-        <v>Elektronik ve telekom</v>
-      </c>
-      <c r="E213" t="str">
-        <v>https://www.aetelectronics.com</v>
-      </c>
-      <c r="F213" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G213">
-        <v>1</v>
-      </c>
-      <c r="H213" t="str">
-        <v/>
-      </c>
-      <c r="I213" t="str">
-        <v/>
-      </c>
-      <c r="J213" t="str">
-        <v/>
-      </c>
-      <c r="K213" t="str">
-        <v/>
-      </c>
-      <c r="L213" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M213" t="str">
-        <v/>
-      </c>
-      <c r="N213" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O213" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214">
-        <v>11</v>
-      </c>
-      <c r="B214" t="str">
-        <v>Infrasis</v>
-      </c>
-      <c r="C214" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D214" t="str">
-        <v>Siber mühendislik</v>
-      </c>
-      <c r="E214" t="str">
-        <v>https://infrasis.com.tr</v>
-      </c>
-      <c r="F214" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G214">
-        <v>1</v>
-      </c>
-      <c r="H214" t="str">
-        <v/>
-      </c>
-      <c r="I214" t="str">
-        <v/>
-      </c>
-      <c r="J214" t="str">
-        <v/>
-      </c>
-      <c r="K214" t="str">
-        <v/>
-      </c>
-      <c r="L214" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M214" t="str">
-        <v/>
-      </c>
-      <c r="N214" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O214" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215">
-        <v>10</v>
-      </c>
-      <c r="B215" t="str">
-        <v>Seccops</v>
-      </c>
-      <c r="C215" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D215" t="str">
-        <v>Kurumsal siber güvenlik</v>
-      </c>
-      <c r="E215" t="str">
-        <v>https://seccops.com</v>
-      </c>
-      <c r="F215" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G215">
-        <v>1</v>
-      </c>
-      <c r="H215" t="str">
-        <v/>
-      </c>
-      <c r="I215" t="str">
-        <v/>
-      </c>
-      <c r="J215" t="str">
-        <v/>
-      </c>
-      <c r="K215" t="str">
-        <v/>
-      </c>
-      <c r="L215" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M215" t="str">
-        <v/>
-      </c>
-      <c r="N215" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O215" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216">
-        <v>9</v>
-      </c>
-      <c r="B216" t="str">
-        <v>Onex Yazılım</v>
-      </c>
-      <c r="C216" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D216" t="str">
-        <v>M2M ve gömülü yazılım</v>
-      </c>
-      <c r="E216" t="str">
-        <v>https://onexyazilim.com</v>
-      </c>
-      <c r="F216" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G216">
-        <v>1</v>
-      </c>
-      <c r="H216" t="str">
-        <v/>
-      </c>
-      <c r="I216" t="str">
-        <v/>
-      </c>
-      <c r="J216" t="str">
-        <v/>
-      </c>
-      <c r="K216" t="str">
-        <v/>
-      </c>
-      <c r="L216" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M216" t="str">
-        <v/>
-      </c>
-      <c r="N216" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O216" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217">
-        <v>8</v>
-      </c>
-      <c r="B217" t="str">
-        <v>Inventra</v>
-      </c>
-      <c r="C217" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D217" t="str">
-        <v>Gömülü sistemler</v>
-      </c>
-      <c r="E217" t="str">
-        <v>https://www.inventra.com.tr</v>
-      </c>
-      <c r="F217" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G217">
-        <v>1</v>
-      </c>
-      <c r="H217" t="str">
-        <v/>
-      </c>
-      <c r="I217" t="str">
-        <v/>
-      </c>
-      <c r="J217" t="str">
-        <v/>
-      </c>
-      <c r="K217" t="str">
-        <v/>
-      </c>
-      <c r="L217" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M217" t="str">
-        <v/>
-      </c>
-      <c r="N217" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O217" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218">
-        <v>7</v>
-      </c>
-      <c r="B218" t="str">
-        <v>Cyberwise</v>
-      </c>
-      <c r="C218" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D218" t="str">
-        <v>Entegre siber güvenlik</v>
-      </c>
-      <c r="E218" t="str">
-        <v>https://cyberwise.com</v>
-      </c>
-      <c r="F218" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G218">
-        <v>1</v>
-      </c>
-      <c r="H218" t="str">
-        <v/>
-      </c>
-      <c r="I218" t="str">
-        <v/>
-      </c>
-      <c r="J218" t="str">
-        <v/>
-      </c>
-      <c r="K218" t="str">
-        <v/>
-      </c>
-      <c r="L218" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M218" t="str">
-        <v/>
-      </c>
-      <c r="N218" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O218" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219">
-        <v>6</v>
-      </c>
-      <c r="B219" t="str">
-        <v>Desird Tasarım</v>
-      </c>
-      <c r="C219" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D219" t="str">
-        <v>Mikrokontrol ve gömülü yazılım</v>
-      </c>
-      <c r="E219" t="str">
-        <v>https://desird.com</v>
-      </c>
-      <c r="F219" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G219">
-        <v>1</v>
-      </c>
-      <c r="H219" t="str">
-        <v/>
-      </c>
-      <c r="I219" t="str">
-        <v/>
-      </c>
-      <c r="J219" t="str">
-        <v/>
-      </c>
-      <c r="K219" t="str">
-        <v/>
-      </c>
-      <c r="L219" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M219" t="str">
-        <v/>
-      </c>
-      <c r="N219" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O219" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220">
-        <v>5</v>
-      </c>
-      <c r="B220" t="str">
-        <v>Siemens</v>
-      </c>
-      <c r="C220" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D220" t="str">
-        <v>Enerji ve otomasyon stajı</v>
-      </c>
-      <c r="E220" t="str">
-        <v>https://www.siemens.com/tr</v>
-      </c>
-      <c r="F220" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G220">
-        <v>1</v>
-      </c>
-      <c r="H220" t="str">
-        <v/>
-      </c>
-      <c r="I220" t="str">
-        <v/>
-      </c>
-      <c r="J220" t="str">
-        <v/>
-      </c>
-      <c r="K220" t="str">
-        <v/>
-      </c>
-      <c r="L220" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M220" t="str">
-        <v/>
-      </c>
-      <c r="N220" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O220" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221">
-        <v>4</v>
-      </c>
-      <c r="B221" t="str">
-        <v>Aselsan</v>
-      </c>
-      <c r="C221" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D221" t="str">
-        <v>2026 Summer | Embedded systems, defense tech and secure systems odakli ekipler.</v>
-      </c>
-      <c r="E221" t="str">
-        <v>https://www.aselsan.com/en</v>
-      </c>
-      <c r="F221" t="str">
-        <v>Turkey, TR</v>
-      </c>
-      <c r="G221">
-        <v>4</v>
-      </c>
-      <c r="H221" t="str">
-        <v/>
-      </c>
-      <c r="I221" t="str">
-        <v/>
-      </c>
-      <c r="J221" t="str">
-        <v/>
-      </c>
-      <c r="K221" t="str">
-        <v/>
-      </c>
-      <c r="L221" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M221" t="str">
-        <v/>
-      </c>
-      <c r="N221" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O221" t="str">
-        <v>2026-02-04 16:19:45</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222">
-        <v>3</v>
-      </c>
-      <c r="B222" t="str">
-        <v>ePati</v>
-      </c>
-      <c r="C222" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D222" t="str">
-        <v>Yerli siber güvenlik ürünleri geliştiriyor</v>
-      </c>
-      <c r="E222" t="str">
-        <v>https://www.technoscope.com.tr</v>
-      </c>
-      <c r="F222" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G222">
-        <v>1</v>
-      </c>
-      <c r="H222" t="str">
-        <v/>
-      </c>
-      <c r="I222" t="str">
-        <v/>
-      </c>
-      <c r="J222" t="str">
-        <v/>
-      </c>
-      <c r="K222" t="str">
-        <v/>
-      </c>
-      <c r="L222" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M222" t="str">
-        <v/>
-      </c>
-      <c r="N222" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O222" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223">
-        <v>2</v>
-      </c>
-      <c r="B223" t="str">
-        <v>Barikat</v>
-      </c>
-      <c r="C223" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D223" t="str">
-        <v>Siber güvenlik çözümleri sağlayıcısı</v>
-      </c>
-      <c r="E223" t="str">
-        <v>Barikat</v>
-      </c>
-      <c r="F223" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G223">
-        <v>1</v>
-      </c>
-      <c r="H223" t="str">
-        <v/>
-      </c>
-      <c r="I223" t="str">
-        <v/>
-      </c>
-      <c r="J223" t="str">
-        <v/>
-      </c>
-      <c r="K223" t="str">
-        <v/>
-      </c>
-      <c r="L223" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M223" t="str">
-        <v/>
-      </c>
-      <c r="N223" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O223" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224">
-        <v>1</v>
-      </c>
-      <c r="B224" t="str">
-        <v>MELSiS</v>
-      </c>
-      <c r="C224" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D224" t="str">
-        <v>Elektronik tasarım ve gömülü sistem çözümleri</v>
-      </c>
-      <c r="E224" t="str">
-        <v>MELSİS</v>
-      </c>
-      <c r="F224" t="str">
-        <v>Türkiye</v>
-      </c>
-      <c r="G224">
-        <v>1</v>
-      </c>
-      <c r="H224" t="str">
-        <v/>
-      </c>
-      <c r="I224" t="str">
-        <v/>
-      </c>
-      <c r="J224" t="str">
-        <v/>
-      </c>
-      <c r="K224" t="str">
-        <v/>
-      </c>
-      <c r="L224" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="M224" t="str">
-        <v/>
-      </c>
-      <c r="N224" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-      <c r="O224" t="str">
-        <v>2026-02-04 00:22:37</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O209"/>
   </ignoredErrors>
 </worksheet>
 </file>